--- a/CUQ/_docs/Notes.xlsx
+++ b/CUQ/_docs/Notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gregordudle/Developments/Semantic-SI/CUQ/_docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/n00002621/PycharmProjects/SI-Reference-Point-2023/CUQ/_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC655AC3-DD64-7B4A-80B4-F41D9A1D21A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE5A3D8-8FBC-3B49-ABA6-81F5E5BEC026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24200" yWindow="15460" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="en" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="673">
   <si>
     <t>id</t>
   </si>
@@ -178,9 +178,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>\text{A}</t>
-  </si>
-  <si>
     <t>Ampere second unit symbol</t>
   </si>
   <si>
@@ -202,9 +199,6 @@
     <t>Δ&lt;em&gt;ν&lt;/em&gt;&lt;sub&gt;Cs&lt;/sub&gt;</t>
   </si>
   <si>
-    <t>\Delta\nu_\text{Cs}</t>
-  </si>
-  <si>
     <t>Δ&amp;#x1D708;Cs</t>
   </si>
   <si>
@@ -220,9 +214,6 @@
     <t>m</t>
   </si>
   <si>
-    <t>\text{m}</t>
-  </si>
-  <si>
     <t>Speed of light constant value</t>
   </si>
   <si>
@@ -316,9 +307,6 @@
     <t>s</t>
   </si>
   <si>
-    <t>\text{s}</t>
-  </si>
-  <si>
     <t>Hyperfine cesium constant value</t>
   </si>
   <si>
@@ -352,9 +340,6 @@
     <t>kg</t>
   </si>
   <si>
-    <t>\text{kg}</t>
-  </si>
-  <si>
     <t>Planck constant symbol</t>
   </si>
   <si>
@@ -424,9 +409,6 @@
     <t>J</t>
   </si>
   <si>
-    <t>\text{J}</t>
-  </si>
-  <si>
     <t>Planck constant in SI unit symbol</t>
   </si>
   <si>
@@ -559,9 +541,6 @@
     <t>csis</t>
   </si>
   <si>
-    <t>^{133}\text{Cs}</t>
-  </si>
-  <si>
     <t>elmd</t>
   </si>
   <si>
@@ -733,9 +712,6 @@
     <t>wtps</t>
   </si>
   <si>
-    <t>T_{\text{TPW}}</t>
-  </si>
-  <si>
     <t>Water triple point value/unit</t>
   </si>
   <si>
@@ -835,9 +811,6 @@
     <t>mmcs</t>
   </si>
   <si>
-    <t>M(^{12}\text{C})</t>
-  </si>
-  <si>
     <t>Molar mass of carbon value</t>
   </si>
   <si>
@@ -862,9 +835,6 @@
     <t>mcos</t>
   </si>
   <si>
-    <t>M_{\text{u}}</t>
-  </si>
-  <si>
     <t>Molar mass constant value</t>
   </si>
   <si>
@@ -886,18 +856,12 @@
     <t>uams</t>
   </si>
   <si>
-    <t>m_{\text{u}}</t>
-  </si>
-  <si>
     <t>Unified atomic mass constant value</t>
   </si>
   <si>
     <t>uamv</t>
   </si>
   <si>
-    <t>m(^{12}{\text{C}})/12</t>
-  </si>
-  <si>
     <t>Molar mass of chemical definition</t>
   </si>
   <si>
@@ -979,18 +943,12 @@
     <t>hfcu</t>
   </si>
   <si>
-    <t>\text{Hz}</t>
-  </si>
-  <si>
     <t>Elementry chemical entity symbol</t>
   </si>
   <si>
     <t>eces</t>
   </si>
   <si>
-    <t>m(\text{X})</t>
-  </si>
-  <si>
     <t>Celcius temperature quantity equation</t>
   </si>
   <si>
@@ -1036,15 +994,9 @@
     <t>wpss</t>
   </si>
   <si>
-    <t>\text{W sr}^{-1}</t>
-  </si>
-  <si>
     <t>cans</t>
   </si>
   <si>
-    <t>\text{cd}</t>
-  </si>
-  <si>
     <t>Frequency symbol</t>
   </si>
   <si>
@@ -1084,9 +1036,6 @@
     <t>mols</t>
   </si>
   <si>
-    <t>\text{mol}</t>
-  </si>
-  <si>
     <t>Inverse mole unit symbol</t>
   </si>
   <si>
@@ -1099,9 +1048,6 @@
     <t>kims</t>
   </si>
   <si>
-    <t>\text{kg/mol}</t>
-  </si>
-  <si>
     <t>Relative atomic mass symbol</t>
   </si>
   <si>
@@ -1339,18 +1285,12 @@
     <t>wats</t>
   </si>
   <si>
-    <t>\text{W}</t>
-  </si>
-  <si>
     <t>Lumen unit symbol</t>
   </si>
   <si>
     <t>lums</t>
   </si>
   <si>
-    <t>\text{lm}</t>
-  </si>
-  <si>
     <t xml:space="preserve">@lums@\ @wats@^{-1} </t>
   </si>
   <si>
@@ -1366,9 +1306,6 @@
     <t>strs</t>
   </si>
   <si>
-    <t>\text{sr}</t>
-  </si>
-  <si>
     <t>Steradian unit symbol</t>
   </si>
   <si>
@@ -1414,9 +1351,6 @@
     <t>mpvu</t>
   </si>
   <si>
-    <t>571\ \text{mm}</t>
-  </si>
-  <si>
     <t>1\,650\,763.73</t>
   </si>
   <si>
@@ -1438,12 +1372,6 @@
     <t>dorb</t>
   </si>
   <si>
-    <t>2\text{p}^{10}</t>
-  </si>
-  <si>
-    <t>5\text{d}^{5}</t>
-  </si>
-  <si>
     <t>avos</t>
   </si>
   <si>
@@ -1492,21 +1420,6 @@
     <t>@cans@\ @strs@\ @wats@^{-1}</t>
   </si>
   <si>
-    <t>\text{K}</t>
-  </si>
-  <si>
-    <t>\text{C}</t>
-  </si>
-  <si>
-    <t>\text{H}</t>
-  </si>
-  <si>
-    <t>\text{N}</t>
-  </si>
-  <si>
-    <t>N_{\text{A}}</t>
-  </si>
-  <si>
     <t>Celcius to Kelvin offset (French)</t>
   </si>
   <si>
@@ -1585,9 +1498,6 @@
     <t>@cans@\:@strs@\:@kgms@^{-1}\:@mtrs@^{-2}\:@secs@^{3}</t>
   </si>
   <si>
-    <t>1\;@hfcu@ = \frac{@hfcs@}{@hfcv@}\ \text{or}\ 1\ @secs@ = \frac{@hfcv@}{@hfcs@}</t>
-  </si>
-  <si>
     <t>Candela unit in SI symbol</t>
   </si>
   <si>
@@ -1646,12 +1556,6 @@
   </si>
   <si>
     <t>The molar mass of any atom or molecule X may still be obtained from its relative atomic mass from the equation \[@mmxd@\] and the molar mass of any atom or molecule X is also related to the mass of the elementary entity @eces@ by the relation \[@mmed@\].</t>
-  </si>
-  <si>
-    <t>M(\text{X})</t>
-  </si>
-  <si>
-    <t>A_{\text{r}}(\text{X})</t>
   </si>
   <si>
     <t>In these equations @mcos@ is the molar mass constant, equal to @mcov@ and @uams@ is the unified atomic mass constant, equal to @uamv@. They are related to the Avogadro constant through the relation \[@mmav@\].</t>
@@ -1803,12 +1707,6 @@
     <t>lecs</t>
   </si>
   <si>
-    <t>luminous efficacy</t>
-  </si>
-  <si>
-    <t>K_{\text{cd}}</t>
-  </si>
-  <si>
     <t>ampere1948</t>
   </si>
   <si>
@@ -1942,6 +1840,225 @@
   </si>
   <si>
     <t>1\;@amps@ = \frac{1}{(@hfcv@)(@elmv@)}\,@hfcs@\;@elms@ \approx @icev@ @hfcs@\;@elms@</t>
+  </si>
+  <si>
+    <t>Volt unit symbol</t>
+  </si>
+  <si>
+    <t>vlts</t>
+  </si>
+  <si>
+    <t>webs</t>
+  </si>
+  <si>
+    <t>Weber unit symbol</t>
+  </si>
+  <si>
+    <t>\rm{A}</t>
+  </si>
+  <si>
+    <t>N_{\rm{A}}</t>
+  </si>
+  <si>
+    <t>\rm{cd}</t>
+  </si>
+  <si>
+    <t>\rm{C}</t>
+  </si>
+  <si>
+    <t>^{133}\rm{Cs}</t>
+  </si>
+  <si>
+    <t>5\rm{d}^{5}</t>
+  </si>
+  <si>
+    <t>m(\rm{X})</t>
+  </si>
+  <si>
+    <t>M(\rm{X})</t>
+  </si>
+  <si>
+    <t>\rm{H}</t>
+  </si>
+  <si>
+    <t>\rm{Hz}</t>
+  </si>
+  <si>
+    <t>\rm{J}</t>
+  </si>
+  <si>
+    <t>\rm{K}</t>
+  </si>
+  <si>
+    <t>\rm{kg}</t>
+  </si>
+  <si>
+    <t>\rm{kg/mol}</t>
+  </si>
+  <si>
+    <t>K_{\rm{cd}}</t>
+  </si>
+  <si>
+    <t>\rm{lm}</t>
+  </si>
+  <si>
+    <t>M_{\rm{u}}</t>
+  </si>
+  <si>
+    <t>M(^{12}\rm{C})</t>
+  </si>
+  <si>
+    <t>\rm{mol}</t>
+  </si>
+  <si>
+    <t>571\ \rm{mm}</t>
+  </si>
+  <si>
+    <t>\rm{m}</t>
+  </si>
+  <si>
+    <t>\rm{N}</t>
+  </si>
+  <si>
+    <t>2\rm{p}^{10}</t>
+  </si>
+  <si>
+    <t>A_{\rm{r}}(\rm{X})</t>
+  </si>
+  <si>
+    <t>1\;@hfcu@ = \frac{@hfcs@}{@hfcv@}\ \rm{or}\ 1\ @secs@ = \frac{@hfcv@}{@hfcs@}</t>
+  </si>
+  <si>
+    <t>\rm{s}</t>
+  </si>
+  <si>
+    <t>\rm{sr}</t>
+  </si>
+  <si>
+    <t>m_{\rm{u}}</t>
+  </si>
+  <si>
+    <t>m(^{12}{\rm{C}})/12</t>
+  </si>
+  <si>
+    <t>\rm{W}</t>
+  </si>
+  <si>
+    <t>\rm{W sr}^{-1}</t>
+  </si>
+  <si>
+    <t>\rm{Wb}</t>
+  </si>
+  <si>
+    <t>T_{\rm{TPW}}</t>
+  </si>
+  <si>
+    <t>luminous efficacy constant symbol</t>
+  </si>
+  <si>
+    <t>luminous efficacy constant value</t>
+  </si>
+  <si>
+    <t>lecv</t>
+  </si>
+  <si>
+    <t>@lecv@</t>
+  </si>
+  <si>
+    <t>\Delta\nu_{\rm{Cs}}</t>
+  </si>
+  <si>
+    <t>Hertz unit symbol</t>
+  </si>
+  <si>
+    <t>htzs</t>
+  </si>
+  <si>
+    <t>@htzs@</t>
+  </si>
+  <si>
+    <t>Becquerel unit symbol</t>
+  </si>
+  <si>
+    <t>becs</t>
+  </si>
+  <si>
+    <t>\rm{Bq}</t>
+  </si>
+  <si>
+    <t>\rm{V}</t>
+  </si>
+  <si>
+    <t>Farad unit symbol</t>
+  </si>
+  <si>
+    <t>fars</t>
+  </si>
+  <si>
+    <t>\rm{F}</t>
+  </si>
+  <si>
+    <t>Gray unit symbol</t>
+  </si>
+  <si>
+    <t>grys</t>
+  </si>
+  <si>
+    <t>\rm{Gy}</t>
+  </si>
+  <si>
+    <t>Sievert unit symbol</t>
+  </si>
+  <si>
+    <t>sevs</t>
+  </si>
+  <si>
+    <t>\rm{Sv}</t>
+  </si>
+  <si>
+    <t>Katal unit symbol</t>
+  </si>
+  <si>
+    <t>kats</t>
+  </si>
+  <si>
+    <t>\rm{kat}</t>
+  </si>
+  <si>
+    <t>Lux unit symbol</t>
+  </si>
+  <si>
+    <t>luxs</t>
+  </si>
+  <si>
+    <t>\rm{lx}</t>
+  </si>
+  <si>
+    <t>Pascal unit symbol</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>\rm{Pa}</t>
+  </si>
+  <si>
+    <t>Siemens unit symbol</t>
+  </si>
+  <si>
+    <t>sies</t>
+  </si>
+  <si>
+    <t>\rm{S}</t>
+  </si>
+  <si>
+    <t>Tesla unit symbol</t>
+  </si>
+  <si>
+    <t>tess</t>
+  </si>
+  <si>
+    <t>\rm{T}</t>
   </si>
 </sst>
 </file>
@@ -2847,10 +2964,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -2867,13 +2984,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>526</v>
+        <v>496</v>
       </c>
       <c r="E2" s="4">
         <v>44978.666134259256</v>
@@ -2884,7 +3001,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
@@ -2901,7 +3018,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -2918,7 +3035,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C5" s="2">
         <v>4</v>
@@ -2935,7 +3052,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
@@ -2952,13 +3069,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>540</v>
+        <v>508</v>
       </c>
       <c r="E7" s="4">
         <v>45104.336331018516</v>
@@ -2969,13 +3086,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>541</v>
+        <v>509</v>
       </c>
       <c r="E8" s="4">
         <v>45104.365567129629</v>
@@ -2986,13 +3103,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>542</v>
+        <v>510</v>
       </c>
       <c r="E9" s="4">
         <v>45105.140208333331</v>
@@ -3003,7 +3120,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
@@ -3020,7 +3137,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C11" s="2">
         <v>4</v>
@@ -3037,7 +3154,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C12" s="2">
         <v>5</v>
@@ -3054,7 +3171,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
@@ -3071,13 +3188,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="E14" s="4">
         <v>44978.666134259256</v>
@@ -3088,13 +3205,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="E15" s="4">
         <v>44978.666134259256</v>
@@ -3105,13 +3222,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="E16" s="4">
         <v>44978.666134259256</v>
@@ -3122,13 +3239,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C17" s="2">
         <v>4</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="E17" s="4">
         <v>44978.666134259256</v>
@@ -3139,13 +3256,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>527</v>
+        <v>497</v>
       </c>
       <c r="E18" s="4">
         <v>44978.666134259256</v>
@@ -3156,7 +3273,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
@@ -3173,7 +3290,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
@@ -3190,13 +3307,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C21" s="2">
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>528</v>
+        <v>498</v>
       </c>
       <c r="E21" s="4">
         <v>44978.666134259256</v>
@@ -3207,13 +3324,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C22" s="2">
         <v>5</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="E22" s="4">
         <v>44978.666134259256</v>
@@ -3224,13 +3341,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C23" s="2">
         <v>6</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="E23" s="4">
         <v>44978.666134259256</v>
@@ -3241,7 +3358,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C24" s="2">
         <v>7</v>
@@ -3258,13 +3375,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>535</v>
+        <v>505</v>
       </c>
       <c r="E25" s="4">
         <v>44978.666134259256</v>
@@ -3275,13 +3392,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="E26" s="4">
         <v>44978.666134259256</v>
@@ -3292,13 +3409,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="E27" s="4">
         <v>44978.666134259256</v>
@@ -3309,13 +3426,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C28" s="2">
         <v>4</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="E28" s="4">
         <v>44978.666134259256</v>
@@ -3326,13 +3443,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C29" s="2">
         <v>5</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>539</v>
+        <v>507</v>
       </c>
       <c r="E29" s="4">
         <v>44978.666134259256</v>
@@ -3343,7 +3460,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C30" s="2">
         <v>6</v>
@@ -3360,13 +3477,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
       <c r="E31" s="4">
         <v>44978.666134259256</v>
@@ -3377,13 +3494,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="E32" s="4">
         <v>44944.721134259256</v>
@@ -3394,7 +3511,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -3411,7 +3528,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
@@ -3428,7 +3545,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2">
         <v>2</v>
@@ -3445,7 +3562,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
@@ -3462,7 +3579,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C37" s="2">
         <v>2</v>
@@ -3479,7 +3596,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -3496,7 +3613,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C39" s="2">
         <v>2</v>
@@ -3513,7 +3630,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2">
         <v>3</v>
@@ -3530,7 +3647,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2">
         <v>2</v>
@@ -3547,7 +3664,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2">
         <v>3</v>
@@ -3564,7 +3681,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -3581,7 +3698,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2">
         <v>3</v>
@@ -3598,7 +3715,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2">
         <v>4</v>
@@ -3615,7 +3732,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -3632,13 +3749,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2">
         <v>4</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>621</v>
+        <v>587</v>
       </c>
       <c r="E47" s="4">
         <v>44944.732523148145</v>
@@ -3649,13 +3766,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>622</v>
+        <v>588</v>
       </c>
       <c r="E48" s="4">
         <v>44944.731400462966</v>
@@ -3666,7 +3783,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C49" s="2">
         <v>3</v>
@@ -3683,7 +3800,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C50" s="2">
         <v>2</v>
@@ -3703,13 +3820,13 @@
         <v>50</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>589</v>
+        <v>555</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="E53" s="8">
         <v>45126.62222222222</v>
@@ -3720,7 +3837,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>591</v>
+        <v>557</v>
       </c>
       <c r="D54" s="10"/>
     </row>
@@ -3729,13 +3846,13 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>593</v>
+        <v>559</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>595</v>
+        <v>561</v>
       </c>
       <c r="E55" s="8">
         <v>45126.62222222222</v>
@@ -3746,13 +3863,13 @@
         <v>53</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>593</v>
+        <v>559</v>
       </c>
       <c r="C56" s="2">
         <v>2</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>594</v>
+        <v>560</v>
       </c>
       <c r="E56" s="4">
         <v>45126.62222222222</v>
@@ -3763,13 +3880,13 @@
         <v>54</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>597</v>
+        <v>563</v>
       </c>
       <c r="E57" s="4">
         <v>45126.62222222222</v>
@@ -3780,13 +3897,13 @@
         <v>55</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>599</v>
+        <v>565</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>598</v>
+        <v>564</v>
       </c>
       <c r="E58" s="4">
         <v>45126.62222222222</v>
@@ -3797,13 +3914,13 @@
         <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>600</v>
+        <v>566</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>598</v>
+        <v>564</v>
       </c>
       <c r="E59" s="4">
         <v>45126.62222222222</v>
@@ -3814,13 +3931,13 @@
         <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>603</v>
+        <v>569</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>601</v>
+        <v>567</v>
       </c>
       <c r="E60" s="4">
         <v>45126.62222222222</v>
@@ -3831,13 +3948,13 @@
         <v>58</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>603</v>
+        <v>569</v>
       </c>
       <c r="C61" s="2">
         <v>2</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>602</v>
+        <v>568</v>
       </c>
       <c r="E61" s="4">
         <v>45126.62222222222</v>
@@ -3848,13 +3965,13 @@
         <v>59</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>604</v>
+        <v>570</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>592</v>
+        <v>558</v>
       </c>
       <c r="E62" s="4">
         <v>45126.62222222222</v>
@@ -3897,13 +4014,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>549</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" ht="34">
@@ -3911,13 +4028,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>554</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" ht="34">
@@ -3925,13 +4042,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>555</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" ht="34">
@@ -3939,13 +4056,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C5" s="2">
         <v>4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>556</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" ht="51">
@@ -3953,13 +4070,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>557</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" ht="17">
@@ -3967,13 +4084,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>558</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" ht="17">
@@ -3981,13 +4098,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" ht="34">
@@ -3995,13 +4112,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>560</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" ht="34">
@@ -4009,13 +4126,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>561</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" ht="34">
@@ -4023,13 +4140,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C11" s="2">
         <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>562</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4037,13 +4154,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C12" s="2">
         <v>5</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>563</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" ht="51">
@@ -4051,13 +4168,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>564</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4065,13 +4182,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>565</v>
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4079,13 +4196,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" ht="51">
@@ -4093,13 +4210,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" ht="68">
@@ -4107,13 +4224,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C17" s="2">
         <v>4</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>568</v>
+        <v>536</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" ht="34">
@@ -4121,13 +4238,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>569</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4135,13 +4252,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>570</v>
+        <v>538</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" ht="51">
@@ -4149,13 +4266,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" ht="68">
@@ -4163,13 +4280,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C21" s="2">
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>572</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" ht="85">
@@ -4177,13 +4294,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C22" s="2">
         <v>5</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>573</v>
+        <v>541</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" ht="34">
@@ -4191,13 +4308,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C23" s="2">
         <v>6</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>574</v>
+        <v>542</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4205,13 +4322,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C24" s="2">
         <v>7</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>575</v>
+        <v>543</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4219,13 +4336,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4233,13 +4350,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" ht="51">
@@ -4247,13 +4364,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>578</v>
+        <v>546</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" ht="85">
@@ -4261,13 +4378,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C28" s="2">
         <v>4</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>579</v>
+        <v>547</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="2" customFormat="1" ht="34">
@@ -4275,13 +4392,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C29" s="2">
         <v>5</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="2" customFormat="1" ht="85">
@@ -4289,13 +4406,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C30" s="2">
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="2" customFormat="1" ht="34">
@@ -4303,13 +4420,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="2" customFormat="1" ht="34">
@@ -4317,13 +4434,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>583</v>
+        <v>551</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4331,13 +4448,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>605</v>
+        <v>571</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4345,13 +4462,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>606</v>
+        <v>572</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4359,13 +4476,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2">
         <v>2</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>607</v>
+        <v>573</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4373,13 +4490,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>609</v>
+        <v>575</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4387,13 +4504,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C37" s="2">
         <v>2</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>610</v>
+        <v>576</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4401,13 +4518,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>612</v>
+        <v>578</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4415,13 +4532,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C39" s="2">
         <v>2</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>608</v>
+        <v>574</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4429,13 +4546,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2">
         <v>3</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>611</v>
+        <v>577</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4443,13 +4560,13 @@
         <v>51</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2">
         <v>2</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>619</v>
+        <v>585</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4457,13 +4574,13 @@
         <v>52</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2">
         <v>3</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>613</v>
+        <v>579</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4471,13 +4588,13 @@
         <v>53</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>615</v>
+        <v>581</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4485,13 +4602,13 @@
         <v>54</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2">
         <v>3</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>614</v>
+        <v>580</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4499,13 +4616,13 @@
         <v>55</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2">
         <v>4</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>616</v>
+        <v>582</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4513,13 +4630,13 @@
         <v>56</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>620</v>
+        <v>586</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4527,13 +4644,13 @@
         <v>57</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2">
         <v>4</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>621</v>
+        <v>587</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="2" customFormat="1" ht="17">
@@ -4541,13 +4658,13 @@
         <v>58</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>622</v>
+        <v>588</v>
       </c>
     </row>
     <row r="49" spans="1:5" s="2" customFormat="1" ht="17" customHeight="1">
@@ -4555,13 +4672,13 @@
         <v>59</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="C49" s="2">
         <v>3</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>618</v>
+        <v>584</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="2" customFormat="1" ht="34">
@@ -4569,13 +4686,13 @@
         <v>70</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C50" s="2">
         <v>2</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>617</v>
+        <v>583</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="17">
@@ -4583,13 +4700,13 @@
         <v>50</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>589</v>
+        <v>555</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>624</v>
+        <v>590</v>
       </c>
       <c r="E53" s="8"/>
     </row>
@@ -4598,7 +4715,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>591</v>
+        <v>557</v>
       </c>
       <c r="D54" s="10"/>
     </row>
@@ -4607,13 +4724,13 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>593</v>
+        <v>559</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>630</v>
+        <v>596</v>
       </c>
       <c r="E55" s="8"/>
     </row>
@@ -4622,13 +4739,13 @@
         <v>53</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>593</v>
+        <v>559</v>
       </c>
       <c r="C56" s="2">
         <v>2</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>625</v>
+        <v>591</v>
       </c>
       <c r="E56" s="4"/>
     </row>
@@ -4637,13 +4754,13 @@
         <v>54</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>627</v>
+        <v>593</v>
       </c>
       <c r="E57" s="4"/>
     </row>
@@ -4652,13 +4769,13 @@
         <v>55</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>599</v>
+        <v>565</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>626</v>
+        <v>592</v>
       </c>
       <c r="E58" s="4"/>
     </row>
@@ -4667,13 +4784,13 @@
         <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>600</v>
+        <v>566</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>626</v>
+        <v>592</v>
       </c>
       <c r="E59" s="4"/>
     </row>
@@ -4682,13 +4799,13 @@
         <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>603</v>
+        <v>569</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>628</v>
+        <v>594</v>
       </c>
       <c r="E60" s="4"/>
     </row>
@@ -4697,13 +4814,13 @@
         <v>58</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>603</v>
+        <v>569</v>
       </c>
       <c r="C61" s="2">
         <v>2</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>629</v>
+        <v>595</v>
       </c>
       <c r="E61" s="4"/>
     </row>
@@ -4712,13 +4829,13 @@
         <v>59</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>604</v>
+        <v>570</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>592</v>
+        <v>558</v>
       </c>
       <c r="E62" s="4"/>
     </row>
@@ -4747,7 +4864,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396D6CEF-66BA-914C-BC20-42B24F721DE4}">
-  <dimension ref="A1:I143"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
@@ -4764,10 +4881,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="C1" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D1" t="s">
         <v>32</v>
@@ -4793,16 +4910,16 @@
         <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D2" t="s">
         <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4810,16 +4927,16 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D3" t="s">
         <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4827,16 +4944,16 @@
         <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="D4" t="s">
         <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4844,16 +4961,16 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>633</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4861,16 +4978,16 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>506</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -4890,7 +5007,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>47</v>
+        <v>604</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>46</v>
@@ -4904,25 +5021,25 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
         <v>48</v>
       </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -4930,16 +5047,16 @@
         <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4947,16 +5064,16 @@
         <v>139</v>
       </c>
       <c r="B10" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -4964,16 +5081,16 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>552</v>
+        <v>520</v>
       </c>
       <c r="D11" t="s">
         <v>39</v>
       </c>
       <c r="E11" t="s">
+        <v>521</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4981,16 +5098,16 @@
         <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>489</v>
+        <v>605</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4998,16 +5115,16 @@
         <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D13" t="s">
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -5015,2472 +5132,2654 @@
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D14" t="s">
         <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15">
-        <v>52</v>
-      </c>
       <c r="B15" t="s">
-        <v>217</v>
+        <v>645</v>
       </c>
       <c r="D15" t="s">
         <v>39</v>
       </c>
       <c r="E15" t="s">
-        <v>218</v>
+        <v>646</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>219</v>
+        <v>647</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="D16" t="s">
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>370</v>
+        <v>211</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>514</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D17" t="s">
         <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>368</v>
+        <v>485</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>417</v>
+        <v>348</v>
       </c>
       <c r="D18" t="s">
         <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>416</v>
+        <v>349</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>418</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="D19" t="s">
         <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>253</v>
+        <v>353</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>254</v>
+        <v>354</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>320</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>304</v>
+        <v>245</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>305</v>
+        <v>246</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>534</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>518</v>
+        <v>290</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>335</v>
+        <v>490</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D24" t="s">
         <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>493</v>
+        <v>319</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>499</v>
+        <v>606</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="D25" t="s">
         <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>498</v>
+        <v>464</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>248</v>
+        <v>461</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>249</v>
+        <v>469</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>250</v>
+        <v>462</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>318</v>
+        <v>240</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E27" t="s">
-        <v>319</v>
+        <v>241</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>320</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>494</v>
+        <v>304</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s">
-        <v>497</v>
+        <v>305</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>495</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
       <c r="D29" t="s">
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>374</v>
+        <v>468</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>375</v>
+        <v>466</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
-        <v>245</v>
+        <v>467</v>
       </c>
       <c r="D30" t="s">
         <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>246</v>
+        <v>356</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>247</v>
+        <v>357</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D31" t="s">
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>512</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
+        <v>64</v>
+      </c>
+      <c r="B32" t="s">
+        <v>243</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33">
         <v>137</v>
       </c>
-      <c r="B32" t="s">
-        <v>501</v>
-      </c>
-      <c r="D32" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" t="s">
-        <v>502</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
       <c r="B33" t="s">
-        <v>517</v>
+        <v>472</v>
       </c>
       <c r="D33" t="s">
         <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>519</v>
+        <v>473</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>521</v>
+        <v>474</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34">
-        <v>10</v>
-      </c>
       <c r="B34" t="s">
-        <v>414</v>
+        <v>487</v>
       </c>
       <c r="D34" t="s">
         <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>415</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>77</v>
+        <v>489</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>78</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>396</v>
       </c>
       <c r="D35" t="s">
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>173</v>
+        <v>397</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>174</v>
+        <v>607</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36">
-        <v>122</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>445</v>
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>166</v>
       </c>
       <c r="D36" t="s">
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>446</v>
+        <v>167</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>447</v>
+        <v>608</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37">
-        <v>120</v>
-      </c>
-      <c r="B37" t="s">
-        <v>440</v>
+        <v>122</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>424</v>
       </c>
       <c r="D37" t="s">
         <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>484</v>
+        <v>426</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="B38" t="s">
-        <v>309</v>
+        <v>420</v>
       </c>
       <c r="D38" t="s">
         <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>310</v>
+        <v>421</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>311</v>
+        <v>460</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>465</v>
+        <v>297</v>
       </c>
       <c r="D39" t="s">
         <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>466</v>
+        <v>298</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>468</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="B40" t="s">
-        <v>224</v>
+        <v>443</v>
       </c>
       <c r="D40" t="s">
         <v>39</v>
       </c>
       <c r="E40" t="s">
-        <v>225</v>
+        <v>444</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>226</v>
+        <v>609</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D41" t="s">
         <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>315</v>
+        <v>220</v>
       </c>
       <c r="D42" t="s">
         <v>39</v>
       </c>
       <c r="E42" t="s">
-        <v>316</v>
+        <v>221</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>317</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>409</v>
+        <v>302</v>
       </c>
       <c r="D43" t="s">
         <v>39</v>
       </c>
       <c r="E43" t="s">
-        <v>175</v>
+        <v>303</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>424</v>
+        <v>610</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="D44" t="s">
         <v>39</v>
       </c>
       <c r="E44" t="s">
-        <v>412</v>
+        <v>168</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>524</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>66</v>
+        <v>392</v>
       </c>
       <c r="D45" t="s">
         <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>413</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>67</v>
+        <v>394</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>68</v>
+        <v>494</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D46" t="s">
         <v>39</v>
       </c>
       <c r="E46" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>428</v>
+        <v>65</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>357</v>
+        <v>71</v>
       </c>
       <c r="D47" t="s">
         <v>39</v>
       </c>
       <c r="E47" t="s">
-        <v>358</v>
+        <v>380</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>537</v>
+        <v>410</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>242</v>
+        <v>339</v>
       </c>
       <c r="D48" t="s">
         <v>39</v>
       </c>
       <c r="E48" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>244</v>
+        <v>611</v>
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49">
-        <v>107</v>
-      </c>
       <c r="B49" t="s">
-        <v>359</v>
+        <v>649</v>
       </c>
       <c r="D49" t="s">
         <v>39</v>
       </c>
       <c r="E49" t="s">
-        <v>360</v>
+        <v>650</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>531</v>
+        <v>651</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>336</v>
+        <v>234</v>
       </c>
       <c r="D50" t="s">
         <v>39</v>
       </c>
       <c r="E50" t="s">
-        <v>337</v>
+        <v>235</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>338</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D51" t="s">
         <v>39</v>
       </c>
       <c r="E51" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B52" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D52" t="s">
         <v>39</v>
       </c>
       <c r="E52" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="B53" t="s">
-        <v>183</v>
+        <v>309</v>
       </c>
       <c r="D53" t="s">
         <v>39</v>
       </c>
       <c r="E53" t="s">
-        <v>184</v>
+        <v>310</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>487</v>
+        <v>407</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>311</v>
       </c>
       <c r="D54" t="s">
         <v>39</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>54</v>
+        <v>312</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>57</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55">
-        <v>89</v>
-      </c>
       <c r="B55" t="s">
-        <v>312</v>
+        <v>652</v>
       </c>
       <c r="D55" t="s">
         <v>39</v>
       </c>
       <c r="E55" t="s">
-        <v>313</v>
+        <v>653</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>314</v>
+        <v>654</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
         <v>39</v>
       </c>
       <c r="E56" t="s">
-        <v>95</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>96</v>
+        <v>612</v>
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57">
-        <v>31</v>
-      </c>
       <c r="B57" t="s">
-        <v>404</v>
+        <v>642</v>
       </c>
       <c r="D57" t="s">
         <v>39</v>
       </c>
       <c r="E57" t="s">
-        <v>403</v>
+        <v>643</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>171</v>
+        <v>613</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="D58" t="s">
         <v>39</v>
       </c>
       <c r="E58" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>101</v>
+        <v>641</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="D59" t="s">
         <v>39</v>
       </c>
       <c r="E59" t="s">
-        <v>362</v>
+        <v>301</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>363</v>
+        <v>644</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
         <v>39</v>
       </c>
       <c r="E60" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
       <c r="D61" t="s">
         <v>39</v>
       </c>
       <c r="E61" t="s">
-        <v>449</v>
+        <v>385</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>450</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>239</v>
+        <v>94</v>
       </c>
       <c r="D62" t="s">
         <v>39</v>
       </c>
       <c r="E62" t="s">
-        <v>240</v>
-      </c>
-      <c r="F62" t="s">
-        <v>241</v>
+        <v>95</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>485</v>
+        <v>97</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>343</v>
       </c>
       <c r="D63" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="E63" t="s">
-        <v>142</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>143</v>
+        <v>344</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>143</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="D64" t="s">
         <v>39</v>
       </c>
       <c r="E64" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>158</v>
+        <v>614</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>427</v>
       </c>
       <c r="D65" t="s">
         <v>39</v>
       </c>
       <c r="E65" t="s">
-        <v>103</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>104</v>
+        <v>428</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>104</v>
+        <v>429</v>
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66">
-        <v>26</v>
-      </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>658</v>
       </c>
       <c r="D66" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="E66" t="s">
-        <v>145</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>146</v>
+        <v>659</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>148</v>
+        <v>660</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>451</v>
+        <v>231</v>
       </c>
       <c r="D67" t="s">
         <v>39</v>
       </c>
       <c r="E67" t="s">
-        <v>452</v>
+        <v>232</v>
+      </c>
+      <c r="F67" t="s">
+        <v>233</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>453</v>
+        <v>615</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>352</v>
+        <v>135</v>
       </c>
       <c r="D68" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E68" t="s">
-        <v>353</v>
+        <v>136</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>354</v>
+        <v>479</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>455</v>
+        <v>149</v>
       </c>
       <c r="D69" t="s">
         <v>39</v>
       </c>
       <c r="E69" t="s">
-        <v>456</v>
+        <v>150</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>454</v>
+        <v>152</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="B70" t="s">
-        <v>364</v>
+        <v>98</v>
       </c>
       <c r="D70" t="s">
         <v>39</v>
       </c>
       <c r="E70" t="s">
-        <v>365</v>
+        <v>99</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>453</v>
+        <v>616</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="D71" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E71" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>164</v>
+        <v>511</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="B72" t="s">
-        <v>587</v>
+        <v>430</v>
       </c>
       <c r="D72" t="s">
         <v>39</v>
       </c>
       <c r="E72" t="s">
-        <v>586</v>
+        <v>431</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>588</v>
+        <v>432</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B73" t="s">
-        <v>439</v>
+        <v>335</v>
       </c>
       <c r="D73" t="s">
         <v>39</v>
       </c>
       <c r="E73" t="s">
-        <v>483</v>
+        <v>336</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>438</v>
+        <v>617</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B74" t="s">
+        <v>434</v>
+      </c>
+      <c r="D74" t="s">
+        <v>39</v>
+      </c>
+      <c r="E74" t="s">
         <v>435</v>
       </c>
-      <c r="D74" t="s">
-        <v>39</v>
-      </c>
-      <c r="E74" t="s">
-        <v>436</v>
-      </c>
       <c r="G74" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="B75" t="s">
-        <v>273</v>
+        <v>346</v>
       </c>
       <c r="D75" t="s">
         <v>39</v>
       </c>
       <c r="E75" t="s">
-        <v>274</v>
+        <v>347</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>275</v>
+        <v>432</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="B76" t="s">
-        <v>276</v>
+        <v>155</v>
       </c>
       <c r="D76" t="s">
         <v>39</v>
       </c>
       <c r="E76" t="s">
-        <v>277</v>
+        <v>156</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>278</v>
+        <v>158</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="B77" t="s">
-        <v>291</v>
+        <v>637</v>
       </c>
       <c r="D77" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="E77" t="s">
-        <v>292</v>
+        <v>554</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78">
-        <v>71</v>
-      </c>
       <c r="B78" t="s">
-        <v>264</v>
+        <v>638</v>
       </c>
       <c r="D78" t="s">
         <v>39</v>
       </c>
       <c r="E78" t="s">
-        <v>265</v>
+        <v>639</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>266</v>
+        <v>328</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="B79" t="s">
-        <v>270</v>
+        <v>419</v>
       </c>
       <c r="D79" t="s">
         <v>39</v>
       </c>
       <c r="E79" t="s">
-        <v>271</v>
+        <v>459</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>272</v>
+        <v>418</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80">
+        <v>118</v>
+      </c>
+      <c r="B80" t="s">
+        <v>416</v>
+      </c>
+      <c r="D80" t="s">
+        <v>39</v>
+      </c>
+      <c r="E80" t="s">
+        <v>417</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="B81" t="s">
+        <v>661</v>
+      </c>
+      <c r="D81" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" t="s">
+        <v>662</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82">
+        <v>74</v>
+      </c>
+      <c r="B82" t="s">
+        <v>264</v>
+      </c>
+      <c r="D82" t="s">
+        <v>39</v>
+      </c>
+      <c r="E82" t="s">
+        <v>265</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83">
+        <v>75</v>
+      </c>
+      <c r="B83" t="s">
+        <v>266</v>
+      </c>
+      <c r="D83" t="s">
+        <v>39</v>
+      </c>
+      <c r="E83" t="s">
+        <v>267</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84">
+        <v>81</v>
+      </c>
+      <c r="B84" t="s">
+        <v>279</v>
+      </c>
+      <c r="D84" t="s">
+        <v>82</v>
+      </c>
+      <c r="E84" t="s">
+        <v>280</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85">
+        <v>71</v>
+      </c>
+      <c r="B85" t="s">
+        <v>256</v>
+      </c>
+      <c r="D85" t="s">
+        <v>39</v>
+      </c>
+      <c r="E85" t="s">
+        <v>257</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86">
+        <v>73</v>
+      </c>
+      <c r="B86" t="s">
+        <v>261</v>
+      </c>
+      <c r="D86" t="s">
+        <v>39</v>
+      </c>
+      <c r="E86" t="s">
+        <v>262</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87">
         <v>72</v>
       </c>
-      <c r="B80" t="s">
-        <v>267</v>
-      </c>
-      <c r="D80" t="s">
-        <v>39</v>
-      </c>
-      <c r="E80" t="s">
-        <v>268</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81">
+      <c r="B87" t="s">
+        <v>258</v>
+      </c>
+      <c r="D87" t="s">
+        <v>39</v>
+      </c>
+      <c r="E87" t="s">
+        <v>259</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B88" t="s">
+        <v>277</v>
+      </c>
+      <c r="D88" t="s">
+        <v>82</v>
+      </c>
+      <c r="E88" t="s">
+        <v>278</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
+        <v>79</v>
+      </c>
+      <c r="B89" t="s">
+        <v>275</v>
+      </c>
+      <c r="D89" t="s">
+        <v>82</v>
+      </c>
+      <c r="E89" t="s">
+        <v>276</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
+        <v>69</v>
+      </c>
+      <c r="B90" t="s">
+        <v>481</v>
+      </c>
+      <c r="D90" t="s">
+        <v>82</v>
+      </c>
+      <c r="E90" t="s">
+        <v>482</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91">
+        <v>103</v>
+      </c>
+      <c r="B91" t="s">
+        <v>333</v>
+      </c>
+      <c r="D91" t="s">
+        <v>39</v>
+      </c>
+      <c r="E91" t="s">
+        <v>401</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>102</v>
+      </c>
+      <c r="B92" t="s">
+        <v>331</v>
+      </c>
+      <c r="D92" t="s">
+        <v>39</v>
+      </c>
+      <c r="E92" t="s">
+        <v>332</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93">
+        <v>83</v>
+      </c>
+      <c r="B93" t="s">
+        <v>284</v>
+      </c>
+      <c r="D93" t="s">
+        <v>39</v>
+      </c>
+      <c r="E93" t="s">
+        <v>285</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94">
+        <v>82</v>
+      </c>
+      <c r="B94" t="s">
+        <v>281</v>
+      </c>
+      <c r="D94" t="s">
+        <v>39</v>
+      </c>
+      <c r="E94" t="s">
+        <v>282</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95">
+        <v>84</v>
+      </c>
+      <c r="B95" t="s">
+        <v>287</v>
+      </c>
+      <c r="D95" t="s">
+        <v>39</v>
+      </c>
+      <c r="E95" t="s">
+        <v>288</v>
+      </c>
+      <c r="G95" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D81" t="s">
-        <v>85</v>
-      </c>
-      <c r="E81" t="s">
-        <v>290</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
-      <c r="A82">
-        <v>79</v>
-      </c>
-      <c r="B82" t="s">
-        <v>287</v>
-      </c>
-      <c r="D82" t="s">
-        <v>85</v>
-      </c>
-      <c r="E82" t="s">
-        <v>288</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
-      <c r="A83">
-        <v>69</v>
-      </c>
-      <c r="B83" t="s">
-        <v>510</v>
-      </c>
-      <c r="D83" t="s">
-        <v>85</v>
-      </c>
-      <c r="E83" t="s">
-        <v>511</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84">
-        <v>103</v>
-      </c>
-      <c r="B84" t="s">
-        <v>350</v>
-      </c>
-      <c r="D84" t="s">
-        <v>39</v>
-      </c>
-      <c r="E84" t="s">
-        <v>419</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85">
-        <v>102</v>
-      </c>
-      <c r="B85" t="s">
-        <v>347</v>
-      </c>
-      <c r="D85" t="s">
-        <v>39</v>
-      </c>
-      <c r="E85" t="s">
-        <v>348</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86">
-        <v>83</v>
-      </c>
-      <c r="B86" t="s">
-        <v>296</v>
-      </c>
-      <c r="D86" t="s">
-        <v>39</v>
-      </c>
-      <c r="E86" t="s">
-        <v>297</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87">
-        <v>82</v>
-      </c>
-      <c r="B87" t="s">
-        <v>293</v>
-      </c>
-      <c r="D87" t="s">
-        <v>39</v>
-      </c>
-      <c r="E87" t="s">
-        <v>294</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88">
-        <v>84</v>
-      </c>
-      <c r="B88" t="s">
-        <v>299</v>
-      </c>
-      <c r="D88" t="s">
-        <v>39</v>
-      </c>
-      <c r="E88" t="s">
-        <v>300</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89">
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96">
         <v>99</v>
       </c>
-      <c r="B89" t="s">
-        <v>339</v>
-      </c>
-      <c r="D89" t="s">
-        <v>39</v>
-      </c>
-      <c r="E89" t="s">
-        <v>340</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90">
-        <v>87</v>
-      </c>
-      <c r="B90" t="s">
-        <v>306</v>
-      </c>
-      <c r="D90" t="s">
-        <v>39</v>
-      </c>
-      <c r="E90" t="s">
-        <v>307</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91">
-        <v>126</v>
-      </c>
-      <c r="B91" t="s">
-        <v>457</v>
-      </c>
-      <c r="D91" t="s">
-        <v>39</v>
-      </c>
-      <c r="E91" t="s">
-        <v>458</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
-      <c r="A92">
-        <v>12</v>
-      </c>
-      <c r="B92" t="s">
-        <v>84</v>
-      </c>
-      <c r="D92" t="s">
-        <v>85</v>
-      </c>
-      <c r="E92" t="s">
-        <v>86</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
-      <c r="A93">
-        <v>5</v>
-      </c>
-      <c r="B93" t="s">
-        <v>58</v>
-      </c>
-      <c r="D93" t="s">
-        <v>39</v>
-      </c>
-      <c r="E93" t="s">
-        <v>59</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9">
-      <c r="A94">
-        <v>127</v>
-      </c>
-      <c r="B94" t="s">
-        <v>461</v>
-      </c>
-      <c r="D94" t="s">
-        <v>39</v>
-      </c>
-      <c r="E94" t="s">
-        <v>462</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9">
-      <c r="A95">
-        <v>39</v>
-      </c>
-      <c r="B95" t="s">
-        <v>185</v>
-      </c>
-      <c r="D95" t="s">
-        <v>39</v>
-      </c>
-      <c r="E95" t="s">
-        <v>186</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9">
-      <c r="A96">
-        <v>138</v>
-      </c>
       <c r="B96" t="s">
-        <v>546</v>
+        <v>323</v>
       </c>
       <c r="D96" t="s">
         <v>39</v>
       </c>
       <c r="E96" t="s">
-        <v>547</v>
-      </c>
-      <c r="F96" t="s">
-        <v>548</v>
+        <v>324</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>548</v>
+        <v>325</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="B97" t="s">
-        <v>130</v>
+        <v>294</v>
       </c>
       <c r="D97" t="s">
         <v>39</v>
       </c>
       <c r="E97" t="s">
-        <v>131</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>132</v>
+        <v>295</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>422</v>
+        <v>296</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="B98" t="s">
-        <v>165</v>
+        <v>436</v>
       </c>
       <c r="D98" t="s">
         <v>39</v>
       </c>
       <c r="E98" t="s">
-        <v>166</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>167</v>
+        <v>437</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>170</v>
+        <v>623</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D99" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E99" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>109</v>
+        <v>480</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="D100" t="s">
         <v>39</v>
       </c>
       <c r="E100" t="s">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>120</v>
+        <v>624</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>439</v>
       </c>
       <c r="D101" t="s">
         <v>39</v>
       </c>
       <c r="E101" t="s">
-        <v>112</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>113</v>
+        <v>440</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>116</v>
+        <v>438</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B102" t="s">
-        <v>407</v>
+        <v>178</v>
       </c>
       <c r="D102" t="s">
         <v>39</v>
       </c>
       <c r="E102" t="s">
-        <v>408</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>545</v>
+        <v>625</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>463</v>
+        <v>514</v>
       </c>
       <c r="D103" t="s">
         <v>39</v>
       </c>
       <c r="E103" t="s">
-        <v>464</v>
+        <v>515</v>
+      </c>
+      <c r="F103" t="s">
+        <v>516</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>467</v>
+        <v>516</v>
       </c>
     </row>
     <row r="104" spans="1:9">
-      <c r="A104">
-        <v>95</v>
-      </c>
       <c r="B104" t="s">
-        <v>328</v>
+        <v>664</v>
       </c>
       <c r="D104" t="s">
         <v>39</v>
       </c>
       <c r="E104" t="s">
-        <v>329</v>
+        <v>665</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>330</v>
+        <v>666</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="B105" t="s">
-        <v>345</v>
+        <v>124</v>
       </c>
       <c r="D105" t="s">
         <v>39</v>
       </c>
       <c r="E105" t="s">
-        <v>346</v>
+        <v>125</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>515</v>
+        <v>403</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="B106" t="s">
-        <v>342</v>
+        <v>159</v>
       </c>
       <c r="D106" t="s">
         <v>39</v>
       </c>
       <c r="E106" t="s">
-        <v>343</v>
+        <v>160</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>344</v>
+        <v>162</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107">
+        <v>17</v>
+      </c>
+      <c r="B107" t="s">
+        <v>101</v>
+      </c>
+      <c r="D107" t="s">
+        <v>39</v>
+      </c>
+      <c r="E107" t="s">
+        <v>102</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H107" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B107" t="s">
-        <v>355</v>
-      </c>
-      <c r="D107" t="s">
-        <v>39</v>
-      </c>
-      <c r="E107" t="s">
-        <v>356</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>538</v>
+      <c r="I107" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108">
+        <v>19</v>
+      </c>
+      <c r="B108" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108" t="s">
+        <v>39</v>
+      </c>
+      <c r="E108" t="s">
+        <v>113</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G108" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B108" t="s">
-        <v>402</v>
-      </c>
-      <c r="D108" t="s">
-        <v>85</v>
-      </c>
-      <c r="E108" t="s">
-        <v>401</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>516</v>
+      <c r="H108" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="B109" t="s">
-        <v>477</v>
+        <v>106</v>
       </c>
       <c r="D109" t="s">
         <v>39</v>
       </c>
       <c r="E109" t="s">
-        <v>478</v>
+        <v>107</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>479</v>
+        <v>109</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>389</v>
       </c>
       <c r="D110" t="s">
         <v>39</v>
       </c>
       <c r="E110" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>123</v>
+        <v>512</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>125</v>
+        <v>513</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="B111" t="s">
-        <v>90</v>
+        <v>441</v>
       </c>
       <c r="D111" t="s">
         <v>39</v>
       </c>
       <c r="E111" t="s">
-        <v>91</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>92</v>
+        <v>442</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>92</v>
+        <v>626</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="B112" t="s">
-        <v>135</v>
+        <v>314</v>
       </c>
       <c r="D112" t="s">
         <v>39</v>
       </c>
       <c r="E112" t="s">
-        <v>136</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>137</v>
+        <v>315</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>140</v>
+        <v>316</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="B113" t="s">
-        <v>480</v>
+        <v>329</v>
       </c>
       <c r="D113" t="s">
         <v>39</v>
       </c>
       <c r="E113" t="s">
-        <v>481</v>
+        <v>330</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="B114" t="s">
-        <v>38</v>
+        <v>326</v>
       </c>
       <c r="D114" t="s">
         <v>39</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>42</v>
+        <v>640</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B115" t="s">
-        <v>70</v>
+        <v>337</v>
       </c>
       <c r="D115" t="s">
         <v>39</v>
       </c>
       <c r="E115" t="s">
-        <v>71</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>72</v>
+        <v>338</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>399</v>
+        <v>627</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>62</v>
+        <v>384</v>
       </c>
       <c r="D116" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E116" t="s">
-        <v>63</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>64</v>
+        <v>383</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>64</v>
+        <v>628</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>405</v>
+        <v>453</v>
       </c>
       <c r="D117" t="s">
         <v>39</v>
       </c>
       <c r="E117" t="s">
-        <v>406</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>80</v>
+        <v>454</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>83</v>
+        <v>455</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B118" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="D118" t="s">
         <v>39</v>
       </c>
       <c r="E118" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119">
-        <v>121</v>
+        <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>444</v>
+        <v>87</v>
       </c>
       <c r="D119" t="s">
         <v>39</v>
       </c>
       <c r="E119" t="s">
-        <v>442</v>
+        <v>88</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>443</v>
+        <v>629</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B120" t="s">
-        <v>222</v>
+        <v>129</v>
       </c>
       <c r="D120" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="E120" t="s">
-        <v>223</v>
+        <v>130</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>532</v>
+        <v>132</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="B121" t="s">
-        <v>220</v>
+        <v>456</v>
       </c>
       <c r="D121" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="E121" t="s">
-        <v>221</v>
+        <v>457</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>513</v>
+        <v>458</v>
       </c>
     </row>
     <row r="122" spans="1:9">
-      <c r="A122">
-        <v>92</v>
-      </c>
       <c r="B122" t="s">
-        <v>321</v>
+        <v>667</v>
       </c>
       <c r="D122" t="s">
         <v>39</v>
       </c>
       <c r="E122" t="s">
-        <v>241</v>
+        <v>668</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>322</v>
+        <v>669</v>
       </c>
     </row>
     <row r="123" spans="1:9">
-      <c r="A123">
-        <v>77</v>
-      </c>
       <c r="B123" t="s">
-        <v>281</v>
+        <v>655</v>
       </c>
       <c r="D123" t="s">
         <v>39</v>
       </c>
       <c r="E123" t="s">
-        <v>282</v>
+        <v>656</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>283</v>
+        <v>657</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>284</v>
+        <v>38</v>
       </c>
       <c r="D124" t="s">
         <v>39</v>
       </c>
       <c r="E124" t="s">
-        <v>285</v>
+        <v>40</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>286</v>
+        <v>42</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>205</v>
+        <v>67</v>
       </c>
       <c r="D125" t="s">
         <v>39</v>
       </c>
       <c r="E125" t="s">
-        <v>206</v>
+        <v>68</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>207</v>
+        <v>405</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="B126" t="s">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="D126" t="s">
         <v>39</v>
       </c>
       <c r="E126" t="s">
-        <v>197</v>
+        <v>60</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>198</v>
+        <v>62</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>202</v>
+        <v>387</v>
       </c>
       <c r="D127" t="s">
         <v>39</v>
       </c>
       <c r="E127" t="s">
-        <v>203</v>
+        <v>388</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>204</v>
+        <v>78</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B128" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="D128" t="s">
         <v>39</v>
       </c>
       <c r="E128" t="s">
-        <v>194</v>
+        <v>144</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>195</v>
+        <v>146</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="B129" t="s">
-        <v>214</v>
+        <v>423</v>
       </c>
       <c r="D129" t="s">
         <v>39</v>
       </c>
       <c r="E129" t="s">
-        <v>215</v>
+        <v>422</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>216</v>
+        <v>630</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B130" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D130" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E130" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B131" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="D131" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E131" t="s">
-        <v>200</v>
-      </c>
-      <c r="G131" t="s">
-        <v>201</v>
+        <v>214</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="B132" t="s">
-        <v>190</v>
+        <v>307</v>
       </c>
       <c r="D132" t="s">
         <v>39</v>
       </c>
       <c r="E132" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>192</v>
+        <v>308</v>
       </c>
     </row>
     <row r="133" spans="1:7">
-      <c r="A133">
-        <v>40</v>
-      </c>
       <c r="B133" t="s">
-        <v>187</v>
+        <v>670</v>
       </c>
       <c r="D133" t="s">
         <v>39</v>
       </c>
       <c r="E133" t="s">
-        <v>188</v>
+        <v>671</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>189</v>
+        <v>672</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="B134" t="s">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="D134" t="s">
         <v>39</v>
       </c>
       <c r="E134" t="s">
-        <v>181</v>
+        <v>272</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>182</v>
+        <v>631</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="B135" t="s">
-        <v>209</v>
+        <v>273</v>
       </c>
       <c r="D135" t="s">
         <v>39</v>
       </c>
       <c r="E135" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>211</v>
+        <v>632</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="B136" t="s">
-        <v>376</v>
+        <v>198</v>
       </c>
       <c r="D136" t="s">
         <v>39</v>
       </c>
       <c r="E136" t="s">
-        <v>377</v>
+        <v>199</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>378</v>
+        <v>200</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B137" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D137" t="s">
         <v>39</v>
       </c>
       <c r="E137" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>522</v>
+        <v>191</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="B138" t="s">
-        <v>432</v>
+        <v>195</v>
       </c>
       <c r="D138" t="s">
         <v>39</v>
       </c>
       <c r="E138" t="s">
-        <v>433</v>
+        <v>196</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>434</v>
+        <v>197</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="B139" t="s">
-        <v>331</v>
+        <v>186</v>
       </c>
       <c r="D139" t="s">
         <v>39</v>
       </c>
       <c r="E139" t="s">
-        <v>332</v>
+        <v>187</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>333</v>
+        <v>188</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B140" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="D140" t="s">
         <v>39</v>
       </c>
       <c r="E140" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B141" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="D141" t="s">
         <v>39</v>
       </c>
       <c r="E141" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>238</v>
+        <v>495</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B142" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="D142" t="s">
         <v>39</v>
       </c>
       <c r="E142" t="s">
-        <v>234</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>235</v>
+        <v>193</v>
+      </c>
+      <c r="G142" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143">
+        <v>41</v>
+      </c>
+      <c r="B143" t="s">
+        <v>183</v>
+      </c>
+      <c r="D143" t="s">
+        <v>39</v>
+      </c>
+      <c r="E143" t="s">
+        <v>184</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144">
+        <v>40</v>
+      </c>
+      <c r="B144" t="s">
+        <v>180</v>
+      </c>
+      <c r="D144" t="s">
+        <v>39</v>
+      </c>
+      <c r="E144" t="s">
+        <v>181</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145">
+        <v>37</v>
+      </c>
+      <c r="B145" t="s">
+        <v>173</v>
+      </c>
+      <c r="D145" t="s">
+        <v>39</v>
+      </c>
+      <c r="E145" t="s">
+        <v>174</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146">
+        <v>48</v>
+      </c>
+      <c r="B146" t="s">
+        <v>202</v>
+      </c>
+      <c r="D146" t="s">
+        <v>39</v>
+      </c>
+      <c r="E146" t="s">
+        <v>203</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147">
+        <v>114</v>
+      </c>
+      <c r="B147" t="s">
+        <v>358</v>
+      </c>
+      <c r="D147" t="s">
+        <v>39</v>
+      </c>
+      <c r="E147" t="s">
+        <v>359</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148">
+        <v>47</v>
+      </c>
+      <c r="B148" t="s">
+        <v>180</v>
+      </c>
+      <c r="D148" t="s">
+        <v>39</v>
+      </c>
+      <c r="E148" t="s">
+        <v>201</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="B149" t="s">
+        <v>600</v>
+      </c>
+      <c r="D149" t="s">
+        <v>39</v>
+      </c>
+      <c r="E149" t="s">
+        <v>601</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150">
+        <v>117</v>
+      </c>
+      <c r="B150" t="s">
+        <v>414</v>
+      </c>
+      <c r="D150" t="s">
+        <v>39</v>
+      </c>
+      <c r="E150" t="s">
+        <v>415</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151">
+        <v>96</v>
+      </c>
+      <c r="B151" t="s">
+        <v>317</v>
+      </c>
+      <c r="D151" t="s">
+        <v>39</v>
+      </c>
+      <c r="E151" t="s">
+        <v>318</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="B152" t="s">
+        <v>603</v>
+      </c>
+      <c r="D152" t="s">
+        <v>39</v>
+      </c>
+      <c r="E152" t="s">
+        <v>602</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153">
+        <v>57</v>
+      </c>
+      <c r="B153" t="s">
+        <v>223</v>
+      </c>
+      <c r="D153" t="s">
+        <v>39</v>
+      </c>
+      <c r="E153" t="s">
+        <v>224</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154">
+        <v>59</v>
+      </c>
+      <c r="B154" t="s">
+        <v>228</v>
+      </c>
+      <c r="D154" t="s">
+        <v>39</v>
+      </c>
+      <c r="E154" t="s">
+        <v>229</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155">
+        <v>58</v>
+      </c>
+      <c r="B155" t="s">
+        <v>225</v>
+      </c>
+      <c r="D155" t="s">
+        <v>39</v>
+      </c>
+      <c r="E155" t="s">
+        <v>226</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156">
         <v>136</v>
       </c>
-      <c r="B143" t="s">
-        <v>500</v>
-      </c>
-      <c r="D143" t="s">
-        <v>39</v>
-      </c>
-      <c r="E143" t="s">
-        <v>505</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>504</v>
+      <c r="B156" t="s">
+        <v>471</v>
+      </c>
+      <c r="D156" t="s">
+        <v>39</v>
+      </c>
+      <c r="E156" t="s">
+        <v>476</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I143">
-    <sortCondition ref="E2:E143"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I156">
+    <sortCondition ref="E2:E156"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="G131" r:id="rId1" xr:uid="{A7EDDAF4-0BC6-5047-97F5-7FCD19354202}"/>
+    <hyperlink ref="G142" r:id="rId1" xr:uid="{A7EDDAF4-0BC6-5047-97F5-7FCD19354202}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CUQ/_docs/Notes.xlsx
+++ b/CUQ/_docs/Notes.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/n00002621/PycharmProjects/SI-Reference-Point-2023/CUQ/_docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gruber04\git_repos\BIPM\Semantic-SI\CUQ\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE5A3D8-8FBC-3B49-ABA6-81F5E5BEC026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6E7C8C-F8F3-4836-B380-1BEE1E4BE94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24200" yWindow="15460" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-8310" windowWidth="38640" windowHeight="21390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="en" sheetId="1" r:id="rId1"/>
     <sheet name="fr" sheetId="2" r:id="rId2"/>
     <sheet name="symbols" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -67,9 +67,6 @@
     <t>The previous definition of the kilogram fixed the value of the mass of the international prototype of the kilogram, @kgmp@, to be equal to one kilogram exactly and the value of the Planck constant @plks@ had to be determined by experiment. The present definition fixes the numerical value of @plks@ exactly and the mass of the prototype has now to be determined by experiment.</t>
   </si>
   <si>
-    <t>Note that with the present definition, primary realizations of the Kelvin can, in principle, be established at any point of the temperature scale.</t>
-  </si>
-  <si>
     <t>In the name "amount of substance", the word "substance" will typically be replaced by words to specify the substance concerned in any particular application, for example "amount of hydrogen chloride", or "amount of benzene". It is important to give a precise definition of the entity involved (as emphasized in the definition of the mole); this should preferably be done by specifying the molecular chemical formula of the material involved. Although the word "amount" has a more general dictionary definition, the abbreviation of the full name "amount of substance" to "amount" may be used for brevity. This also applies to derived quantities such as "amount-of-substance concentration", which may simply be called "amount concentration". In the field of clinical chemistry, the name "amount-of-substance concentration" is generally abbreviated to "substance concentration".</t>
   </si>
   <si>
@@ -190,9 +187,6 @@
     <t>@amps@\ @secs@</t>
   </si>
   <si>
-    <t>Hyperfine cesium constant symbol</t>
-  </si>
-  <si>
     <t>hfcs</t>
   </si>
   <si>
@@ -205,9 +199,6 @@
     <t>ΔνCs</t>
   </si>
   <si>
-    <t>Meter unit symbol</t>
-  </si>
-  <si>
     <t>mtrs</t>
   </si>
   <si>
@@ -280,9 +271,6 @@
     <t>c = 299 792 458 m s^-1</t>
   </si>
   <si>
-    <t>Meter unit definition</t>
-  </si>
-  <si>
     <t>equation</t>
   </si>
   <si>
@@ -307,9 +295,6 @@
     <t>s</t>
   </si>
   <si>
-    <t>Hyperfine cesium constant value</t>
-  </si>
-  <si>
     <t>hfcv</t>
   </si>
   <si>
@@ -319,9 +304,6 @@
     <t>9\:192\:631\:770</t>
   </si>
   <si>
-    <t>Hyperfine cesium/speed of light value</t>
-  </si>
-  <si>
     <t>hslv</t>
   </si>
   <si>
@@ -424,9 +406,6 @@
     <t>@plks@ = @plkv@ @plku@</t>
   </si>
   <si>
-    <t>Per square meter second unit symbol</t>
-  </si>
-  <si>
     <t>smsu</t>
   </si>
   <si>
@@ -535,9 +514,6 @@
     <t>@hfcs@ = @hfcv@\ @hfcu@</t>
   </si>
   <si>
-    <t>Cesium 133 isotope symbol</t>
-  </si>
-  <si>
     <t>csis</t>
   </si>
   <si>
@@ -748,33 +724,21 @@
     <t>@fpws@ = @celo@\ @kels@</t>
   </si>
   <si>
-    <t>Celcius temperature quantity symbol</t>
-  </si>
-  <si>
     <t>cels</t>
   </si>
   <si>
     <t>t</t>
   </si>
   <si>
-    <t>Celcius temperature quantity definition</t>
-  </si>
-  <si>
     <t>celd</t>
   </si>
   <si>
     <t>@cels@ = @tmps@ - @fpws@</t>
   </si>
   <si>
-    <t>Celcius unit symbol</t>
-  </si>
-  <si>
     <t>ceus</t>
   </si>
   <si>
-    <t>Celcius to Kelvin definition</t>
-  </si>
-  <si>
     <t>c2kd</t>
   </si>
   <si>
@@ -787,9 +751,6 @@
     <t>T_{90}</t>
   </si>
   <si>
-    <t>ITS-90 Celcius symbol</t>
-  </si>
-  <si>
     <t>90cs</t>
   </si>
   <si>
@@ -874,9 +835,6 @@
     <t>mmed</t>
   </si>
   <si>
-    <t>Molar mass via avogadro constant definition</t>
-  </si>
-  <si>
     <t>mmav</t>
   </si>
   <si>
@@ -928,18 +886,12 @@
     <t>@morv@\ @hfcu@</t>
   </si>
   <si>
-    <t>Radition direction value/unit</t>
-  </si>
-  <si>
     <t>divu</t>
   </si>
   <si>
     <t>@radi@\ @wpss@</t>
   </si>
   <si>
-    <t>Hyperfine cesium constant unit</t>
-  </si>
-  <si>
     <t>hfcu</t>
   </si>
   <si>
@@ -949,9 +901,6 @@
     <t>eces</t>
   </si>
   <si>
-    <t>Celcius temperature quantity equation</t>
-  </si>
-  <si>
     <t>cele</t>
   </si>
   <si>
@@ -1066,18 +1015,12 @@
     <t>fpws</t>
   </si>
   <si>
-    <t>Inverse hyperfine cesium elementary charge value</t>
-  </si>
-  <si>
     <t>icev</t>
   </si>
   <si>
     <t>6.789\:687 \times 10^{8}</t>
   </si>
   <si>
-    <t>Kilogram meter squared second inv. squared per kelvin unit symbol</t>
-  </si>
-  <si>
     <t>kmss</t>
   </si>
   <si>
@@ -1096,9 +1039,6 @@
     <t>bolu</t>
   </si>
   <si>
-    <t>Boltzmann constant / (Planck constant *elemenary charge) value</t>
-  </si>
-  <si>
     <t>bpev</t>
   </si>
   <si>
@@ -1195,9 +1135,6 @@
     <t>hfcx</t>
   </si>
   <si>
-    <t>Hyperfine cesium constant exact relation</t>
-  </si>
-  <si>
     <t>Speed of light constant exact relation</t>
   </si>
   <si>
@@ -1309,9 +1246,6 @@
     <t>Steradian unit symbol</t>
   </si>
   <si>
-    <t>Candela steradian per kilogram inv. meter squared. second cubed unit symbol</t>
-  </si>
-  <si>
     <t>csks</t>
   </si>
   <si>
@@ -1327,9 +1261,6 @@
     <t>@jles@\ @kels@^{-1}</t>
   </si>
   <si>
-    <t>Kilogram, meter squared, inverse second squared, per kelvin unit symbol</t>
-  </si>
-  <si>
     <t>kgss</t>
   </si>
   <si>
@@ -1339,24 +1270,15 @@
     <t>@kgms@\ @mtrs@^{2}\ @secs@^{-1}</t>
   </si>
   <si>
-    <t>Kilogram, meter squared, inverse second unit symbol</t>
-  </si>
-  <si>
     <t>kmis</t>
   </si>
   <si>
-    <t>Meter horizontal plane distance value/unit</t>
-  </si>
-  <si>
     <t>mpvu</t>
   </si>
   <si>
     <t>1\,650\,763.73</t>
   </si>
   <si>
-    <t>Meter vacuum wavelengths value</t>
-  </si>
-  <si>
     <t>mvwv</t>
   </si>
   <si>
@@ -1420,27 +1342,15 @@
     <t>@cans@\ @strs@\ @wats@^{-1}</t>
   </si>
   <si>
-    <t>Celcius to Kelvin offset (French)</t>
-  </si>
-  <si>
     <t>273,16</t>
   </si>
   <si>
-    <t>Inverse Celcius to Kelvin offset (French)</t>
-  </si>
-  <si>
     <t>cefi</t>
   </si>
   <si>
-    <t>Inverse Celcius to Kelvin offset (English)</t>
-  </si>
-  <si>
     <t>1/@celo@</t>
   </si>
   <si>
-    <t>Celcius to Kelvin offset (English)</t>
-  </si>
-  <si>
     <t>celi</t>
   </si>
   <si>
@@ -1486,9 +1396,6 @@
     <t>mold</t>
   </si>
   <si>
-    <t>@circ@{C}</t>
-  </si>
-  <si>
     <t>1\;@kels@ = \left(\frac{@bolv@}{@bols@}\right)\ {@bolu@}</t>
   </si>
   <si>
@@ -1529,9 +1436,6 @@
   </si>
   <si>
     <t>This definition implies the exact relation @bolx@. Inverting this relation gives an exact expression for the kelvin in terms of the defining constants @bols@, @plks@ and @hfcs@: \[@tmpd@\] which is equal to \[@tmpa@\].</t>
-  </si>
-  <si>
-    <t>As a result of the way temperature scales used to be defined, it remains common practice to express a thermodynamic temperature, symbol @cels@, in terms of its difference from the reference temperature @fpwd@, close to the ice point. This difference is called the Celsius temperature, symbol @cels@ which is defined by the quantity equation \[@celd@\].</t>
   </si>
   <si>
     <t>The unit of Celsius temperature is the degree Celsius, symbol @ceus@, which is by definition equal in magnitude to the unit kelvin. A difference or interval of temperature may be expressed in kelvin or in degrees Celsius, the numerical value of the temperature difference being the same in either case. However, the numerical value of a Celsius temperature expressed in degrees Celsius is related to the numerical value of the thermodynamic temperature expressed in kelvin by the relation \[@c2kd@\] (see 5.4.1 for an explanation of the notation used here).</t>
@@ -1656,10 +1560,6 @@
   <si>
     <t>La précédente définition du kelvin établissait la température du point triple de l’eau @wtps@ comme étant exactement égale à @wtvu@. Étant donné que l’actuelle définition du kelvin
 fixe la valeur numérique de @bols@ et non plus celle de @wtps@, cette dernière doit désormais être déterminée de façon expérimentale. Au moment de l’adoption de l’actuelle définition du kelvin, @wtps@ était égale à @wtvu@ avec une incertitude-type relative de @wtpu@ déterminée à partir des mesures de @bols@ réalisées avant la redéfinition..</t>
-  </si>
-  <si>
-    <t>En raison de la manière dont les échelles de température étaient habituellement définies, il est resté d’usage courant d’exprimer la température thermodynamique, symbole @cels@, en fonction de sa différence par rapport à la température de référence @fpwd@ proche du point de congélation de l’eau. Cette différence de température est appelée température Celsius, symbole @cels@ ; elle est définie par l’équation aux grandeurs :
-\[@celd@\].</t>
   </si>
   <si>
     <t>L’unité de température Celsius est le degré Celsius, symbole @ceus@, qui par définition est égal en amplitude à l’unité « kelvin ». Une différence ou un intervalle de température peut s’exprimer aussi bien en kelvins qu’en degrés Celsius, la valeur numérique de la différence de température étant la même dans les deux cas. La valeur numérique de la température Celsius exprimée en degrés Celsius est liée à la valeur numérique de la température thermodynamique exprimée en kelvins par la relation :
@@ -2059,6 +1959,106 @@
   </si>
   <si>
     <t>\rm{T}</t>
+  </si>
+  <si>
+    <t>As a result of the way temperature scales used to be defined, it remains common practice to express a thermodynamic temperature, symbol @kels@, in terms of its difference from the reference temperature @fpwd@, close to the ice point. This difference is called the Celsius temperature, symbol @cels@ which is defined by the quantity equation \[@celd@\].</t>
+  </si>
+  <si>
+    <t>En raison de la manière dont les échelles de température étaient habituellement définies, il est resté d’usage courant d’exprimer la température thermodynamique, symbole @kels@, en fonction de sa différence par rapport à la température de référence @fpwd@ proche du point de congélation de l’eau. Cette différence de température est appelée température Celsius, symbole @cels@ ; elle est définie par l’équation aux grandeurs :
+\[@celd@\].</t>
+  </si>
+  <si>
+    <t>\rm{@circ@{C}}</t>
+  </si>
+  <si>
+    <t>ITS-90 Celsius symbol</t>
+  </si>
+  <si>
+    <t>Celsius to Kelvin definition</t>
+  </si>
+  <si>
+    <t>Inverse Celsius to Kelvin offset (French)</t>
+  </si>
+  <si>
+    <t>Celsius to Kelvin offset (French)</t>
+  </si>
+  <si>
+    <t>Celsius temperature quantity definition</t>
+  </si>
+  <si>
+    <t>Celsius temperature quantity equation</t>
+  </si>
+  <si>
+    <t>Inverse Celsius to Kelvin offset (English)</t>
+  </si>
+  <si>
+    <t>Celsius to Kelvin offset (English)</t>
+  </si>
+  <si>
+    <t>Celsius temperature quantity symbol</t>
+  </si>
+  <si>
+    <t>Celsius unit symbol</t>
+  </si>
+  <si>
+    <t>Boltzmann constant / (Planck constant *elementary charge) value</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium constant symbol</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium constant unit</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium constant value</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium constant exact relation</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium/speed of light value</t>
+  </si>
+  <si>
+    <t>Inverse hyperfine caesium elementary charge value</t>
+  </si>
+  <si>
+    <t>Candela steradian per kilogram inv. metre squared. second cubed unit symbol</t>
+  </si>
+  <si>
+    <t>Kilogram, metre squared, inverse second squared, per kelvin unit symbol</t>
+  </si>
+  <si>
+    <t>Kilogram, metre squared, inverse second unit symbol</t>
+  </si>
+  <si>
+    <t>Kilogram metre squared second inv. squared per kelvin unit symbol</t>
+  </si>
+  <si>
+    <t>Per square metre second unit symbol</t>
+  </si>
+  <si>
+    <t>Radiation direction value/unit</t>
+  </si>
+  <si>
+    <t>Caesium 133 isotope symbol</t>
+  </si>
+  <si>
+    <t>Metre horizontal plane distance value/unit</t>
+  </si>
+  <si>
+    <t>Metre unit definition</t>
+  </si>
+  <si>
+    <t>Metre unit symbol</t>
+  </si>
+  <si>
+    <t>Metre vacuum wavelengths value</t>
+  </si>
+  <si>
+    <t>Molar mass via Avogadro constant definition</t>
+  </si>
+  <si>
+    <t>Note that with the present definition, primary realizations of the kelvin can, in principle, be established at any point of the temperature scale.</t>
   </si>
 </sst>
 </file>
@@ -2599,48 +2599,48 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Akzent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Akzent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Akzent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Akzent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Akzent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Akzent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Ausgabe" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Berechnung" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Eingabe" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Ergebnis" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Erklärender Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Überschrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Überschrift 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Überschrift 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2656,7 +2656,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2953,21 +2953,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.875" customWidth="1"/>
+    <col min="3" max="3" width="6.875" customWidth="1"/>
     <col min="4" max="4" width="177" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -2979,46 +2979,46 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="2" spans="1:5" s="2" customFormat="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
       <c r="E2" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="4" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -3030,12 +3030,12 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C5" s="2">
         <v>4</v>
@@ -3047,80 +3047,80 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="6" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="7" spans="1:5" s="2" customFormat="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>508</v>
+        <v>476</v>
       </c>
       <c r="E7" s="4">
         <v>45104.336331018516</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="8" spans="1:5" s="2" customFormat="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="E8" s="4">
         <v>45104.365567129629</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="E9" s="4">
         <v>45105.140208333331</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="10" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
@@ -3132,29 +3132,29 @@
         <v>45105.154224537036</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="11" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C11" s="2">
         <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="4">
         <v>45105.16302083333</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="12" spans="1:5" s="2" customFormat="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C12" s="2">
         <v>5</v>
@@ -3166,12 +3166,12 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="13" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
@@ -3183,630 +3183,630 @@
         <v>45105.158726851849</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="14" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>493</v>
+        <v>462</v>
       </c>
       <c r="E14" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="15" spans="1:5" s="2" customFormat="1">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="E15" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="2" customFormat="1" ht="51">
+    <row r="16" spans="1:5" s="2" customFormat="1" ht="47.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>408</v>
+        <v>387</v>
       </c>
       <c r="E16" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="2" customFormat="1" ht="68">
+    <row r="17" spans="1:5" s="2" customFormat="1" ht="63">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C17" s="2">
         <v>4</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="E17" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="18" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>497</v>
+        <v>466</v>
       </c>
       <c r="E18" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="19" spans="1:5" s="2" customFormat="1">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="2" customFormat="1" ht="51">
+    <row r="20" spans="1:5" s="2" customFormat="1" ht="47.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="21" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C21" s="2">
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>498</v>
+        <v>640</v>
       </c>
       <c r="E21" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="2" customFormat="1" ht="51">
+    <row r="22" spans="1:5" s="2" customFormat="1" ht="47.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C22" s="2">
         <v>5</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>499</v>
+        <v>467</v>
       </c>
       <c r="E22" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="23" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C23" s="2">
         <v>6</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="E23" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="24" spans="1:5" s="2" customFormat="1">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C24" s="2">
         <v>7</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>10</v>
+        <v>672</v>
       </c>
       <c r="E24" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="25" spans="1:5" s="2" customFormat="1">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>505</v>
+        <v>473</v>
       </c>
       <c r="E25" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="26" spans="1:5" s="2" customFormat="1">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="E26" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="2" customFormat="1" ht="51">
+    <row r="27" spans="1:5" s="2" customFormat="1" ht="47.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="E27" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="28" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C28" s="2">
         <v>4</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="E28" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="29" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C29" s="2">
         <v>5</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
       <c r="E29" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="2" customFormat="1" ht="85">
+    <row r="30" spans="1:5" s="2" customFormat="1" ht="78.75">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C30" s="2">
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="31" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
       <c r="E31" s="4">
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="2" customFormat="1" ht="34">
+    <row r="32" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="E32" s="4">
         <v>44944.721134259256</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="33" spans="1:5" s="2" customFormat="1">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33" s="4">
         <v>44944.729699074072</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="34" spans="1:5" s="2" customFormat="1">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" s="4">
         <v>44944.729988425926</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="35" spans="1:5" s="2" customFormat="1">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2">
         <v>2</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E35" s="4">
         <v>44944.728692129633</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="36" spans="1:5" s="2" customFormat="1">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E36" s="4">
         <v>44944.730671296296</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="37" spans="1:5" s="2" customFormat="1">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2">
         <v>2</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E37" s="4">
         <v>44944.731365740743</v>
       </c>
     </row>
-    <row r="38" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="38" spans="1:5" s="2" customFormat="1">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E38" s="4">
         <v>44944.731944444444</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="39" spans="1:5" s="2" customFormat="1">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2">
         <v>2</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E39" s="4">
         <v>44944.732581018521</v>
       </c>
     </row>
-    <row r="40" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="40" spans="1:5" s="2" customFormat="1">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2">
         <v>3</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E40" s="4">
         <v>44944.732546296298</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="41" spans="1:5" s="2" customFormat="1">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2">
         <v>2</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E41" s="4">
         <v>44944.729699074072</v>
       </c>
     </row>
-    <row r="42" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="42" spans="1:5" s="2" customFormat="1">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2">
         <v>3</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E42" s="4">
         <v>44944.729699074072</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="43" spans="1:5" s="2" customFormat="1">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E43" s="4">
         <v>44944.728715277779</v>
       </c>
     </row>
-    <row r="44" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="44" spans="1:5" s="2" customFormat="1">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2">
         <v>3</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E44" s="4">
         <v>44944.72865740741</v>
       </c>
     </row>
-    <row r="45" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="45" spans="1:5" s="2" customFormat="1">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C45" s="2">
         <v>4</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E45" s="4">
         <v>44944.728634259256</v>
       </c>
     </row>
-    <row r="46" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="46" spans="1:5" s="2" customFormat="1">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E46" s="4">
         <v>44944.732604166667</v>
       </c>
     </row>
-    <row r="47" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="47" spans="1:5" s="2" customFormat="1">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2">
         <v>4</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>587</v>
+        <v>554</v>
       </c>
       <c r="E47" s="4">
         <v>44944.732523148145</v>
       </c>
     </row>
-    <row r="48" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="48" spans="1:5" s="2" customFormat="1">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>588</v>
+        <v>555</v>
       </c>
       <c r="E48" s="4">
         <v>44944.731400462966</v>
       </c>
     </row>
-    <row r="49" spans="1:5" s="2" customFormat="1" ht="17" customHeight="1">
+    <row r="49" spans="1:5" s="2" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2">
         <v>3</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E49" s="4">
         <v>44944.73133101852</v>
       </c>
     </row>
-    <row r="50" spans="1:5" s="2" customFormat="1" ht="17">
+    <row r="50" spans="1:5" s="2" customFormat="1">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2">
         <v>2</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E50" s="4">
         <v>44978.666134259256</v>
@@ -3815,18 +3815,18 @@
     <row r="51" spans="1:5">
       <c r="B51" s="6"/>
     </row>
-    <row r="53" spans="1:5" ht="17">
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>50</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>556</v>
+        <v>523</v>
       </c>
       <c r="E53" s="8">
         <v>45126.62222222222</v>
@@ -3837,7 +3837,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>557</v>
+        <v>524</v>
       </c>
       <c r="D54" s="10"/>
     </row>
@@ -3846,30 +3846,30 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>561</v>
+        <v>528</v>
       </c>
       <c r="E55" s="8">
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="51">
+    <row r="56" spans="1:5" ht="47.25">
       <c r="A56" s="2">
         <v>53</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="C56" s="2">
         <v>2</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>560</v>
+        <v>527</v>
       </c>
       <c r="E56" s="4">
         <v>45126.62222222222</v>
@@ -3880,47 +3880,47 @@
         <v>54</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>562</v>
+        <v>529</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>563</v>
+        <v>530</v>
       </c>
       <c r="E57" s="4">
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="17">
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>55</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>565</v>
+        <v>532</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>564</v>
+        <v>531</v>
       </c>
       <c r="E58" s="4">
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="17">
+    <row r="59" spans="1:5">
       <c r="A59" s="2">
         <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>566</v>
+        <v>533</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>564</v>
+        <v>531</v>
       </c>
       <c r="E59" s="4">
         <v>45126.62222222222</v>
@@ -3931,13 +3931,13 @@
         <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>569</v>
+        <v>536</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="E60" s="4">
         <v>45126.62222222222</v>
@@ -3948,13 +3948,13 @@
         <v>58</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>569</v>
+        <v>536</v>
       </c>
       <c r="C61" s="2">
         <v>2</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E61" s="4">
         <v>45126.62222222222</v>
@@ -3965,13 +3965,13 @@
         <v>59</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="E62" s="4">
         <v>45126.62222222222</v>
@@ -3986,13 +3986,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C76578C5-08B3-574F-BA8C-FE251C939966}">
   <dimension ref="A1:E70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="6.875" customWidth="1"/>
     <col min="4" max="4" width="177" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1">
@@ -4009,704 +4009,704 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" ht="17">
+    <row r="2" spans="1:4" s="2" customFormat="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C3" s="2">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C5" s="2">
         <v>4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" ht="51">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="2" customFormat="1" ht="47.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="2" customFormat="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="2" customFormat="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C11" s="2">
         <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="2" customFormat="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C12" s="2">
         <v>5</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="2" customFormat="1" ht="51">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="2" customFormat="1" ht="47.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="2" customFormat="1">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="2" customFormat="1">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" ht="51">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="2" customFormat="1" ht="47.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" ht="68">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="2" customFormat="1" ht="63">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C17" s="2">
         <v>4</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="2" customFormat="1">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="2" customFormat="1">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" ht="51">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="2" customFormat="1" ht="47.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" ht="68">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="2" customFormat="1" ht="63">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C21" s="2">
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" ht="85">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="2" customFormat="1" ht="78.75">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C22" s="2">
         <v>5</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C23" s="2">
         <v>6</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="2" customFormat="1">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="C24" s="2">
         <v>7</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="2" customFormat="1">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="2" customFormat="1">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="2" customFormat="1" ht="51">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="2" customFormat="1" ht="47.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="2" customFormat="1" ht="85">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="2" customFormat="1" ht="78.75">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C28" s="2">
         <v>4</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C29" s="2">
         <v>5</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="2" customFormat="1" ht="85">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="2" customFormat="1" ht="78.75">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C30" s="2">
         <v>6</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="C31" s="2">
         <v>1</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" s="2" customFormat="1" ht="34">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="2" customFormat="1" ht="31.5">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" s="2" customFormat="1">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" s="2" customFormat="1">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" s="2" customFormat="1">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2">
         <v>2</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="2" customFormat="1">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" s="2" customFormat="1">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2">
         <v>2</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="2" customFormat="1">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" s="2" customFormat="1">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2">
         <v>2</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" s="2" customFormat="1">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2">
         <v>3</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" s="2" customFormat="1">
       <c r="A41" s="2">
         <v>51</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2">
         <v>2</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" s="2" customFormat="1">
       <c r="A42" s="2">
         <v>52</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2">
         <v>3</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" s="2" customFormat="1">
       <c r="A43" s="2">
         <v>53</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" s="2" customFormat="1">
       <c r="A44" s="2">
         <v>54</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2">
         <v>3</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" s="2" customFormat="1">
       <c r="A45" s="2">
         <v>55</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C45" s="2">
         <v>4</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" s="2" customFormat="1">
       <c r="A46" s="2">
         <v>56</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" s="2" customFormat="1">
       <c r="A47" s="2">
         <v>57</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2">
         <v>4</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" s="2" customFormat="1" ht="17">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" s="2" customFormat="1">
       <c r="A48" s="2">
         <v>58</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="2" customFormat="1" ht="17" customHeight="1">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="2" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A49" s="2">
         <v>59</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2">
         <v>3</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="2" customFormat="1" ht="34">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="2" customFormat="1" ht="31.5">
       <c r="A50" s="2">
         <v>70</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2">
         <v>2</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="17">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>50</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>590</v>
+        <v>557</v>
       </c>
       <c r="E53" s="8"/>
     </row>
@@ -4715,7 +4715,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>557</v>
+        <v>524</v>
       </c>
       <c r="D54" s="10"/>
     </row>
@@ -4724,28 +4724,28 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="E55" s="8"/>
     </row>
-    <row r="56" spans="1:5" ht="51">
+    <row r="56" spans="1:5" ht="47.25">
       <c r="A56" s="2">
         <v>53</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="C56" s="2">
         <v>2</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>591</v>
+        <v>558</v>
       </c>
       <c r="E56" s="4"/>
     </row>
@@ -4754,58 +4754,58 @@
         <v>54</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>562</v>
+        <v>529</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>593</v>
+        <v>560</v>
       </c>
       <c r="E57" s="4"/>
     </row>
-    <row r="58" spans="1:5" ht="17">
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>55</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>565</v>
+        <v>532</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="E58" s="4"/>
     </row>
-    <row r="59" spans="1:5" ht="17">
+    <row r="59" spans="1:5">
       <c r="A59" s="2">
         <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>566</v>
+        <v>533</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
       <c r="E59" s="4"/>
     </row>
-    <row r="60" spans="1:5" ht="17">
+    <row r="60" spans="1:5">
       <c r="A60" s="2">
         <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>569</v>
+        <v>536</v>
       </c>
       <c r="C60" s="2">
         <v>1</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>594</v>
+        <v>561</v>
       </c>
       <c r="E60" s="4"/>
     </row>
@@ -4814,13 +4814,13 @@
         <v>58</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>569</v>
+        <v>536</v>
       </c>
       <c r="C61" s="2">
         <v>2</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>595</v>
+        <v>562</v>
       </c>
       <c r="E61" s="4"/>
     </row>
@@ -4829,13 +4829,13 @@
         <v>59</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="C62" s="2">
         <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="E62" s="4"/>
     </row>
@@ -4865,14 +4865,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396D6CEF-66BA-914C-BC20-42B24F721DE4}">
   <dimension ref="A1:I156"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="29.6640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="36.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="29.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="29.625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="36.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.625" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="33" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4881,28 +4881,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="C1" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="D1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4910,16 +4910,16 @@
         <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>643</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4927,16 +4927,16 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4944,16 +4944,16 @@
         <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4961,16 +4961,16 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>599</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4978,16 +4978,16 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -4995,25 +4995,25 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>604</v>
+        <v>571</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -5021,25 +5021,25 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
         <v>47</v>
       </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -5047,16 +5047,16 @@
         <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5064,16 +5064,16 @@
         <v>139</v>
       </c>
       <c r="B10" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
+        <v>487</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5081,16 +5081,16 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
+        <v>488</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>489</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="D11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>521</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -5098,16 +5098,16 @@
         <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>605</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -5115,16 +5115,16 @@
         <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -5132,30 +5132,30 @@
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="B15" t="s">
-        <v>645</v>
+        <v>612</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>646</v>
+        <v>613</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>647</v>
+        <v>614</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -5163,16 +5163,16 @@
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5180,16 +5180,16 @@
         <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5197,16 +5197,16 @@
         <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -5214,16 +5214,16 @@
         <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -5231,16 +5231,16 @@
         <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>353</v>
+        <v>653</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -5248,16 +5248,16 @@
         <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>245</v>
+        <v>644</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -5265,16 +5265,16 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>504</v>
+        <v>472</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5282,16 +5282,16 @@
         <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5299,16 +5299,16 @@
         <v>97</v>
       </c>
       <c r="B24" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>606</v>
+        <v>573</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5316,16 +5316,16 @@
         <v>134</v>
       </c>
       <c r="B25" t="s">
-        <v>463</v>
+        <v>645</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>464</v>
+        <v>436</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5333,16 +5333,16 @@
         <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>461</v>
+        <v>646</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -5350,16 +5350,16 @@
         <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>240</v>
+        <v>647</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -5367,16 +5367,16 @@
         <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>304</v>
+        <v>648</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5384,16 +5384,16 @@
         <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>465</v>
+        <v>649</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5401,16 +5401,16 @@
         <v>113</v>
       </c>
       <c r="B30" t="s">
-        <v>467</v>
+        <v>650</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5418,16 +5418,16 @@
         <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>237</v>
+        <v>651</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5435,16 +5435,16 @@
         <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>652</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>483</v>
+        <v>642</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -5452,30 +5452,30 @@
         <v>137</v>
       </c>
       <c r="B33" t="s">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>474</v>
+        <v>444</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="B34" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>491</v>
+        <v>460</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -5483,25 +5483,25 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>607</v>
+        <v>574</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -5509,16 +5509,16 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>666</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E36" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>608</v>
+        <v>575</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -5526,16 +5526,16 @@
         <v>122</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>424</v>
+        <v>660</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -5543,16 +5543,16 @@
         <v>120</v>
       </c>
       <c r="B38" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E38" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -5560,16 +5560,16 @@
         <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>297</v>
+        <v>665</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E39" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -5577,16 +5577,16 @@
         <v>129</v>
       </c>
       <c r="B40" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="D40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E40" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>609</v>
+        <v>576</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -5594,16 +5594,16 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E41" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -5611,16 +5611,16 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E42" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -5628,16 +5628,16 @@
         <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="D43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E43" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>610</v>
+        <v>577</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -5645,16 +5645,16 @@
         <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="D44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E44" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5662,16 +5662,16 @@
         <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="D45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E45" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>494</v>
+        <v>463</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5679,25 +5679,25 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" t="s">
+        <v>374</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D46" t="s">
-        <v>39</v>
-      </c>
-      <c r="E46" t="s">
-        <v>395</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="I46" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5705,25 +5705,25 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E47" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5731,30 +5731,30 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E48" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>611</v>
+        <v>578</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="B49" t="s">
-        <v>649</v>
+        <v>616</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E49" t="s">
-        <v>650</v>
+        <v>617</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>651</v>
+        <v>618</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5762,16 +5762,16 @@
         <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E50" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5779,16 +5779,16 @@
         <v>107</v>
       </c>
       <c r="B51" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="D51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E51" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5796,16 +5796,16 @@
         <v>98</v>
       </c>
       <c r="B52" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="D52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E52" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5813,16 +5813,16 @@
         <v>93</v>
       </c>
       <c r="B53" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E53" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5830,30 +5830,30 @@
         <v>94</v>
       </c>
       <c r="B54" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="D54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E54" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="B55" t="s">
-        <v>652</v>
+        <v>619</v>
       </c>
       <c r="D55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E55" t="s">
-        <v>653</v>
+        <v>620</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>654</v>
+        <v>621</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5861,30 +5861,30 @@
         <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E56" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>612</v>
+        <v>579</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="B57" t="s">
-        <v>642</v>
+        <v>609</v>
       </c>
       <c r="D57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E57" t="s">
-        <v>643</v>
+        <v>610</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>613</v>
+        <v>580</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5892,25 +5892,25 @@
         <v>4</v>
       </c>
       <c r="B58" t="s">
+        <v>654</v>
+      </c>
+      <c r="D58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E58" t="s">
+        <v>50</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" t="s">
-        <v>39</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="G58" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5918,16 +5918,16 @@
         <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>300</v>
+        <v>655</v>
       </c>
       <c r="D59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E59" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>644</v>
+        <v>611</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5935,25 +5935,25 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>90</v>
+        <v>656</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5961,16 +5961,16 @@
         <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>386</v>
+        <v>657</v>
       </c>
       <c r="D61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E61" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5978,25 +5978,25 @@
         <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>658</v>
       </c>
       <c r="D62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E62" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -6004,16 +6004,16 @@
         <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>343</v>
+        <v>659</v>
       </c>
       <c r="D63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E63" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -6021,25 +6021,25 @@
         <v>21</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D64" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E64" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>614</v>
+        <v>581</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -6047,30 +6047,30 @@
         <v>123</v>
       </c>
       <c r="B65" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="D65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E65" t="s">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="B66" t="s">
-        <v>658</v>
+        <v>625</v>
       </c>
       <c r="D66" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E66" t="s">
-        <v>659</v>
+        <v>626</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -6078,19 +6078,19 @@
         <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E67" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F67" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -6098,25 +6098,25 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D68" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E68" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -6124,25 +6124,25 @@
         <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E69" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -6150,25 +6150,25 @@
         <v>16</v>
       </c>
       <c r="B70" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D70" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E70" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>616</v>
+        <v>583</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -6176,25 +6176,25 @@
         <v>26</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D71" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E71" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>511</v>
+        <v>479</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -6202,16 +6202,16 @@
         <v>124</v>
       </c>
       <c r="B72" t="s">
-        <v>430</v>
+        <v>661</v>
       </c>
       <c r="D72" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E72" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>432</v>
+        <v>409</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -6219,16 +6219,16 @@
         <v>104</v>
       </c>
       <c r="B73" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="D73" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E73" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>617</v>
+        <v>584</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -6236,16 +6236,16 @@
         <v>125</v>
       </c>
       <c r="B74" t="s">
-        <v>434</v>
+        <v>662</v>
       </c>
       <c r="D74" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E74" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -6253,16 +6253,16 @@
         <v>109</v>
       </c>
       <c r="B75" t="s">
-        <v>346</v>
+        <v>663</v>
       </c>
       <c r="D75" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E75" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>432</v>
+        <v>409</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -6270,25 +6270,25 @@
         <v>29</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E76" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -6296,30 +6296,30 @@
         <v>141</v>
       </c>
       <c r="B77" t="s">
-        <v>637</v>
+        <v>604</v>
       </c>
       <c r="D77" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E77" t="s">
-        <v>554</v>
+        <v>521</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>618</v>
+        <v>585</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="B78" t="s">
-        <v>638</v>
+        <v>605</v>
       </c>
       <c r="D78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E78" t="s">
-        <v>639</v>
+        <v>606</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6327,16 +6327,16 @@
         <v>119</v>
       </c>
       <c r="B79" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="D79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E79" t="s">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6344,30 +6344,30 @@
         <v>118</v>
       </c>
       <c r="B80" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="D80" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E80" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>619</v>
+        <v>586</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="B81" t="s">
-        <v>661</v>
+        <v>628</v>
       </c>
       <c r="D81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E81" t="s">
-        <v>662</v>
+        <v>629</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>663</v>
+        <v>630</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -6375,16 +6375,16 @@
         <v>74</v>
       </c>
       <c r="B82" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="D82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E82" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>620</v>
+        <v>587</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -6392,16 +6392,16 @@
         <v>75</v>
       </c>
       <c r="B83" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="D83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E83" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -6409,16 +6409,16 @@
         <v>81</v>
       </c>
       <c r="B84" t="s">
-        <v>279</v>
+        <v>671</v>
       </c>
       <c r="D84" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E84" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>589</v>
+        <v>556</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -6426,16 +6426,16 @@
         <v>71</v>
       </c>
       <c r="B85" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D85" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E85" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>621</v>
+        <v>588</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -6443,16 +6443,16 @@
         <v>73</v>
       </c>
       <c r="B86" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E86" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -6460,16 +6460,16 @@
         <v>72</v>
       </c>
       <c r="B87" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D87" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E87" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6477,16 +6477,16 @@
         <v>80</v>
       </c>
       <c r="B88" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="D88" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E88" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>597</v>
+        <v>564</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6494,16 +6494,16 @@
         <v>79</v>
       </c>
       <c r="B89" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D89" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E89" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>598</v>
+        <v>565</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6511,16 +6511,16 @@
         <v>69</v>
       </c>
       <c r="B90" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
       <c r="D90" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E90" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6528,16 +6528,16 @@
         <v>103</v>
       </c>
       <c r="B91" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="D91" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E91" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6545,16 +6545,16 @@
         <v>102</v>
       </c>
       <c r="B92" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="D92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E92" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>622</v>
+        <v>589</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6562,16 +6562,16 @@
         <v>83</v>
       </c>
       <c r="B93" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="D93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E93" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6579,16 +6579,16 @@
         <v>82</v>
       </c>
       <c r="B94" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="D94" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E94" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6596,16 +6596,16 @@
         <v>84</v>
       </c>
       <c r="B95" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="D95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E95" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6613,16 +6613,16 @@
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="D96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E96" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6630,16 +6630,16 @@
         <v>87</v>
       </c>
       <c r="B97" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="D97" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E97" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6647,16 +6647,16 @@
         <v>126</v>
       </c>
       <c r="B98" t="s">
-        <v>436</v>
+        <v>667</v>
       </c>
       <c r="D98" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E98" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>623</v>
+        <v>590</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6664,25 +6664,25 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
+        <v>668</v>
+      </c>
+      <c r="D99" t="s">
+        <v>78</v>
+      </c>
+      <c r="E99" t="s">
+        <v>79</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H99" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D99" t="s">
+      <c r="I99" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="E99" t="s">
-        <v>83</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6690,25 +6690,25 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>56</v>
+        <v>669</v>
       </c>
       <c r="D100" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E100" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>624</v>
+        <v>591</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6716,16 +6716,16 @@
         <v>127</v>
       </c>
       <c r="B101" t="s">
-        <v>439</v>
+        <v>670</v>
       </c>
       <c r="D101" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E101" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>438</v>
+        <v>413</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6733,16 +6733,16 @@
         <v>39</v>
       </c>
       <c r="B102" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D102" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E102" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>625</v>
+        <v>592</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6750,33 +6750,33 @@
         <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
       <c r="D103" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E103" t="s">
-        <v>515</v>
+        <v>483</v>
       </c>
       <c r="F103" t="s">
-        <v>516</v>
+        <v>484</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>516</v>
+        <v>484</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="B104" t="s">
-        <v>664</v>
+        <v>631</v>
       </c>
       <c r="D104" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E104" t="s">
-        <v>665</v>
+        <v>632</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>666</v>
+        <v>633</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6784,25 +6784,25 @@
         <v>22</v>
       </c>
       <c r="B105" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E105" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6810,25 +6810,25 @@
         <v>30</v>
       </c>
       <c r="B106" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D106" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E106" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6836,25 +6836,25 @@
         <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D107" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E107" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6862,25 +6862,25 @@
         <v>19</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E108" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6888,25 +6888,25 @@
         <v>18</v>
       </c>
       <c r="B109" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D109" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E109" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6914,25 +6914,25 @@
         <v>23</v>
       </c>
       <c r="B110" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="D110" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E110" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>512</v>
+        <v>480</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>513</v>
+        <v>481</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6940,16 +6940,16 @@
         <v>128</v>
       </c>
       <c r="B111" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="D111" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E111" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>626</v>
+        <v>593</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6957,16 +6957,16 @@
         <v>95</v>
       </c>
       <c r="B112" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="D112" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E112" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -6974,16 +6974,16 @@
         <v>101</v>
       </c>
       <c r="B113" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="D113" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E113" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -6991,16 +6991,16 @@
         <v>100</v>
       </c>
       <c r="B114" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="D114" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E114" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>640</v>
+        <v>607</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7008,16 +7008,16 @@
         <v>105</v>
       </c>
       <c r="B115" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="D115" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E115" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>627</v>
+        <v>594</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7025,16 +7025,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="D116" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E116" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>628</v>
+        <v>595</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7042,16 +7042,16 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="D117" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E117" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7059,25 +7059,25 @@
         <v>20</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D118" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E118" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7085,25 +7085,25 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D119" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E119" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>629</v>
+        <v>596</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7111,25 +7111,25 @@
         <v>24</v>
       </c>
       <c r="B120" t="s">
-        <v>129</v>
+        <v>664</v>
       </c>
       <c r="D120" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E120" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7137,44 +7137,44 @@
         <v>132</v>
       </c>
       <c r="B121" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="D121" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E121" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="B122" t="s">
-        <v>667</v>
+        <v>634</v>
       </c>
       <c r="D122" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E122" t="s">
-        <v>668</v>
+        <v>635</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>669</v>
+        <v>636</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="B123" t="s">
-        <v>655</v>
+        <v>622</v>
       </c>
       <c r="D123" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E123" t="s">
-        <v>656</v>
+        <v>623</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>657</v>
+        <v>624</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7182,25 +7182,25 @@
         <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D124" t="s">
+        <v>38</v>
+      </c>
+      <c r="E124" t="s">
         <v>39</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="G124" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G124" s="1" t="s">
+      <c r="H124" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H124" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="I124" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7208,25 +7208,25 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
+        <v>64</v>
+      </c>
+      <c r="D125" t="s">
+        <v>38</v>
+      </c>
+      <c r="E125" t="s">
+        <v>65</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="H125" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D125" t="s">
-        <v>39</v>
-      </c>
-      <c r="E125" t="s">
-        <v>68</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="I125" s="1" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7234,25 +7234,25 @@
         <v>6</v>
       </c>
       <c r="B126" t="s">
+        <v>56</v>
+      </c>
+      <c r="D126" t="s">
+        <v>38</v>
+      </c>
+      <c r="E126" t="s">
+        <v>57</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G126" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D126" t="s">
-        <v>39</v>
-      </c>
-      <c r="E126" t="s">
-        <v>60</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="H126" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7260,25 +7260,25 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="D127" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E127" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="F127" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I127" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7286,25 +7286,25 @@
         <v>27</v>
       </c>
       <c r="B128" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D128" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E128" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -7312,16 +7312,16 @@
         <v>121</v>
       </c>
       <c r="B129" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="D129" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E129" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>630</v>
+        <v>597</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -7329,16 +7329,16 @@
         <v>54</v>
       </c>
       <c r="B130" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D130" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E130" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -7346,16 +7346,16 @@
         <v>53</v>
       </c>
       <c r="B131" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D131" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E131" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>484</v>
+        <v>453</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -7363,30 +7363,30 @@
         <v>92</v>
       </c>
       <c r="B132" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="D132" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E132" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="B133" t="s">
-        <v>670</v>
+        <v>637</v>
       </c>
       <c r="D133" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E133" t="s">
-        <v>671</v>
+        <v>638</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>672</v>
+        <v>639</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7394,16 +7394,16 @@
         <v>77</v>
       </c>
       <c r="B134" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D134" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E134" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>631</v>
+        <v>598</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7411,16 +7411,16 @@
         <v>78</v>
       </c>
       <c r="B135" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="D135" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E135" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>632</v>
+        <v>599</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7428,16 +7428,16 @@
         <v>46</v>
       </c>
       <c r="B136" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D136" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E136" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7445,16 +7445,16 @@
         <v>43</v>
       </c>
       <c r="B137" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D137" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E137" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7462,16 +7462,16 @@
         <v>45</v>
       </c>
       <c r="B138" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D138" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E138" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7479,16 +7479,16 @@
         <v>42</v>
       </c>
       <c r="B139" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D139" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E139" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7496,16 +7496,16 @@
         <v>50</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D140" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E140" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7513,16 +7513,16 @@
         <v>49</v>
       </c>
       <c r="B141" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D141" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E141" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>495</v>
+        <v>464</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7530,16 +7530,16 @@
         <v>44</v>
       </c>
       <c r="B142" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D142" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E142" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G142" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7547,16 +7547,16 @@
         <v>41</v>
       </c>
       <c r="B143" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D143" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E143" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7564,16 +7564,16 @@
         <v>40</v>
       </c>
       <c r="B144" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D144" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E144" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -7581,16 +7581,16 @@
         <v>37</v>
       </c>
       <c r="B145" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D145" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E145" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -7598,16 +7598,16 @@
         <v>48</v>
       </c>
       <c r="B146" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D146" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E146" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -7615,16 +7615,16 @@
         <v>114</v>
       </c>
       <c r="B147" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="D147" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E147" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -7632,30 +7632,30 @@
         <v>47</v>
       </c>
       <c r="B148" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D148" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E148" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>492</v>
+        <v>461</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="B149" t="s">
-        <v>600</v>
+        <v>567</v>
       </c>
       <c r="D149" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E149" t="s">
-        <v>601</v>
+        <v>568</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>648</v>
+        <v>615</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -7663,16 +7663,16 @@
         <v>117</v>
       </c>
       <c r="B150" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="D150" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E150" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>633</v>
+        <v>600</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -7680,30 +7680,30 @@
         <v>96</v>
       </c>
       <c r="B151" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="D151" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E151" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>634</v>
+        <v>601</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="B152" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="D152" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E152" t="s">
+        <v>569</v>
+      </c>
+      <c r="G152" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -7711,16 +7711,16 @@
         <v>57</v>
       </c>
       <c r="B153" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E153" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>636</v>
+        <v>603</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -7728,16 +7728,16 @@
         <v>59</v>
       </c>
       <c r="B154" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D154" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E154" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -7745,16 +7745,16 @@
         <v>58</v>
       </c>
       <c r="B155" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D155" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E155" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -7762,16 +7762,16 @@
         <v>136</v>
       </c>
       <c r="B156" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="D156" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E156" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/CUQ/_docs/Notes.xlsx
+++ b/CUQ/_docs/Notes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gruber04\git_repos\BIPM\Semantic-SI\CUQ\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6E7C8C-F8F3-4836-B380-1BEE1E4BE94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5E0589-6050-4105-971C-A724E96B92BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-8310" windowWidth="38640" windowHeight="21390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1961,104 +1961,104 @@
     <t>\rm{T}</t>
   </si>
   <si>
-    <t>As a result of the way temperature scales used to be defined, it remains common practice to express a thermodynamic temperature, symbol @kels@, in terms of its difference from the reference temperature @fpwd@, close to the ice point. This difference is called the Celsius temperature, symbol @cels@ which is defined by the quantity equation \[@celd@\].</t>
-  </si>
-  <si>
-    <t>En raison de la manière dont les échelles de température étaient habituellement définies, il est resté d’usage courant d’exprimer la température thermodynamique, symbole @kels@, en fonction de sa différence par rapport à la température de référence @fpwd@ proche du point de congélation de l’eau. Cette différence de température est appelée température Celsius, symbole @cels@ ; elle est définie par l’équation aux grandeurs :
+    <t>\rm{@circ@{C}}</t>
+  </si>
+  <si>
+    <t>ITS-90 Celsius symbol</t>
+  </si>
+  <si>
+    <t>Celsius to Kelvin definition</t>
+  </si>
+  <si>
+    <t>Inverse Celsius to Kelvin offset (French)</t>
+  </si>
+  <si>
+    <t>Celsius to Kelvin offset (French)</t>
+  </si>
+  <si>
+    <t>Celsius temperature quantity definition</t>
+  </si>
+  <si>
+    <t>Celsius temperature quantity equation</t>
+  </si>
+  <si>
+    <t>Inverse Celsius to Kelvin offset (English)</t>
+  </si>
+  <si>
+    <t>Celsius to Kelvin offset (English)</t>
+  </si>
+  <si>
+    <t>Celsius temperature quantity symbol</t>
+  </si>
+  <si>
+    <t>Celsius unit symbol</t>
+  </si>
+  <si>
+    <t>Boltzmann constant / (Planck constant *elementary charge) value</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium constant symbol</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium constant unit</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium constant value</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium constant exact relation</t>
+  </si>
+  <si>
+    <t>Hyperfine caesium/speed of light value</t>
+  </si>
+  <si>
+    <t>Inverse hyperfine caesium elementary charge value</t>
+  </si>
+  <si>
+    <t>Candela steradian per kilogram inv. metre squared. second cubed unit symbol</t>
+  </si>
+  <si>
+    <t>Kilogram, metre squared, inverse second squared, per kelvin unit symbol</t>
+  </si>
+  <si>
+    <t>Kilogram, metre squared, inverse second unit symbol</t>
+  </si>
+  <si>
+    <t>Kilogram metre squared second inv. squared per kelvin unit symbol</t>
+  </si>
+  <si>
+    <t>Per square metre second unit symbol</t>
+  </si>
+  <si>
+    <t>Radiation direction value/unit</t>
+  </si>
+  <si>
+    <t>Caesium 133 isotope symbol</t>
+  </si>
+  <si>
+    <t>Metre horizontal plane distance value/unit</t>
+  </si>
+  <si>
+    <t>Metre unit definition</t>
+  </si>
+  <si>
+    <t>Metre unit symbol</t>
+  </si>
+  <si>
+    <t>Metre vacuum wavelengths value</t>
+  </si>
+  <si>
+    <t>Molar mass via Avogadro constant definition</t>
+  </si>
+  <si>
+    <t>Note that with the present definition, primary realizations of the kelvin can, in principle, be established at any point of the temperature scale.</t>
+  </si>
+  <si>
+    <t>As a result of the way temperature scales used to be defined, it remains common practice to express a thermodynamic temperature, symbol @tmps@, in terms of its difference from the reference temperature @fpwd@, close to the ice point. This difference is called the Celsius temperature, symbol @cels@ which is defined by the quantity equation \[@celd@\].</t>
+  </si>
+  <si>
+    <t>En raison de la manière dont les échelles de température étaient habituellement définies, il est resté d’usage courant d’exprimer la température thermodynamique, symbole @tmps@, en fonction de sa différence par rapport à la température de référence @fpwd@ proche du point de congélation de l’eau. Cette différence de température est appelée température Celsius, symbole @cels@ ; elle est définie par l’équation aux grandeurs :
 \[@celd@\].</t>
-  </si>
-  <si>
-    <t>\rm{@circ@{C}}</t>
-  </si>
-  <si>
-    <t>ITS-90 Celsius symbol</t>
-  </si>
-  <si>
-    <t>Celsius to Kelvin definition</t>
-  </si>
-  <si>
-    <t>Inverse Celsius to Kelvin offset (French)</t>
-  </si>
-  <si>
-    <t>Celsius to Kelvin offset (French)</t>
-  </si>
-  <si>
-    <t>Celsius temperature quantity definition</t>
-  </si>
-  <si>
-    <t>Celsius temperature quantity equation</t>
-  </si>
-  <si>
-    <t>Inverse Celsius to Kelvin offset (English)</t>
-  </si>
-  <si>
-    <t>Celsius to Kelvin offset (English)</t>
-  </si>
-  <si>
-    <t>Celsius temperature quantity symbol</t>
-  </si>
-  <si>
-    <t>Celsius unit symbol</t>
-  </si>
-  <si>
-    <t>Boltzmann constant / (Planck constant *elementary charge) value</t>
-  </si>
-  <si>
-    <t>Hyperfine caesium constant symbol</t>
-  </si>
-  <si>
-    <t>Hyperfine caesium constant unit</t>
-  </si>
-  <si>
-    <t>Hyperfine caesium constant value</t>
-  </si>
-  <si>
-    <t>Hyperfine caesium constant exact relation</t>
-  </si>
-  <si>
-    <t>Hyperfine caesium/speed of light value</t>
-  </si>
-  <si>
-    <t>Inverse hyperfine caesium elementary charge value</t>
-  </si>
-  <si>
-    <t>Candela steradian per kilogram inv. metre squared. second cubed unit symbol</t>
-  </si>
-  <si>
-    <t>Kilogram, metre squared, inverse second squared, per kelvin unit symbol</t>
-  </si>
-  <si>
-    <t>Kilogram, metre squared, inverse second unit symbol</t>
-  </si>
-  <si>
-    <t>Kilogram metre squared second inv. squared per kelvin unit symbol</t>
-  </si>
-  <si>
-    <t>Per square metre second unit symbol</t>
-  </si>
-  <si>
-    <t>Radiation direction value/unit</t>
-  </si>
-  <si>
-    <t>Caesium 133 isotope symbol</t>
-  </si>
-  <si>
-    <t>Metre horizontal plane distance value/unit</t>
-  </si>
-  <si>
-    <t>Metre unit definition</t>
-  </si>
-  <si>
-    <t>Metre unit symbol</t>
-  </si>
-  <si>
-    <t>Metre vacuum wavelengths value</t>
-  </si>
-  <si>
-    <t>Molar mass via Avogadro constant definition</t>
-  </si>
-  <si>
-    <t>Note that with the present definition, primary realizations of the kelvin can, in principle, be established at any point of the temperature scale.</t>
   </si>
 </sst>
 </file>
@@ -3313,7 +3313,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>640</v>
+        <v>671</v>
       </c>
       <c r="E21" s="4">
         <v>44978.666134259256</v>
@@ -3364,7 +3364,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E24" s="4">
         <v>44978.666134259256</v>
@@ -4286,7 +4286,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>641</v>
+        <v>672</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" ht="78.75">
@@ -4910,7 +4910,7 @@
         <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
@@ -5231,7 +5231,7 @@
         <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D20" t="s">
         <v>38</v>
@@ -5248,7 +5248,7 @@
         <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D21" t="s">
         <v>78</v>
@@ -5316,7 +5316,7 @@
         <v>134</v>
       </c>
       <c r="B25" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D25" t="s">
         <v>38</v>
@@ -5333,7 +5333,7 @@
         <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D26" t="s">
         <v>38</v>
@@ -5350,7 +5350,7 @@
         <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D27" t="s">
         <v>78</v>
@@ -5367,7 +5367,7 @@
         <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D28" t="s">
         <v>78</v>
@@ -5384,7 +5384,7 @@
         <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D29" t="s">
         <v>38</v>
@@ -5401,7 +5401,7 @@
         <v>113</v>
       </c>
       <c r="B30" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D30" t="s">
         <v>38</v>
@@ -5418,7 +5418,7 @@
         <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D31" t="s">
         <v>38</v>
@@ -5435,7 +5435,7 @@
         <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
@@ -5444,7 +5444,7 @@
         <v>233</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -5509,7 +5509,7 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D36" t="s">
         <v>38</v>
@@ -5526,7 +5526,7 @@
         <v>122</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D37" t="s">
         <v>38</v>
@@ -5560,7 +5560,7 @@
         <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D39" t="s">
         <v>38</v>
@@ -5892,7 +5892,7 @@
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D58" t="s">
         <v>38</v>
@@ -5918,7 +5918,7 @@
         <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D59" t="s">
         <v>38</v>
@@ -5935,7 +5935,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D60" t="s">
         <v>38</v>
@@ -5961,7 +5961,7 @@
         <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D61" t="s">
         <v>38</v>
@@ -5978,7 +5978,7 @@
         <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D62" t="s">
         <v>38</v>
@@ -6004,7 +6004,7 @@
         <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D63" t="s">
         <v>38</v>
@@ -6202,7 +6202,7 @@
         <v>124</v>
       </c>
       <c r="B72" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D72" t="s">
         <v>38</v>
@@ -6236,7 +6236,7 @@
         <v>125</v>
       </c>
       <c r="B74" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D74" t="s">
         <v>38</v>
@@ -6253,7 +6253,7 @@
         <v>109</v>
       </c>
       <c r="B75" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D75" t="s">
         <v>38</v>
@@ -6409,7 +6409,7 @@
         <v>81</v>
       </c>
       <c r="B84" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D84" t="s">
         <v>78</v>
@@ -6647,7 +6647,7 @@
         <v>126</v>
       </c>
       <c r="B98" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D98" t="s">
         <v>38</v>
@@ -6664,7 +6664,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D99" t="s">
         <v>78</v>
@@ -6690,7 +6690,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D100" t="s">
         <v>38</v>
@@ -6716,7 +6716,7 @@
         <v>127</v>
       </c>
       <c r="B101" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D101" t="s">
         <v>38</v>
@@ -7111,7 +7111,7 @@
         <v>24</v>
       </c>
       <c r="B120" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D120" t="s">
         <v>38</v>

--- a/CUQ/_docs/Notes.xlsx
+++ b/CUQ/_docs/Notes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gruber04\git_repos\BIPM\Semantic-SI\CUQ\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5E0589-6050-4105-971C-A724E96B92BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAF9511-BE2B-4822-A852-96CD9A0C43CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-8310" windowWidth="38640" windowHeight="21390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,9 +55,6 @@
     <t>The reference to an unperturbed atom is intended to make it clear that the definition of the SI second is based on an isolated caesium atom that is unperturbed by any external field, such as ambient black-body radiation.</t>
   </si>
   <si>
-    <t>The second, so defined, is the unit of proper time in the sense of the general theory of relativity. To allow the provision of a coordinated time scale, the signals of different primary clocks in different locations are combined, which have to be corrected for relativistic caesium frequency shifts (see section 2.3.6).</t>
-  </si>
-  <si>
     <t>The effect of this definition is to define the unit @pksi@ (the unit of both the physical quantities action and angular momentum). Together with the definitions of the second and the metre this leads to a definition of the unit of mass expressed in terms of the Planck constant @plks@.</t>
   </si>
   <si>
@@ -1438,12 +1435,6 @@
     <t>This definition implies the exact relation @bolx@. Inverting this relation gives an exact expression for the kelvin in terms of the defining constants @bols@, @plks@ and @hfcs@: \[@tmpd@\] which is equal to \[@tmpa@\].</t>
   </si>
   <si>
-    <t>The unit of Celsius temperature is the degree Celsius, symbol @ceus@, which is by definition equal in magnitude to the unit kelvin. A difference or interval of temperature may be expressed in kelvin or in degrees Celsius, the numerical value of the temperature difference being the same in either case. However, the numerical value of a Celsius temperature expressed in degrees Celsius is related to the numerical value of the thermodynamic temperature expressed in kelvin by the relation \[@c2kd@\] (see 5.4.1 for an explanation of the notation used here).</t>
-  </si>
-  <si>
-    <t>The kelvin and the degree Celsius are also units of the International Temperature Scale of 1990 (ITS-90) adopted by the CIPM in 1989 in Recommendation 5 (CI-1989, PV, &lt;strong&gt;57&lt;/strong&gt;, 115). Note that the ITS-90 defines two quantities @90ks@ and @90cs@ which are close approximations to the corresponding thermodynamic temperatures @tmps@ and @cels@.</t>
-  </si>
-  <si>
     <t>T_{0}</t>
   </si>
   <si>
@@ -1492,9 +1483,6 @@
     <t>\Omega</t>
   </si>
   <si>
-    <t>Cette définition implique la relation exacte @hfcx@. En inversant cette relation, la seconde est exprimée en fonction de la constante @hfcs@: \[@secd@\]</t>
-  </si>
-  <si>
     <t>arcminute</t>
   </si>
   <si>
@@ -1513,21 +1501,12 @@
     <t>Il est fait référence à un atome non perturbé afin d’indiquer clairement que la définition de la seconde du SI se fonde sur un atome de césium isolé qui n’est pas perturbé par un champ externe quel qu’il soit, tel que la radiation d’un corps noir à température ambiante.</t>
   </si>
   <si>
-    <t>La seconde ainsi définie est l’unité de temps propre, au sens de la théorie générale de la relativité. Pour établir une échelle de temps coordonné, les signaux de différentes horloges primaires dans le monde sont combinés, puis des corrections sont appliquées pour tenir compte du décalage relativiste de fréquence entre les étalons à césium (voir section 2.3.6).</t>
-  </si>
-  <si>
     <t>Le CIPM a adopté différentes représentations secondaires de la seconde fondées sur un nombre choisi de raies spectrales d’atomes, ions ou molécules. Les fréquences non perturbées de ces raies peuvent être déterminées avec une incertitude relative qui n’est pas inférieure à celle de la réalisation de la seconde fondée sur la transition hyperfine de l’atome de @csis@ mais certaines peuvent être reproduites avec une meilleure stabilité.</t>
   </si>
   <si>
-    <t>Cette définition implique la relation exacte @solx@. En inversant cette relation, le mètre est exprimé en fonction des constantes @sols@ et @hfcs@: \[@mtrd@\]</t>
-  </si>
-  <si>
     <t>Il résulte de cette définition que le mètre est la longueur du trajet parcouru dans le vide par la lumière pendant une durée de @soli@ de seconde.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette définition implique la relation exacte @plkx@. En inversant cette relation, le kilogramme est exprimé en fonction des trois constantes @plks@, @hfcs@ et @sols@: \[@kgmd@\] relation identique à \[@kgod@\]. </t>
-  </si>
-  <si>
     <t>Cette définition permet de définir l’unité @pksi@ (l’unité des grandeurs physiques « action » et « moment cinétique »). Ainsi associée aux définitions de la seconde et du mètre, l’unité de masse est exprimée en fonction de la constante de Planck @plks@.</t>
   </si>
   <si>
@@ -1540,9 +1519,6 @@
     <t>La précédente définition du kilogramme fixait la valeur de la masse du prototype international du kilogramme, @kgmp@, à exactement un kilogramme ; la valeur de la constante de Planck @plks@ devait donc être déterminée de façon expérimentale. L’actuelle définition du kilogrammme fixe la valeur numérique de @plks@ de façon exacte et la masse du prototype doit désormais être déterminée de façon expérimentale.</t>
   </si>
   <si>
-    <t>Cette définition implique la relation exacte @elmd@. En inversant cette relation, l’ampère est exprimé en fonction des constante @elms@ et @hfcs@: \[@ampd@\] relation identique à  \[@ampa@\].</t>
-  </si>
-  <si>
     <t>Il résulte de cette définition qu’un ampère est le courant électrique correspondant au flux de @elmi@ charges élémentaires par seconde.</t>
   </si>
   <si>
@@ -1550,9 +1526,6 @@
   </si>
   <si>
     <t>Ainsi, comme la permittivité diélectrique du vide @veps@ (également connue sous le nom de constante électrique), l’impédance du vide caractéristique @vcis@ et l’admittance du vide @vads@ sont égales à @vepd@, @vcid@, et @vadd@ respectivement, les valeurs de @veps@, @vcis@ et @vads@ doivent désormais être déterminées de façon expérimentale et ont la même incertitude-type relative que @vmps@ puisque la valeur de @elms@ est connue avec exactitude. Le produit @vemp@ et le quotient @vcmq@ restent exacts. Au moment de l’adoption de l’actuelle définition de l’ampère, @vmps@ était égale à @vmvu@ avec une incertitude-type relative de @vmpu@.</t>
-  </si>
-  <si>
-    <t>Cette définition implique la relation exacte @bolx@. En inversant cette relation, le kelvin est exprimé en fonction des constantes @bols@, @plks@ et @hfcs@: \[@tmpd@\] relation identique à \[@tmpa@\].</t>
   </si>
   <si>
     <t>Il résulte de cette définition qu’un kelvin est égal au changement de la température thermodynamique résultant d’un changement de l’énergie thermique @ebts@ de @ebtv@.</t>
@@ -1562,42 +1535,18 @@
 fixe la valeur numérique de @bols@ et non plus celle de @wtps@, cette dernière doit désormais être déterminée de façon expérimentale. Au moment de l’adoption de l’actuelle définition du kelvin, @wtps@ était égale à @wtvu@ avec une incertitude-type relative de @wtpu@ déterminée à partir des mesures de @bols@ réalisées avant la redéfinition..</t>
   </si>
   <si>
-    <t>L’unité de température Celsius est le degré Celsius, symbole @ceus@, qui par définition est égal en amplitude à l’unité « kelvin ». Une différence ou un intervalle de température peut s’exprimer aussi bien en kelvins qu’en degrés Celsius, la valeur numérique de la différence de température étant la même dans les deux cas. La valeur numérique de la température Celsius exprimée en degrés Celsius est liée à la valeur numérique de la température thermodynamique exprimée en kelvins par la relation :
-\[@c2kd@\]
-(voir section 5.4.1 pour une explication de la notation utilisée ici).</t>
-  </si>
-  <si>
-    <t>Le kelvin et le degré Celsius sont aussi les unités de l’Échelle internationale de température de 1990 (EIT-90) adoptée par le CIPM en 1989 dans sa Recommandation 5 (CI-1989, PV,  &lt;strong&gt;57&lt;/strong&gt;, 26). Il est à noter que l’EIT-90 définit les deux grandeurs @90ks@ et @90cs@ qui sont de très bonnes approximations des températures thermodynamiques correspondantes @tmps@ et @cels@.</t>
-  </si>
-  <si>
     <t>Il est également à noter que l’actuelle définition de l’unité de température thermodynamique permet d’établir, en principe, des réalisations primaires du kelvin à tout point de l’échelle de température.</t>
   </si>
   <si>
-    <t>Cette définition implique la relation exacte  @avox@. En inversant cette relation, on obtient l’expression exacte de la mole en fonction de la constante @avos@: \[@mold@\].</t>
-  </si>
-  <si>
     <t>Il résulte de cette définition que la mole est la quantité de matière d’un système qui contient @avov@ entités élémentaires spécifiées.</t>
   </si>
   <si>
     <t>La précédente définition de la mole fixait la valeur de la masse molaire du carbone 12, @mmcs@), comme étant exactement égale à @mmcv@. Selon l’actuelle définition de la mole, @mmcs@ n’est plus connue avec exactitude et doit être déterminée de façon expérimentale. La valeur choisie pour @avos@ est telle qu’au moment de l’adoption de la présente définition de la mole, @mmcs@ était égale à @mmcv@ avec une incertitude-type relative de @mmcu@.</t>
   </si>
   <si>
-    <t>La masse molaire d’un atome ou d’une molécule X peut toujours être obtenue à partir de sa masse atomique relative à l’aide de l’équation : \[@mmxd@\]  et la masse molaire d’un atome ou d’une molécule X est également reliée à la masse d’une entité élémentaire m(X) par la relation : @eces@ by the relation \[@mmed@\].
-The molar mass of any atom or molecule X may still be obtained from its relative atomic mass from the equation \[@mmxd@\] and the molar mass of any atom or molecule X is also related to the mass of the elementary entity @eces@ by the relation \[@mmed@\].</t>
-  </si>
-  <si>
-    <t>Dans ces équations, @mcos@ est la constante de masse molaire, égale à @mcov@ et @uams@ est la constante de masse atomique unifiée, égale à @uamv@. Elles sont liées à la constante d’Avogadro par la relation : [@mmav@\].</t>
-  </si>
-  <si>
     <t>Dans le terme « quantité de matière », le mot « matière » sera généralement remplacé par d’autres mots précisant la matière en question pour chaque application particulière ; on pourrait par exemple parler de « quantité de chlorure d’hydrogène » ou de « quantité de benzène ». Il est important de définir précisément l’entité en question (comme le souligne la définition de la mole), de préférence en précisant la formule chimique moléculaire du matériau concerné. Bien que le mot « quantité » ait une définition plus générale dans le dictionnaire, cette abréviation du nom complet « quantité de matière » est parfois utilisée par souci de concision. Ceci s’applique aussi aux grandeurs dérivées telles que la concentration de quantité de matière, qui peut simplement être appelée « concentration de quantité ». Dans le domaine de la chimie clinique, le nom « concentration de quantité de matière » est généralement abrégé en « concentration de matière ».</t>
   </si>
   <si>
-    <t>Cette définition implique la relation exacte @morr@ pour le rayonnement monochromatique de fréquence @morf@. En inversant cette relation, la candela est exprimée en fonction des constantes @mors@, @plks@ et @hfcs@: \[@cand@\] relation identique à  \[@cana@\].</t>
-  </si>
-  <si>
-    <t>Il résulte de cette définition que la candela est l’intensité lumineuse, dans une direction donnée, d’une source qui émet un rayonnement monochromatique de fréquence @movu@ et dont l’intensité énergétique dans cette direction est @divu@. La définition du stéradian est donnée au bas du tableau 4.</t>
-  </si>
-  <si>
     <t>^{\prime}</t>
   </si>
   <si>
@@ -1622,9 +1571,6 @@
     <t>kelvin1967</t>
   </si>
   <si>
-    <t>In addition to the thermodynamic temperature (symbol $T$), expressed in kelvins, use is also made of Celsius temperature (symbol $t$) defined by the equation where \rm{T}_0 = 273,15 K by definition. To express celsius temperature, the unit «degree Celsius» which is equal to the unit «kelvin» is used; in this case, «degree Celsius» is a special name used in place of« kelvin». An interval or difference of Celsius temperature can however, be expressed in kelvin as well as in degrees Celsius.</t>
-  </si>
-  <si>
     <t>The 13th CGPM (1967, Resolution 3) also decided that the unit kelvin and its symbol $K$ should be used to express an interval or a difference of temperature.</t>
   </si>
   <si>
@@ -1691,9 +1637,6 @@
     <t>Il est particulièrement important de distinguer les fréquences des fréquences angulaires car leurs valeurs numériques diffèrent par définition d’un facteur1 de 2π.</t>
   </si>
   <si>
-    <t xml:space="preserve">La charge élémentaire, e, correspond à une constante de couplage de la force électromagnétique via la constante de structure fine @fscd@, où @veps@ est la permittivité diélectrique du vide (également connue sous le nom de constante électrique). </t>
-  </si>
-  <si>
     <t>La valeur numérique de la température Celsius exprimée en degrés Celsius est liée à la valeur numérique de la température thermodynamique exprimée en kelvins par la relation \n@cele@.</t>
   </si>
   <si>
@@ -1712,25 +1655,10 @@
     <t>@mcos@ = @avos@\,@uams@</t>
   </si>
   <si>
-    <t>L’expression « unité MKS de force » qui figure dans le texte original de 1946 a été remplacée ici par « newton », nom adopté pour cette unité par la 9e CGPM (1948, Résolution 7).</t>
-  </si>
-  <si>
-    <t>En dehors de la température thermodynamique (symbole $T$), exprimée en kelvins, on utilise aussi la température Célsius (symbole $t$) définie par l'équation où \rm{T}_0 = 273,15 K par définition. Pour exprimer la température, on utilise l'unité "degré Célsius" qui est égale à l'unitié "kelvin"; "degré Célsius" est un nom spécial employé dans ce cas au lieu de "kelvin". Un intervalle ou une différence de température Célsius peuvent toutefois s'exprimer aussi bien en kelvins qu'en degrés Célsius.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L'ancien prototype international du metre, qui fut sanctionne par la 1re CGPM en 1889, est toujours conserve au Bureau International des Poids et Mesures dans les conditions fixees en 1889. </t>
-  </si>
-  <si>
     <t>Ce prototype international en platine iridié est conservé au Bureau International dans des conditions qui ont été fixées par la CGPM en 1889.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dans la defmition de la mole, ii est entendu que !'on se refere ades atomes de carbone 12 non lies, au repos et dans leur etat fondamental. </t>
-  </si>
-  <si>
     <t>Cette définition précise en même temps la nature de la grandeur dont la mole est l'unité.</t>
-  </si>
-  <si>
-    <t>La 13ème CGPM (1967 Résolution 3) décida aussi que l'unité kelvin et son symbole K sont utilisés pour exprimer un intervalle ou une différence de température.</t>
   </si>
   <si>
     <t>@emms@ = @avos@\,@eces@ = @avos@\,@rams@\,@uams@</t>
@@ -2059,13 +1987,167 @@
   <si>
     <t>En raison de la manière dont les échelles de température étaient habituellement définies, il est resté d’usage courant d’exprimer la température thermodynamique, symbole @tmps@, en fonction de sa différence par rapport à la température de référence @fpwd@ proche du point de congélation de l’eau. Cette différence de température est appelée température Celsius, symbole @cels@ ; elle est définie par l’équation aux grandeurs :
 \[@celd@\].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans la définition de la mole, il est entendu que l'on se réfère à des atomes de carbone 12 non liés, au repos et dans leur état fondamental. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La charge élémentaire, @elms@, correspond à une constante de couplage de la force électromagnétique via la constante de structure fine @fscd@, où @veps@ est la permittivité diélectrique du vide (également connue sous le nom de constante électrique). </t>
+  </si>
+  <si>
+    <t>The second, so defined, is the unit of proper time in the sense of the general theory of relativity. To allow the provision of a coordinated time scale, the signals of different primary clocks in different locations are combined, which have to be corrected for relativistic caesium frequency shifts.</t>
+  </si>
+  <si>
+    <t>The unit of Celsius temperature is the degree Celsius, symbol @ceus@, which is by definition equal in magnitude to the unit kelvin. A difference or interval of temperature may be expressed in kelvin or in degrees Celsius, the numerical value of the temperature difference being the same in either case. However, the numerical value of a Celsius temperature expressed in degrees Celsius is related to the numerical value of the thermodynamic temperature expressed in kelvin by the relation \[@c2kd@\].</t>
+  </si>
+  <si>
+    <t>L’unité de température Celsius est le degré Celsius, symbole @ceus@, qui par définition est égal en amplitude à l’unité « kelvin ». Une différence ou un intervalle de température peut s’exprimer aussi bien en kelvins qu’en degrés Celsius, la valeur numérique de la différence de température étant la même dans les deux cas. La valeur numérique de la température Celsius exprimée en degrés Celsius est liée à la valeur numérique de la température thermodynamique exprimée en kelvins par la relation :
+\[@c2kd@\].</t>
+  </si>
+  <si>
+    <t>La masse molaire d’un atome ou d’une molécule X peut toujours être obtenue à partir de sa masse atomique relative à l’aide de l’équation : \[@mmxd@\]  et la masse molaire d’un atome ou d’une molécule X est également reliée à la masse d’une entité élémentaire m(X) par la relation : @eces@ by the relation \[@mmed@\].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il résulte de cette définition que la candela est l’intensité lumineuse, dans une direction donnée, d’une source qui émet un rayonnement monochromatique de fréquence @movu@ et dont l’intensité énergétique dans cette direction est @divu@. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The kelvin and the degree Celsius are also units of the International Temperature Scale of 1990 (ITS-90) adopted by the CIPM in 1989 in Recommendation 5 (CI-1989, PV, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>57</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 115). Note that the ITS-90 defines two quantities @90ks@ and @90cs@ which are close approximations to the corresponding thermodynamic temperatures @tmps@ and @cels@.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>In addition to the thermodynamic temperature (symbol $T$), expressed in kelvins, use is also made of Celsius temperature (symbol $t$) defined by the equation where</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @fpws@ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= 273,15 K by definition. To express celsius temperature, the unit "degree Celsius" which is equal to the unit "kelvin" is used; in this case, "degree Celsius" is a special name used in place of "kelvin". An interval or difference of Celsius temperature can however, be expressed in kelvin as well as in degrees Celsius.</t>
+    </r>
+  </si>
+  <si>
+    <t>La seconde ainsi définie est l’unité de temps propre, au sens de la théorie générale de la relativité. Pour établir une échelle de temps coordonné, les signaux de différentes horloges primaires dans le monde sont combinés, puis des corrections sont appliquées pour tenir compte du décalage relativiste de fréquence entre les étalons à césium.</t>
+  </si>
+  <si>
+    <t>La 13ᵉ CGPM (1967 Résolution 3) décida aussi que l'unité kelvin et son symbole K sont utilisés pour exprimer un intervalle ou une différence de température.</t>
+  </si>
+  <si>
+    <t>L’expression « unité MKS de force » qui figure dans le texte original de 1946 a été remplacée ici par « newton », nom adopté pour cette unité par la 9ᵉ CGPM (1948, Résolution 7).</t>
+  </si>
+  <si>
+    <t>Cette définition implique la relation exacte @hfcx@. En inversant cette relation, la seconde est exprimée en fonction de la constante @hfcs@ : \[@secd@\]</t>
+  </si>
+  <si>
+    <t>Cette définition implique la relation exacte @solx@. En inversant cette relation, le mètre est exprimé en fonction des constantes @sols@ et @hfcs@ : \[@mtrd@\]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette définition implique la relation exacte @plkx@. En inversant cette relation, le kilogramme est exprimé en fonction des trois constantes @plks@, @hfcs@ et @sols@ : \[@kgmd@\] relation identique à \[@kgod@\]. </t>
+  </si>
+  <si>
+    <t>Cette définition implique la relation exacte @elmd@. En inversant cette relation, l’ampère est exprimé en fonction des constante @elms@ et @hfcs@ : \[@ampd@\] relation identique à  \[@ampa@\].</t>
+  </si>
+  <si>
+    <t>Cette définition implique la relation exacte @bolx@. En inversant cette relation, le kelvin est exprimé en fonction des constantes @bols@, @plks@ et @hfcs@ : \[@tmpd@\] relation identique à \[@tmpa@\].</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Le kelvin et le degré Celsius sont aussi les unités de l’Échelle internationale de température de 1990 (EIT-90) adoptée par le CIPM en 1989 dans sa Recommandation 5 (CI-1989, PV, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>57</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 26). Il est à noter que l’EIT-90 définit les deux grandeurs @90ks@ et @90cs@ qui sont de très bonnes approximations des températures thermodynamiques correspondantes @tmps@ et @cels@.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cette définition implique la relation exacte  @avox@. En inversant cette relation, on obtient l’expression exacte de la mole en fonction de la constante @avos@ : \[@mold@\].</t>
+  </si>
+  <si>
+    <t>Dans ces équations, @mcos@ est la constante de masse molaire, égale à @mcov@ et @uams@ est la constante de masse atomique unifiée, égale à @uamv@. Elles sont liées à la constante d’Avogadro par la relation : \[@mmav@\].</t>
+  </si>
+  <si>
+    <t>Cette définition implique la relation exacte @morr@ pour le rayonnement monochromatique de fréquence @morf@. En inversant cette relation, la candela est exprimée en fonction des constantes @mors@, @plks@ et @hfcs@ : \[@cand@\] relation identique à  \[@cana@\].</t>
+  </si>
+  <si>
+    <r>
+      <t>En dehors de la température thermodynamique (symbole $T$), exprimée en kelvins, on utilise aussi la température Célsius (symbole $t$) définie par l'équation où</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> @fpws@ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= 273,15 K par définition. Pour exprimer la température, on utilise l'unité « degré Célsius » qui est égale à l'unitié « kelvin » ; « degré Célsius » est un nom spécial employé dans ce cas au lieu de « kelvin ». Un intervalle ou une différence de température Célsius peuvent toutefois s'exprimer aussi bien en kelvins qu'en degrés Célsius.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ancien prototype international du metre, qui fut sanctionné par la 1ʳᵉ CGPM en 1889, est toujours conservé au Bureau International des Poids et Mesures dans les conditions fixées en 1889. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2208,20 +2290,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="TimesNewRomanPSMT"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Times"/>
+    </font>
+    <font>
       <sz val="8"/>
-      <color rgb="FF4F4F4F"/>
       <name val="Helvetica"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF3A3A3A"/>
-      <name val="Times"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2571,32 +2663,33 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2644,6 +2737,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF00FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2955,1025 +3053,1026 @@
   <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="5.5" customWidth="1"/>
-    <col min="2" max="2" width="16.875" customWidth="1"/>
-    <col min="3" max="3" width="6.875" customWidth="1"/>
-    <col min="4" max="4" width="177" customWidth="1"/>
-    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="6.875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="177" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.875" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" s="3" customFormat="1">
+      <c r="A1" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="3" customFormat="1">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="E2" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="E5" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="3" customFormat="1">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="E7" s="6">
+        <v>45104.336331018516</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="3" customFormat="1">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="E8" s="6">
+        <v>45104.365567129629</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="E9" s="6">
+        <v>45105.140208333331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="6">
+        <v>45105.154224537036</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="6">
+        <v>45105.16302083333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="3" customFormat="1">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="6">
+        <v>45105.158726851849</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="E14" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="3" customFormat="1">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E15" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="3" customFormat="1" ht="47.25">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E16" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="3" customFormat="1" ht="63">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="E17" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="E18" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="3" customFormat="1">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="3" customFormat="1" ht="47.25">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="3">
+        <v>4</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="E21" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="3" customFormat="1" ht="47.25">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" s="3">
+        <v>5</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="E22" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="3">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="E23" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="3" customFormat="1">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" s="3">
+        <v>7</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="E24" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="3" customFormat="1">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="E25" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="3" customFormat="1">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E26" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="3" customFormat="1" ht="47.25">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C27" s="3">
+        <v>3</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="E27" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C28" s="3">
+        <v>4</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="E28" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29" s="3">
+        <v>5</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="E29" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="3" customFormat="1" ht="78.75">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C30" s="3">
+        <v>6</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="E31" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="E32" s="6">
+        <v>44944.721134259256</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="3" customFormat="1">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="6">
+        <v>44944.729699074072</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="3" customFormat="1">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="6">
+        <v>44944.729988425926</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="3" customFormat="1">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="6">
+        <v>44944.728692129633</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="3" customFormat="1">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="6">
+        <v>44944.730671296296</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="3" customFormat="1">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="6">
+        <v>44944.731365740743</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="3" customFormat="1">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="6">
+        <v>44944.731944444444</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="3" customFormat="1">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="6">
+        <v>44944.732581018521</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="3" customFormat="1">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="6">
+        <v>44944.732546296298</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="3" customFormat="1">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C41" s="3">
+        <v>2</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="6">
+        <v>44944.729699074072</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="3" customFormat="1">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="6">
+        <v>44944.729699074072</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="3" customFormat="1">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="6">
+        <v>44944.728715277779</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" s="3" customFormat="1">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C44" s="3">
+        <v>3</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="6">
+        <v>44944.72865740741</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="3" customFormat="1">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C45" s="3">
+        <v>4</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="6">
+        <v>44944.728634259256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="3" customFormat="1">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="6">
+        <v>44944.732604166667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="3" customFormat="1">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C47" s="3">
+        <v>4</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="E47" s="6">
+        <v>44944.732523148145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="3" customFormat="1">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="E48" s="6">
+        <v>44944.731400462966</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="3" customFormat="1" ht="17.100000000000001" customHeight="1">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C49" s="3">
+        <v>3</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="6">
+        <v>44944.73133101852</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="3" customFormat="1">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C50" s="3">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1">
-      <c r="A2" s="2">
+      <c r="D50" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="6">
+        <v>44978.666134259256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="B51" s="7"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C53" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="D53" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="E53" s="9">
+        <v>45126.62222222222</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D54" s="10"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="C55" s="8">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="E2" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A3" s="2">
+      <c r="D55" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="E55" s="9">
+        <v>45126.62222222222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="47.25">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C56" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="D56" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="E56" s="6">
+        <v>45126.62222222222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E57" s="6">
+        <v>45126.62222222222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="E58" s="6">
+        <v>45126.62222222222</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="E59" s="6">
+        <v>45126.62222222222</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E60" s="6">
+        <v>45126.62222222222</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C61" s="3">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C4" s="2">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C5" s="2">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="2" customFormat="1">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="D61" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="E61" s="6">
+        <v>45126.62222222222</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C62" s="3">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="E7" s="4">
-        <v>45104.336331018516</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="2" customFormat="1">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="E8" s="4">
-        <v>45104.365567129629</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="E9" s="4">
-        <v>45105.140208333331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="4">
-        <v>45105.154224537036</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C11" s="2">
-        <v>4</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="4">
-        <v>45105.16302083333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="2" customFormat="1">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C12" s="2">
-        <v>5</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="4">
-        <v>45105.158726851849</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="E14" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="2" customFormat="1">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C15" s="2">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="E15" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" s="2" customFormat="1" ht="47.25">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E16" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="2" customFormat="1" ht="63">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C17" s="2">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E17" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="E18" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C19" s="2">
-        <v>2</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" s="2" customFormat="1" ht="47.25">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C21" s="2">
-        <v>4</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="E21" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="2" customFormat="1" ht="47.25">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C22" s="2">
-        <v>5</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="E22" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C23" s="2">
-        <v>6</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="E23" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="2" customFormat="1">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C24" s="2">
-        <v>7</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="E24" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" s="2" customFormat="1">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="E25" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="2" customFormat="1">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C26" s="2">
-        <v>2</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="E26" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="2" customFormat="1" ht="47.25">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C27" s="2">
-        <v>3</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="E27" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C28" s="2">
-        <v>4</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="E28" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C29" s="2">
-        <v>5</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="E29" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" s="2" customFormat="1" ht="78.75">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C30" s="2">
-        <v>6</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="E31" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C32" s="2">
-        <v>2</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="E32" s="4">
-        <v>44944.721134259256</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="2" customFormat="1">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="C33" s="2">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="4">
-        <v>44944.729699074072</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="2" customFormat="1">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="C34" s="2">
-        <v>1</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="4">
-        <v>44944.729988425926</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" s="2" customFormat="1">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C35" s="2">
-        <v>2</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="4">
-        <v>44944.728692129633</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="2" customFormat="1">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="C36" s="2">
-        <v>1</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="4">
-        <v>44944.730671296296</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" s="2" customFormat="1">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C37" s="2">
-        <v>2</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="4">
-        <v>44944.731365740743</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="2" customFormat="1">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="C38" s="2">
-        <v>1</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="4">
-        <v>44944.731944444444</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="2" customFormat="1">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C39" s="2">
-        <v>2</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E39" s="4">
-        <v>44944.732581018521</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" s="2" customFormat="1">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C40" s="2">
-        <v>3</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="4">
-        <v>44944.732546296298</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="2" customFormat="1">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="C41" s="2">
-        <v>2</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" s="4">
-        <v>44944.729699074072</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="2" customFormat="1">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="C42" s="2">
-        <v>3</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="4">
-        <v>44944.729699074072</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" s="2" customFormat="1">
-      <c r="A43" s="2">
-        <v>42</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C43" s="2">
-        <v>1</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" s="4">
-        <v>44944.728715277779</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" s="2" customFormat="1">
-      <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C44" s="2">
-        <v>3</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="4">
-        <v>44944.72865740741</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="2" customFormat="1">
-      <c r="A45" s="2">
-        <v>44</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="2">
-        <v>4</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="4">
-        <v>44944.728634259256</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="2" customFormat="1">
-      <c r="A46" s="2">
-        <v>45</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C46" s="2">
-        <v>1</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="4">
-        <v>44944.732604166667</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="2" customFormat="1">
-      <c r="A47" s="2">
-        <v>46</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C47" s="2">
-        <v>4</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="E47" s="4">
-        <v>44944.732523148145</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" s="2" customFormat="1">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C48" s="2">
-        <v>1</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="E48" s="4">
-        <v>44944.731400462966</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="2" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="A49" s="2">
-        <v>48</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C49" s="2">
-        <v>3</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" s="4">
-        <v>44944.73133101852</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="2" customFormat="1">
-      <c r="A50" s="2">
-        <v>49</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="C50" s="2">
-        <v>2</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E50" s="4">
-        <v>44978.666134259256</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="B51" s="6"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>50</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="E53" s="8">
-        <v>45126.62222222222</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2">
-        <v>51</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D54" s="10"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2">
-        <v>52</v>
-      </c>
-      <c r="B55" t="s">
-        <v>526</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>528</v>
-      </c>
-      <c r="E55" s="8">
-        <v>45126.62222222222</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="47.25">
-      <c r="A56" s="2">
-        <v>53</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C56" s="2">
-        <v>2</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="E56" s="4">
-        <v>45126.62222222222</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="2">
-        <v>54</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C57" s="2">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E57" s="4">
-        <v>45126.62222222222</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="2">
-        <v>55</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="E58" s="4">
-        <v>45126.62222222222</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="2">
-        <v>56</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="C59" s="2">
-        <v>1</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="E59" s="4">
-        <v>45126.62222222222</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="2">
-        <v>57</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E60" s="4">
-        <v>45126.62222222222</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="2">
-        <v>58</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C61" s="2">
-        <v>2</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E61" s="4">
-        <v>45126.62222222222</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="2">
-        <v>59</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E62" s="4">
+      <c r="D62" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E62" s="6">
         <v>45126.62222222222</v>
       </c>
     </row>
@@ -3988,868 +4087,869 @@
   <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="5.5" customWidth="1"/>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="6.875" customWidth="1"/>
-    <col min="4" max="4" width="177" customWidth="1"/>
-    <col min="5" max="5" width="20.375" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="8" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="8" customWidth="1"/>
+    <col min="3" max="3" width="6.875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="177" style="8" customWidth="1"/>
+    <col min="5" max="5" width="20.375" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" s="3" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1">
-      <c r="A2" s="2">
+    <row r="2" spans="1:4" s="3" customFormat="1">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="3" customFormat="1" ht="47.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A3" s="2">
+      <c r="D7" s="5" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="3" customFormat="1">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="D8" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C10" s="3">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A4" s="2">
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="3" customFormat="1">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="47.25">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C13" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="D13" s="5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="3" customFormat="1">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="3" customFormat="1">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="3" customFormat="1" ht="47.25">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C16" s="3">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A5" s="2">
+      <c r="D16" s="5" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="3" customFormat="1" ht="63">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C17" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C5" s="2">
+      <c r="D17" s="5" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="3" customFormat="1">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="3" customFormat="1">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="3" customFormat="1" ht="47.25">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="3" customFormat="1" ht="63">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="3">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" ht="47.25">
-      <c r="A6" s="2">
+      <c r="D21" s="5" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="3" customFormat="1" ht="63">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="D22" s="5" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="3">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="3" customFormat="1">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" s="3">
+        <v>7</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="3" customFormat="1">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="3" customFormat="1">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="3" customFormat="1" ht="47.25">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C27" s="3">
+        <v>3</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C28" s="3">
+        <v>4</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29" s="3">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="2" customFormat="1">
-      <c r="A7" s="2">
+      <c r="D29" s="5" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="3" customFormat="1" ht="78.75">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C30" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="D30" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C31" s="3">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="2" customFormat="1">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="D31" s="5" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="3" customFormat="1" ht="31.5">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C32" s="3">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="D32" s="5" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" s="3" customFormat="1">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C33" s="3">
         <v>1</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C10" s="2">
+      <c r="D33" s="5" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" s="3" customFormat="1">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" s="3" customFormat="1">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C35" s="3">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="D35" s="5" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="3" customFormat="1">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" s="3" customFormat="1">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C37" s="3">
+        <v>2</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="3" customFormat="1">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" s="3" customFormat="1">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" s="3" customFormat="1">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" s="3" customFormat="1">
+      <c r="A41" s="3">
+        <v>51</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C41" s="3">
+        <v>2</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" s="3" customFormat="1">
+      <c r="A42" s="3">
+        <v>52</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" s="3" customFormat="1">
+      <c r="A43" s="3">
+        <v>53</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" s="3" customFormat="1">
+      <c r="A44" s="3">
+        <v>54</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C44" s="3">
+        <v>3</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" s="3" customFormat="1">
+      <c r="A45" s="3">
+        <v>55</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C45" s="3">
         <v>4</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="2" customFormat="1">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C12" s="2">
-        <v>5</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="2" customFormat="1" ht="47.25">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="D45" s="5" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" s="3" customFormat="1">
+      <c r="A46" s="3">
+        <v>56</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" s="3" customFormat="1">
+      <c r="A47" s="3">
+        <v>57</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C47" s="3">
+        <v>4</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" s="3" customFormat="1">
+      <c r="A48" s="3">
+        <v>58</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="3" customFormat="1" ht="17.100000000000001" customHeight="1">
+      <c r="A49" s="3">
+        <v>59</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C49" s="3">
         <v>3</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="2" customFormat="1">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="D49" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="3" customFormat="1" ht="31.5">
+      <c r="A50" s="3">
+        <v>70</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C50" s="3">
+        <v>2</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C53" s="3">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="D53" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="E53" s="9"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D54" s="10"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3">
+        <v>52</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="C55" s="8">
+        <v>1</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="E55" s="9"/>
+    </row>
+    <row r="56" spans="1:5" ht="47.25">
+      <c r="A56" s="3">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C56" s="3">
         <v>2</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" ht="47.25">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" ht="63">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C17" s="2">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="2" customFormat="1">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="D56" s="11" t="s">
+        <v>671</v>
+      </c>
+      <c r="E56" s="6"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C57" s="3">
         <v>1</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="2" customFormat="1">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="D57" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="E57" s="6"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="E58" s="6"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="E59" s="6"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="E60" s="6"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C61" s="3">
         <v>2</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" ht="47.25">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" ht="63">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C21" s="2">
-        <v>4</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" ht="78.75">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C22" s="2">
-        <v>5</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C23" s="2">
-        <v>6</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="D61" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="E61" s="6"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" s="2" customFormat="1">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C24" s="2">
-        <v>7</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="2" customFormat="1">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="2" customFormat="1">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C26" s="2">
-        <v>2</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="2" customFormat="1" ht="47.25">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C27" s="2">
-        <v>3</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="2" customFormat="1" ht="78.75">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C28" s="2">
-        <v>4</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C29" s="2">
-        <v>5</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="2" customFormat="1" ht="78.75">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C30" s="2">
-        <v>6</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" s="2" customFormat="1" ht="31.5">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C32" s="2">
-        <v>2</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="2" customFormat="1">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="C33" s="2">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" s="2" customFormat="1">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="C34" s="2">
-        <v>1</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" s="2" customFormat="1">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C35" s="2">
-        <v>2</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="2" customFormat="1">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="C36" s="2">
-        <v>1</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" s="2" customFormat="1">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C37" s="2">
-        <v>2</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" s="2" customFormat="1">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="C38" s="2">
-        <v>1</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" s="2" customFormat="1">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C39" s="2">
-        <v>2</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" s="2" customFormat="1">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C40" s="2">
-        <v>3</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" s="2" customFormat="1">
-      <c r="A41" s="2">
-        <v>51</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="C41" s="2">
-        <v>2</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" s="2" customFormat="1">
-      <c r="A42" s="2">
-        <v>52</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="C42" s="2">
-        <v>3</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" s="2" customFormat="1">
-      <c r="A43" s="2">
-        <v>53</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C43" s="2">
-        <v>1</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" s="2" customFormat="1">
-      <c r="A44" s="2">
-        <v>54</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C44" s="2">
-        <v>3</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" s="2" customFormat="1">
-      <c r="A45" s="2">
-        <v>55</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="2">
-        <v>4</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" s="2" customFormat="1">
-      <c r="A46" s="2">
-        <v>56</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C46" s="2">
-        <v>1</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" s="2" customFormat="1">
-      <c r="A47" s="2">
-        <v>57</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C47" s="2">
-        <v>4</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" s="2" customFormat="1">
-      <c r="A48" s="2">
-        <v>58</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C48" s="2">
-        <v>1</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="2" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="A49" s="2">
-        <v>59</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C49" s="2">
-        <v>3</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="2" customFormat="1" ht="31.5">
-      <c r="A50" s="2">
-        <v>70</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="C50" s="2">
-        <v>2</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>50</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="E53" s="8"/>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2">
-        <v>51</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D54" s="10"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2">
-        <v>52</v>
-      </c>
-      <c r="B55" t="s">
-        <v>526</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>563</v>
-      </c>
-      <c r="E55" s="8"/>
-    </row>
-    <row r="56" spans="1:5" ht="47.25">
-      <c r="A56" s="2">
-        <v>53</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C56" s="2">
-        <v>2</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="E56" s="4"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="2">
-        <v>54</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C57" s="2">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="E57" s="4"/>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="2">
-        <v>55</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="E58" s="4"/>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="2">
-        <v>56</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="C59" s="2">
-        <v>1</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="E59" s="4"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="2">
-        <v>57</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="E60" s="4"/>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="2">
-        <v>58</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C61" s="2">
-        <v>2</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E61" s="4"/>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="2">
-        <v>59</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E62" s="4"/>
+      <c r="E62" s="6"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="D64" s="9"/>
+      <c r="D64" s="11"/>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" s="12"/>
     </row>
     <row r="66" spans="4:4">
-      <c r="D66" s="9"/>
+      <c r="D66" s="11"/>
     </row>
     <row r="67" spans="4:4">
-      <c r="D67" s="11"/>
+      <c r="D67" s="13"/>
     </row>
     <row r="68" spans="4:4">
       <c r="D68" s="12"/>
@@ -4881,28 +4981,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
         <v>341</v>
       </c>
-      <c r="C1" t="s">
-        <v>342</v>
-      </c>
       <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4910,16 +5010,16 @@
         <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>641</v>
+        <v>618</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4927,16 +5027,16 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
         <v>235</v>
       </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G3" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4944,16 +5044,16 @@
         <v>116</v>
       </c>
       <c r="B4" t="s">
+        <v>389</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
         <v>390</v>
       </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4961,16 +5061,16 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" t="s">
         <v>163</v>
       </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>164</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>566</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4978,16 +5078,16 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
         <v>161</v>
       </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>162</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -4995,25 +5095,25 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
         <v>43</v>
       </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>571</v>
+        <v>548</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -5021,25 +5121,25 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
         <v>46</v>
       </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -5047,16 +5147,16 @@
         <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5064,16 +5164,16 @@
         <v>139</v>
       </c>
       <c r="B10" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5081,16 +5181,16 @@
         <v>140</v>
       </c>
       <c r="B11" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -5098,16 +5198,16 @@
         <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>572</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -5115,16 +5215,16 @@
         <v>76</v>
       </c>
       <c r="B13" t="s">
+        <v>255</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>422</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="D13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>423</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -5132,30 +5232,30 @@
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="B15" t="s">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>613</v>
+        <v>590</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>614</v>
+        <v>591</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -5163,16 +5263,16 @@
         <v>52</v>
       </c>
       <c r="B16" t="s">
+        <v>201</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
         <v>202</v>
       </c>
-      <c r="D16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="G16" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5180,16 +5280,16 @@
         <v>111</v>
       </c>
       <c r="B17" t="s">
+        <v>331</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
         <v>332</v>
       </c>
-      <c r="D17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" t="s">
-        <v>333</v>
-      </c>
       <c r="G17" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5197,16 +5297,16 @@
         <v>110</v>
       </c>
       <c r="B18" t="s">
+        <v>328</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
         <v>329</v>
       </c>
-      <c r="D18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="G18" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -5214,16 +5314,16 @@
         <v>51</v>
       </c>
       <c r="B19" t="s">
+        <v>377</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>376</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="D19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" t="s">
-        <v>377</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -5231,16 +5331,16 @@
         <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>651</v>
+        <v>628</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
+        <v>333</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -5248,16 +5348,16 @@
         <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>642</v>
+        <v>619</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -5265,16 +5365,16 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
+        <v>277</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
         <v>278</v>
       </c>
-      <c r="D22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>279</v>
-      </c>
       <c r="G22" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5282,16 +5382,16 @@
         <v>85</v>
       </c>
       <c r="B23" t="s">
+        <v>275</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" t="s">
         <v>276</v>
       </c>
-      <c r="D23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" t="s">
-        <v>277</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5299,16 +5399,16 @@
         <v>97</v>
       </c>
       <c r="B24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>573</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5316,16 +5416,16 @@
         <v>134</v>
       </c>
       <c r="B25" t="s">
-        <v>643</v>
+        <v>620</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5333,16 +5433,16 @@
         <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>644</v>
+        <v>621</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -5350,16 +5450,16 @@
         <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>645</v>
+        <v>622</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27" t="s">
+        <v>230</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -5367,16 +5467,16 @@
         <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s">
+        <v>287</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5384,16 +5484,16 @@
         <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>647</v>
+        <v>624</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E29" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5401,16 +5501,16 @@
         <v>113</v>
       </c>
       <c r="B30" t="s">
-        <v>648</v>
+        <v>625</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E30" t="s">
+        <v>335</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5418,16 +5518,16 @@
         <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>649</v>
+        <v>626</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31" t="s">
+        <v>228</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5435,16 +5535,16 @@
         <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>650</v>
+        <v>627</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>640</v>
+        <v>617</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -5452,30 +5552,30 @@
         <v>137</v>
       </c>
       <c r="B33" t="s">
+        <v>441</v>
+      </c>
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" t="s">
         <v>442</v>
       </c>
-      <c r="D33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="G33" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="B34" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -5483,25 +5583,25 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
+        <v>374</v>
+      </c>
+      <c r="D35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" t="s">
         <v>375</v>
       </c>
-      <c r="D35" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" t="s">
-        <v>376</v>
-      </c>
       <c r="F35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -5509,33 +5609,33 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>664</v>
+        <v>641</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>575</v>
+        <v>552</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37">
         <v>122</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>658</v>
+      <c r="B37" s="2" t="s">
+        <v>635</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E37" t="s">
+        <v>402</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -5543,16 +5643,16 @@
         <v>120</v>
       </c>
       <c r="B38" t="s">
+        <v>398</v>
+      </c>
+      <c r="D38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" t="s">
         <v>399</v>
       </c>
-      <c r="D38" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" t="s">
-        <v>400</v>
-      </c>
       <c r="G38" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -5560,16 +5660,16 @@
         <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>663</v>
+        <v>640</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E39" t="s">
+        <v>282</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -5577,16 +5677,16 @@
         <v>129</v>
       </c>
       <c r="B40" t="s">
+        <v>416</v>
+      </c>
+      <c r="D40" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" t="s">
         <v>417</v>
       </c>
-      <c r="D40" t="s">
-        <v>38</v>
-      </c>
-      <c r="E40" t="s">
-        <v>418</v>
-      </c>
       <c r="G40" s="1" t="s">
-        <v>576</v>
+        <v>553</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -5594,16 +5694,16 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" t="s">
         <v>209</v>
       </c>
-      <c r="D41" t="s">
-        <v>38</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="G41" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -5611,16 +5711,16 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
+        <v>211</v>
+      </c>
+      <c r="D42" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" t="s">
         <v>212</v>
       </c>
-      <c r="D42" t="s">
-        <v>38</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="G42" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -5628,16 +5728,16 @@
         <v>90</v>
       </c>
       <c r="B43" t="s">
+        <v>285</v>
+      </c>
+      <c r="D43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" t="s">
         <v>286</v>
       </c>
-      <c r="D43" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" t="s">
-        <v>287</v>
-      </c>
       <c r="G43" s="1" t="s">
-        <v>577</v>
+        <v>554</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -5645,16 +5745,16 @@
         <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5662,16 +5762,16 @@
         <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E45" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5679,25 +5779,25 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" t="s">
+        <v>37</v>
+      </c>
+      <c r="E46" t="s">
+        <v>373</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D46" t="s">
-        <v>38</v>
-      </c>
-      <c r="E46" t="s">
-        <v>374</v>
-      </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="I46" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5705,25 +5805,25 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" t="s">
+        <v>359</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D47" t="s">
-        <v>38</v>
-      </c>
-      <c r="E47" t="s">
-        <v>360</v>
-      </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="I47" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5731,30 +5831,30 @@
         <v>106</v>
       </c>
       <c r="B48" t="s">
+        <v>321</v>
+      </c>
+      <c r="D48" t="s">
+        <v>37</v>
+      </c>
+      <c r="E48" t="s">
         <v>322</v>
       </c>
-      <c r="D48" t="s">
-        <v>38</v>
-      </c>
-      <c r="E48" t="s">
-        <v>323</v>
-      </c>
       <c r="G48" s="1" t="s">
-        <v>578</v>
+        <v>555</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="B49" t="s">
-        <v>616</v>
+        <v>593</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E49" t="s">
-        <v>617</v>
+        <v>594</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5762,16 +5862,16 @@
         <v>61</v>
       </c>
       <c r="B50" t="s">
+        <v>225</v>
+      </c>
+      <c r="D50" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" t="s">
         <v>226</v>
       </c>
-      <c r="D50" t="s">
-        <v>38</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="G50" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5779,16 +5879,16 @@
         <v>107</v>
       </c>
       <c r="B51" t="s">
+        <v>323</v>
+      </c>
+      <c r="D51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" t="s">
         <v>324</v>
       </c>
-      <c r="D51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51" t="s">
-        <v>325</v>
-      </c>
       <c r="G51" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5796,16 +5896,16 @@
         <v>98</v>
       </c>
       <c r="B52" t="s">
+        <v>302</v>
+      </c>
+      <c r="D52" t="s">
+        <v>37</v>
+      </c>
+      <c r="E52" t="s">
         <v>303</v>
       </c>
-      <c r="D52" t="s">
-        <v>38</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="G52" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5813,16 +5913,16 @@
         <v>93</v>
       </c>
       <c r="B53" t="s">
+        <v>291</v>
+      </c>
+      <c r="D53" t="s">
+        <v>37</v>
+      </c>
+      <c r="E53" t="s">
         <v>292</v>
       </c>
-      <c r="D53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E53" t="s">
-        <v>293</v>
-      </c>
       <c r="G53" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5830,30 +5930,30 @@
         <v>94</v>
       </c>
       <c r="B54" t="s">
+        <v>293</v>
+      </c>
+      <c r="D54" t="s">
+        <v>37</v>
+      </c>
+      <c r="E54" t="s">
         <v>294</v>
       </c>
-      <c r="D54" t="s">
-        <v>38</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="G54" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="B55" t="s">
-        <v>619</v>
+        <v>596</v>
       </c>
       <c r="D55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E55" t="s">
-        <v>620</v>
+        <v>597</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>621</v>
+        <v>598</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5861,30 +5961,30 @@
         <v>38</v>
       </c>
       <c r="B56" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56" t="s">
+        <v>37</v>
+      </c>
+      <c r="E56" t="s">
         <v>168</v>
       </c>
-      <c r="D56" t="s">
-        <v>38</v>
-      </c>
-      <c r="E56" t="s">
-        <v>169</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>579</v>
+        <v>556</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="B57" t="s">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E57" t="s">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>580</v>
+        <v>557</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5892,25 +5992,25 @@
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>652</v>
+        <v>629</v>
       </c>
       <c r="D58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E58" t="s">
+        <v>49</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="G58" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="H58" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5918,16 +6018,16 @@
         <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>653</v>
+        <v>630</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E59" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>611</v>
+        <v>588</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5935,25 +6035,25 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>654</v>
+        <v>631</v>
       </c>
       <c r="D60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E60" t="s">
+        <v>85</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="G60" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="H60" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5961,16 +6061,16 @@
         <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>655</v>
+        <v>632</v>
       </c>
       <c r="D61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E61" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5978,25 +6078,25 @@
         <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>656</v>
+        <v>633</v>
       </c>
       <c r="D62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E62" t="s">
+        <v>88</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="G62" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="H62" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -6004,16 +6104,16 @@
         <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>657</v>
+        <v>634</v>
       </c>
       <c r="D63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E63" t="s">
+        <v>325</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -6021,25 +6121,25 @@
         <v>21</v>
       </c>
       <c r="B64" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" t="s">
+        <v>37</v>
+      </c>
+      <c r="E64" t="s">
         <v>115</v>
       </c>
-      <c r="D64" t="s">
-        <v>38</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="F64" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="G64" s="1" t="s">
-        <v>581</v>
+        <v>558</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -6047,30 +6147,30 @@
         <v>123</v>
       </c>
       <c r="B65" t="s">
+        <v>404</v>
+      </c>
+      <c r="D65" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" t="s">
         <v>405</v>
       </c>
-      <c r="D65" t="s">
-        <v>38</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="G65" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="B66" t="s">
-        <v>625</v>
+        <v>602</v>
       </c>
       <c r="D66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E66" t="s">
-        <v>626</v>
+        <v>603</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>627</v>
+        <v>604</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -6078,19 +6178,19 @@
         <v>60</v>
       </c>
       <c r="B67" t="s">
+        <v>222</v>
+      </c>
+      <c r="D67" t="s">
+        <v>37</v>
+      </c>
+      <c r="E67" t="s">
         <v>223</v>
       </c>
-      <c r="D67" t="s">
-        <v>38</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>224</v>
       </c>
-      <c r="F67" t="s">
-        <v>225</v>
-      </c>
       <c r="G67" s="1" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -6098,25 +6198,25 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
+        <v>127</v>
+      </c>
+      <c r="D68" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" t="s">
         <v>128</v>
       </c>
-      <c r="D68" t="s">
-        <v>78</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="F68" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="G68" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -6124,25 +6224,25 @@
         <v>28</v>
       </c>
       <c r="B69" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" t="s">
+        <v>37</v>
+      </c>
+      <c r="E69" t="s">
         <v>142</v>
       </c>
-      <c r="D69" t="s">
-        <v>38</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="F69" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="G69" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="H69" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="I69" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -6150,25 +6250,25 @@
         <v>16</v>
       </c>
       <c r="B70" t="s">
+        <v>91</v>
+      </c>
+      <c r="D70" t="s">
+        <v>37</v>
+      </c>
+      <c r="E70" t="s">
         <v>92</v>
       </c>
-      <c r="D70" t="s">
-        <v>38</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="F70" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="G70" s="1" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -6176,25 +6276,25 @@
         <v>26</v>
       </c>
       <c r="B71" t="s">
+        <v>130</v>
+      </c>
+      <c r="D71" t="s">
+        <v>77</v>
+      </c>
+      <c r="E71" t="s">
         <v>131</v>
       </c>
-      <c r="D71" t="s">
-        <v>78</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="G71" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="H71" s="1" t="s">
+      <c r="I71" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -6202,16 +6302,16 @@
         <v>124</v>
       </c>
       <c r="B72" t="s">
-        <v>659</v>
+        <v>636</v>
       </c>
       <c r="D72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E72" t="s">
+        <v>407</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -6219,16 +6319,16 @@
         <v>104</v>
       </c>
       <c r="B73" t="s">
+        <v>317</v>
+      </c>
+      <c r="D73" t="s">
+        <v>37</v>
+      </c>
+      <c r="E73" t="s">
         <v>318</v>
       </c>
-      <c r="D73" t="s">
-        <v>38</v>
-      </c>
-      <c r="E73" t="s">
-        <v>319</v>
-      </c>
       <c r="G73" s="1" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -6236,16 +6336,16 @@
         <v>125</v>
       </c>
       <c r="B74" t="s">
-        <v>660</v>
+        <v>637</v>
       </c>
       <c r="D74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E74" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -6253,16 +6353,16 @@
         <v>109</v>
       </c>
       <c r="B75" t="s">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="D75" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E75" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -6270,25 +6370,25 @@
         <v>29</v>
       </c>
       <c r="B76" t="s">
+        <v>147</v>
+      </c>
+      <c r="D76" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" t="s">
         <v>148</v>
       </c>
-      <c r="D76" t="s">
-        <v>38</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="F76" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="H76" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -6296,30 +6396,30 @@
         <v>141</v>
       </c>
       <c r="B77" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="D77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E77" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="B78" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
       <c r="D78" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E78" t="s">
-        <v>606</v>
+        <v>583</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6327,16 +6427,16 @@
         <v>119</v>
       </c>
       <c r="B79" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E79" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6344,30 +6444,30 @@
         <v>118</v>
       </c>
       <c r="B80" t="s">
+        <v>394</v>
+      </c>
+      <c r="D80" t="s">
+        <v>37</v>
+      </c>
+      <c r="E80" t="s">
         <v>395</v>
       </c>
-      <c r="D80" t="s">
-        <v>38</v>
-      </c>
-      <c r="E80" t="s">
-        <v>396</v>
-      </c>
       <c r="G80" s="1" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="B81" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="D81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E81" t="s">
-        <v>629</v>
+        <v>606</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>630</v>
+        <v>607</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -6375,16 +6475,16 @@
         <v>74</v>
       </c>
       <c r="B82" t="s">
+        <v>250</v>
+      </c>
+      <c r="D82" t="s">
+        <v>37</v>
+      </c>
+      <c r="E82" t="s">
         <v>251</v>
       </c>
-      <c r="D82" t="s">
-        <v>38</v>
-      </c>
-      <c r="E82" t="s">
-        <v>252</v>
-      </c>
       <c r="G82" s="1" t="s">
-        <v>587</v>
+        <v>564</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -6392,16 +6492,16 @@
         <v>75</v>
       </c>
       <c r="B83" t="s">
+        <v>252</v>
+      </c>
+      <c r="D83" t="s">
+        <v>37</v>
+      </c>
+      <c r="E83" t="s">
         <v>253</v>
       </c>
-      <c r="D83" t="s">
-        <v>38</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="G83" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -6409,16 +6509,16 @@
         <v>81</v>
       </c>
       <c r="B84" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="D84" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E84" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -6426,16 +6526,16 @@
         <v>71</v>
       </c>
       <c r="B85" t="s">
+        <v>242</v>
+      </c>
+      <c r="D85" t="s">
+        <v>37</v>
+      </c>
+      <c r="E85" t="s">
         <v>243</v>
       </c>
-      <c r="D85" t="s">
-        <v>38</v>
-      </c>
-      <c r="E85" t="s">
-        <v>244</v>
-      </c>
       <c r="G85" s="1" t="s">
-        <v>588</v>
+        <v>565</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -6443,16 +6543,16 @@
         <v>73</v>
       </c>
       <c r="B86" t="s">
+        <v>247</v>
+      </c>
+      <c r="D86" t="s">
+        <v>37</v>
+      </c>
+      <c r="E86" t="s">
         <v>248</v>
       </c>
-      <c r="D86" t="s">
-        <v>38</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="G86" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -6460,16 +6560,16 @@
         <v>72</v>
       </c>
       <c r="B87" t="s">
+        <v>244</v>
+      </c>
+      <c r="D87" t="s">
+        <v>37</v>
+      </c>
+      <c r="E87" t="s">
         <v>245</v>
       </c>
-      <c r="D87" t="s">
-        <v>38</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="G87" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6477,16 +6577,16 @@
         <v>80</v>
       </c>
       <c r="B88" t="s">
+        <v>263</v>
+      </c>
+      <c r="D88" t="s">
+        <v>77</v>
+      </c>
+      <c r="E88" t="s">
         <v>264</v>
       </c>
-      <c r="D88" t="s">
-        <v>78</v>
-      </c>
-      <c r="E88" t="s">
-        <v>265</v>
-      </c>
       <c r="G88" s="1" t="s">
-        <v>564</v>
+        <v>541</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6494,16 +6594,16 @@
         <v>79</v>
       </c>
       <c r="B89" t="s">
+        <v>261</v>
+      </c>
+      <c r="D89" t="s">
+        <v>77</v>
+      </c>
+      <c r="E89" t="s">
         <v>262</v>
       </c>
-      <c r="D89" t="s">
-        <v>78</v>
-      </c>
-      <c r="E89" t="s">
-        <v>263</v>
-      </c>
       <c r="G89" s="1" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6511,16 +6611,16 @@
         <v>69</v>
       </c>
       <c r="B90" t="s">
+        <v>450</v>
+      </c>
+      <c r="D90" t="s">
+        <v>77</v>
+      </c>
+      <c r="E90" t="s">
         <v>451</v>
       </c>
-      <c r="D90" t="s">
-        <v>78</v>
-      </c>
-      <c r="E90" t="s">
-        <v>452</v>
-      </c>
       <c r="G90" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6528,16 +6628,16 @@
         <v>103</v>
       </c>
       <c r="B91" t="s">
+        <v>315</v>
+      </c>
+      <c r="D91" t="s">
+        <v>37</v>
+      </c>
+      <c r="E91" t="s">
+        <v>379</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="D91" t="s">
-        <v>38</v>
-      </c>
-      <c r="E91" t="s">
-        <v>380</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6545,16 +6645,16 @@
         <v>102</v>
       </c>
       <c r="B92" t="s">
+        <v>313</v>
+      </c>
+      <c r="D92" t="s">
+        <v>37</v>
+      </c>
+      <c r="E92" t="s">
         <v>314</v>
       </c>
-      <c r="D92" t="s">
-        <v>38</v>
-      </c>
-      <c r="E92" t="s">
-        <v>315</v>
-      </c>
       <c r="G92" s="1" t="s">
-        <v>589</v>
+        <v>566</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6562,16 +6662,16 @@
         <v>83</v>
       </c>
       <c r="B93" t="s">
+        <v>269</v>
+      </c>
+      <c r="D93" t="s">
+        <v>37</v>
+      </c>
+      <c r="E93" t="s">
         <v>270</v>
       </c>
-      <c r="D93" t="s">
-        <v>38</v>
-      </c>
-      <c r="E93" t="s">
+      <c r="G93" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6579,16 +6679,16 @@
         <v>82</v>
       </c>
       <c r="B94" t="s">
+        <v>266</v>
+      </c>
+      <c r="D94" t="s">
+        <v>37</v>
+      </c>
+      <c r="E94" t="s">
         <v>267</v>
       </c>
-      <c r="D94" t="s">
-        <v>38</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="G94" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6596,16 +6696,16 @@
         <v>84</v>
       </c>
       <c r="B95" t="s">
+        <v>272</v>
+      </c>
+      <c r="D95" t="s">
+        <v>37</v>
+      </c>
+      <c r="E95" t="s">
         <v>273</v>
       </c>
-      <c r="D95" t="s">
-        <v>38</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="G95" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6613,16 +6713,16 @@
         <v>99</v>
       </c>
       <c r="B96" t="s">
+        <v>305</v>
+      </c>
+      <c r="D96" t="s">
+        <v>37</v>
+      </c>
+      <c r="E96" t="s">
         <v>306</v>
       </c>
-      <c r="D96" t="s">
-        <v>38</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="G96" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6630,16 +6730,16 @@
         <v>87</v>
       </c>
       <c r="B97" t="s">
+        <v>279</v>
+      </c>
+      <c r="D97" t="s">
+        <v>37</v>
+      </c>
+      <c r="E97" t="s">
         <v>280</v>
       </c>
-      <c r="D97" t="s">
-        <v>38</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="G97" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6647,16 +6747,16 @@
         <v>126</v>
       </c>
       <c r="B98" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="D98" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E98" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6664,25 +6764,25 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="D99" t="s">
+        <v>77</v>
+      </c>
+      <c r="E99" t="s">
         <v>78</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F99" s="1" t="s">
+      <c r="G99" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H99" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G99" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="H99" s="1" t="s">
+      <c r="I99" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6690,25 +6790,25 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="D100" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E100" t="s">
+        <v>53</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F100" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G100" s="1" t="s">
-        <v>591</v>
+        <v>568</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6716,16 +6816,16 @@
         <v>127</v>
       </c>
       <c r="B101" t="s">
-        <v>668</v>
+        <v>645</v>
       </c>
       <c r="D101" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E101" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6733,16 +6833,16 @@
         <v>39</v>
       </c>
       <c r="B102" t="s">
+        <v>169</v>
+      </c>
+      <c r="D102" t="s">
+        <v>37</v>
+      </c>
+      <c r="E102" t="s">
         <v>170</v>
       </c>
-      <c r="D102" t="s">
-        <v>38</v>
-      </c>
-      <c r="E102" t="s">
-        <v>171</v>
-      </c>
       <c r="G102" s="1" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6750,33 +6850,33 @@
         <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D103" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E103" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F103" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="B104" t="s">
-        <v>631</v>
+        <v>608</v>
       </c>
       <c r="D104" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E104" t="s">
-        <v>632</v>
+        <v>609</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6784,25 +6884,25 @@
         <v>22</v>
       </c>
       <c r="B105" t="s">
+        <v>117</v>
+      </c>
+      <c r="D105" t="s">
+        <v>37</v>
+      </c>
+      <c r="E105" t="s">
         <v>118</v>
       </c>
-      <c r="D105" t="s">
-        <v>38</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="F105" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="G105" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="H105" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="I105" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6810,25 +6910,25 @@
         <v>30</v>
       </c>
       <c r="B106" t="s">
+        <v>151</v>
+      </c>
+      <c r="D106" t="s">
+        <v>37</v>
+      </c>
+      <c r="E106" t="s">
         <v>152</v>
       </c>
-      <c r="D106" t="s">
-        <v>38</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="F106" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="G106" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G106" s="1" t="s">
+      <c r="H106" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6836,25 +6936,25 @@
         <v>17</v>
       </c>
       <c r="B107" t="s">
+        <v>94</v>
+      </c>
+      <c r="D107" t="s">
+        <v>37</v>
+      </c>
+      <c r="E107" t="s">
         <v>95</v>
       </c>
-      <c r="D107" t="s">
-        <v>38</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="F107" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="G107" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G107" s="1" t="s">
+      <c r="H107" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="I107" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6862,25 +6962,25 @@
         <v>19</v>
       </c>
       <c r="B108" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" t="s">
+        <v>37</v>
+      </c>
+      <c r="E108" t="s">
         <v>106</v>
       </c>
-      <c r="D108" t="s">
-        <v>38</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="F108" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="G108" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="G108" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="H108" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6888,25 +6988,25 @@
         <v>18</v>
       </c>
       <c r="B109" t="s">
+        <v>99</v>
+      </c>
+      <c r="D109" t="s">
+        <v>37</v>
+      </c>
+      <c r="E109" t="s">
         <v>100</v>
       </c>
-      <c r="D109" t="s">
-        <v>38</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F109" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="G109" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G109" s="1" t="s">
+      <c r="H109" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H109" s="1" t="s">
+      <c r="I109" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6914,25 +7014,25 @@
         <v>23</v>
       </c>
       <c r="B110" t="s">
+        <v>367</v>
+      </c>
+      <c r="D110" t="s">
+        <v>37</v>
+      </c>
+      <c r="E110" t="s">
         <v>368</v>
       </c>
-      <c r="D110" t="s">
-        <v>38</v>
-      </c>
-      <c r="E110" t="s">
-        <v>369</v>
-      </c>
       <c r="F110" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6940,16 +7040,16 @@
         <v>128</v>
       </c>
       <c r="B111" t="s">
+        <v>414</v>
+      </c>
+      <c r="D111" t="s">
+        <v>37</v>
+      </c>
+      <c r="E111" t="s">
         <v>415</v>
       </c>
-      <c r="D111" t="s">
-        <v>38</v>
-      </c>
-      <c r="E111" t="s">
-        <v>416</v>
-      </c>
       <c r="G111" s="1" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6957,16 +7057,16 @@
         <v>95</v>
       </c>
       <c r="B112" t="s">
+        <v>296</v>
+      </c>
+      <c r="D112" t="s">
+        <v>37</v>
+      </c>
+      <c r="E112" t="s">
         <v>297</v>
       </c>
-      <c r="D112" t="s">
-        <v>38</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="G112" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -6974,16 +7074,16 @@
         <v>101</v>
       </c>
       <c r="B113" t="s">
+        <v>311</v>
+      </c>
+      <c r="D113" t="s">
+        <v>37</v>
+      </c>
+      <c r="E113" t="s">
         <v>312</v>
       </c>
-      <c r="D113" t="s">
-        <v>38</v>
-      </c>
-      <c r="E113" t="s">
-        <v>313</v>
-      </c>
       <c r="G113" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -6991,16 +7091,16 @@
         <v>100</v>
       </c>
       <c r="B114" t="s">
+        <v>308</v>
+      </c>
+      <c r="D114" t="s">
+        <v>37</v>
+      </c>
+      <c r="E114" t="s">
         <v>309</v>
       </c>
-      <c r="D114" t="s">
-        <v>38</v>
-      </c>
-      <c r="E114" t="s">
-        <v>310</v>
-      </c>
       <c r="G114" s="1" t="s">
-        <v>607</v>
+        <v>584</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7008,16 +7108,16 @@
         <v>105</v>
       </c>
       <c r="B115" t="s">
+        <v>319</v>
+      </c>
+      <c r="D115" t="s">
+        <v>37</v>
+      </c>
+      <c r="E115" t="s">
         <v>320</v>
       </c>
-      <c r="D115" t="s">
-        <v>38</v>
-      </c>
-      <c r="E115" t="s">
-        <v>321</v>
-      </c>
       <c r="G115" s="1" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7025,16 +7125,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D116" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E116" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>595</v>
+        <v>572</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7042,16 +7142,16 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
+        <v>426</v>
+      </c>
+      <c r="D117" t="s">
+        <v>37</v>
+      </c>
+      <c r="E117" t="s">
         <v>427</v>
       </c>
-      <c r="D117" t="s">
-        <v>38</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="G117" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7059,25 +7159,25 @@
         <v>20</v>
       </c>
       <c r="B118" t="s">
+        <v>109</v>
+      </c>
+      <c r="D118" t="s">
+        <v>37</v>
+      </c>
+      <c r="E118" t="s">
+        <v>380</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D118" t="s">
-        <v>38</v>
-      </c>
-      <c r="E118" t="s">
-        <v>381</v>
-      </c>
-      <c r="F118" s="1" t="s">
+      <c r="G118" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="H118" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H118" s="1" t="s">
+      <c r="I118" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7085,25 +7185,25 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
+        <v>82</v>
+      </c>
+      <c r="D119" t="s">
+        <v>37</v>
+      </c>
+      <c r="E119" t="s">
         <v>83</v>
       </c>
-      <c r="D119" t="s">
-        <v>38</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="F119" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F119" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="G119" s="1" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7111,25 +7211,25 @@
         <v>24</v>
       </c>
       <c r="B120" t="s">
-        <v>662</v>
+        <v>639</v>
       </c>
       <c r="D120" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E120" t="s">
+        <v>122</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="G120" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G120" s="1" t="s">
+      <c r="H120" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="I120" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7137,44 +7237,44 @@
         <v>132</v>
       </c>
       <c r="B121" t="s">
+        <v>429</v>
+      </c>
+      <c r="D121" t="s">
+        <v>37</v>
+      </c>
+      <c r="E121" t="s">
         <v>430</v>
       </c>
-      <c r="D121" t="s">
-        <v>38</v>
-      </c>
-      <c r="E121" t="s">
+      <c r="G121" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="B122" t="s">
-        <v>634</v>
+        <v>611</v>
       </c>
       <c r="D122" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E122" t="s">
-        <v>635</v>
+        <v>612</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>636</v>
+        <v>613</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="B123" t="s">
-        <v>622</v>
+        <v>599</v>
       </c>
       <c r="D123" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E123" t="s">
-        <v>623</v>
+        <v>600</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>624</v>
+        <v>601</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7182,25 +7282,25 @@
         <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D124" t="s">
+        <v>37</v>
+      </c>
+      <c r="E124" t="s">
         <v>38</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="G124" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G124" s="1" t="s">
+      <c r="H124" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H124" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="I124" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7208,25 +7308,25 @@
         <v>8</v>
       </c>
       <c r="B125" t="s">
+        <v>63</v>
+      </c>
+      <c r="D125" t="s">
+        <v>37</v>
+      </c>
+      <c r="E125" t="s">
         <v>64</v>
       </c>
-      <c r="D125" t="s">
-        <v>38</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="F125" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="G125" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H125" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G125" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="I125" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7234,25 +7334,25 @@
         <v>6</v>
       </c>
       <c r="B126" t="s">
+        <v>55</v>
+      </c>
+      <c r="D126" t="s">
+        <v>37</v>
+      </c>
+      <c r="E126" t="s">
         <v>56</v>
       </c>
-      <c r="D126" t="s">
-        <v>38</v>
-      </c>
-      <c r="E126" t="s">
+      <c r="F126" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="G126" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G126" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="H126" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7260,25 +7360,25 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
+        <v>365</v>
+      </c>
+      <c r="D127" t="s">
+        <v>37</v>
+      </c>
+      <c r="E127" t="s">
         <v>366</v>
       </c>
-      <c r="D127" t="s">
-        <v>38</v>
-      </c>
-      <c r="E127" t="s">
-        <v>367</v>
-      </c>
       <c r="F127" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G127" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G127" s="1" t="s">
+      <c r="H127" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="I127" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7286,25 +7386,25 @@
         <v>27</v>
       </c>
       <c r="B128" t="s">
+        <v>135</v>
+      </c>
+      <c r="D128" t="s">
+        <v>37</v>
+      </c>
+      <c r="E128" t="s">
         <v>136</v>
       </c>
-      <c r="D128" t="s">
-        <v>38</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="F128" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="G128" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G128" s="1" t="s">
+      <c r="H128" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H128" s="1" t="s">
+      <c r="I128" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -7312,16 +7412,16 @@
         <v>121</v>
       </c>
       <c r="B129" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D129" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E129" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -7329,16 +7429,16 @@
         <v>54</v>
       </c>
       <c r="B130" t="s">
+        <v>206</v>
+      </c>
+      <c r="D130" t="s">
+        <v>77</v>
+      </c>
+      <c r="E130" t="s">
         <v>207</v>
       </c>
-      <c r="D130" t="s">
-        <v>78</v>
-      </c>
-      <c r="E130" t="s">
-        <v>208</v>
-      </c>
       <c r="G130" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -7346,16 +7446,16 @@
         <v>53</v>
       </c>
       <c r="B131" t="s">
+        <v>204</v>
+      </c>
+      <c r="D131" t="s">
+        <v>77</v>
+      </c>
+      <c r="E131" t="s">
         <v>205</v>
       </c>
-      <c r="D131" t="s">
-        <v>78</v>
-      </c>
-      <c r="E131" t="s">
-        <v>206</v>
-      </c>
       <c r="G131" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -7363,30 +7463,30 @@
         <v>92</v>
       </c>
       <c r="B132" t="s">
+        <v>289</v>
+      </c>
+      <c r="D132" t="s">
+        <v>37</v>
+      </c>
+      <c r="E132" t="s">
+        <v>224</v>
+      </c>
+      <c r="G132" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="D132" t="s">
-        <v>38</v>
-      </c>
-      <c r="E132" t="s">
-        <v>225</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="B133" t="s">
-        <v>637</v>
+        <v>614</v>
       </c>
       <c r="D133" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E133" t="s">
-        <v>638</v>
+        <v>615</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>639</v>
+        <v>616</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7394,16 +7494,16 @@
         <v>77</v>
       </c>
       <c r="B134" t="s">
+        <v>257</v>
+      </c>
+      <c r="D134" t="s">
+        <v>37</v>
+      </c>
+      <c r="E134" t="s">
         <v>258</v>
       </c>
-      <c r="D134" t="s">
-        <v>38</v>
-      </c>
-      <c r="E134" t="s">
-        <v>259</v>
-      </c>
       <c r="G134" s="1" t="s">
-        <v>598</v>
+        <v>575</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7411,16 +7511,16 @@
         <v>78</v>
       </c>
       <c r="B135" t="s">
+        <v>259</v>
+      </c>
+      <c r="D135" t="s">
+        <v>37</v>
+      </c>
+      <c r="E135" t="s">
         <v>260</v>
       </c>
-      <c r="D135" t="s">
-        <v>38</v>
-      </c>
-      <c r="E135" t="s">
-        <v>261</v>
-      </c>
       <c r="G135" s="1" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7428,16 +7528,16 @@
         <v>46</v>
       </c>
       <c r="B136" t="s">
+        <v>189</v>
+      </c>
+      <c r="D136" t="s">
+        <v>37</v>
+      </c>
+      <c r="E136" t="s">
         <v>190</v>
       </c>
-      <c r="D136" t="s">
-        <v>38</v>
-      </c>
-      <c r="E136" t="s">
+      <c r="G136" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7445,16 +7545,16 @@
         <v>43</v>
       </c>
       <c r="B137" t="s">
+        <v>180</v>
+      </c>
+      <c r="D137" t="s">
+        <v>37</v>
+      </c>
+      <c r="E137" t="s">
         <v>181</v>
       </c>
-      <c r="D137" t="s">
-        <v>38</v>
-      </c>
-      <c r="E137" t="s">
+      <c r="G137" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7462,16 +7562,16 @@
         <v>45</v>
       </c>
       <c r="B138" t="s">
+        <v>186</v>
+      </c>
+      <c r="D138" t="s">
+        <v>37</v>
+      </c>
+      <c r="E138" t="s">
         <v>187</v>
       </c>
-      <c r="D138" t="s">
-        <v>38</v>
-      </c>
-      <c r="E138" t="s">
+      <c r="G138" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7479,16 +7579,16 @@
         <v>42</v>
       </c>
       <c r="B139" t="s">
+        <v>177</v>
+      </c>
+      <c r="D139" t="s">
+        <v>37</v>
+      </c>
+      <c r="E139" t="s">
         <v>178</v>
       </c>
-      <c r="D139" t="s">
-        <v>38</v>
-      </c>
-      <c r="E139" t="s">
+      <c r="G139" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7496,16 +7596,16 @@
         <v>50</v>
       </c>
       <c r="B140" t="s">
+        <v>198</v>
+      </c>
+      <c r="D140" t="s">
+        <v>37</v>
+      </c>
+      <c r="E140" t="s">
         <v>199</v>
       </c>
-      <c r="D140" t="s">
-        <v>38</v>
-      </c>
-      <c r="E140" t="s">
+      <c r="G140" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7513,16 +7613,16 @@
         <v>49</v>
       </c>
       <c r="B141" t="s">
+        <v>196</v>
+      </c>
+      <c r="D141" t="s">
+        <v>37</v>
+      </c>
+      <c r="E141" t="s">
         <v>197</v>
       </c>
-      <c r="D141" t="s">
-        <v>38</v>
-      </c>
-      <c r="E141" t="s">
-        <v>198</v>
-      </c>
       <c r="G141" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7530,16 +7630,16 @@
         <v>44</v>
       </c>
       <c r="B142" t="s">
+        <v>183</v>
+      </c>
+      <c r="D142" t="s">
+        <v>37</v>
+      </c>
+      <c r="E142" t="s">
         <v>184</v>
       </c>
-      <c r="D142" t="s">
-        <v>38</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="G142" t="s">
         <v>185</v>
-      </c>
-      <c r="G142" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7547,16 +7647,16 @@
         <v>41</v>
       </c>
       <c r="B143" t="s">
+        <v>174</v>
+      </c>
+      <c r="D143" t="s">
+        <v>37</v>
+      </c>
+      <c r="E143" t="s">
         <v>175</v>
       </c>
-      <c r="D143" t="s">
-        <v>38</v>
-      </c>
-      <c r="E143" t="s">
+      <c r="G143" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7564,16 +7664,16 @@
         <v>40</v>
       </c>
       <c r="B144" t="s">
+        <v>171</v>
+      </c>
+      <c r="D144" t="s">
+        <v>37</v>
+      </c>
+      <c r="E144" t="s">
         <v>172</v>
       </c>
-      <c r="D144" t="s">
-        <v>38</v>
-      </c>
-      <c r="E144" t="s">
+      <c r="G144" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -7581,16 +7681,16 @@
         <v>37</v>
       </c>
       <c r="B145" t="s">
+        <v>164</v>
+      </c>
+      <c r="D145" t="s">
+        <v>37</v>
+      </c>
+      <c r="E145" t="s">
         <v>165</v>
       </c>
-      <c r="D145" t="s">
-        <v>38</v>
-      </c>
-      <c r="E145" t="s">
+      <c r="G145" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -7598,16 +7698,16 @@
         <v>48</v>
       </c>
       <c r="B146" t="s">
+        <v>193</v>
+      </c>
+      <c r="D146" t="s">
+        <v>37</v>
+      </c>
+      <c r="E146" t="s">
         <v>194</v>
       </c>
-      <c r="D146" t="s">
-        <v>38</v>
-      </c>
-      <c r="E146" t="s">
+      <c r="G146" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -7615,16 +7715,16 @@
         <v>114</v>
       </c>
       <c r="B147" t="s">
+        <v>337</v>
+      </c>
+      <c r="D147" t="s">
+        <v>37</v>
+      </c>
+      <c r="E147" t="s">
         <v>338</v>
       </c>
-      <c r="D147" t="s">
-        <v>38</v>
-      </c>
-      <c r="E147" t="s">
+      <c r="G147" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -7632,30 +7732,30 @@
         <v>47</v>
       </c>
       <c r="B148" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D148" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E148" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="B149" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="D149" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E149" t="s">
-        <v>568</v>
+        <v>545</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>615</v>
+        <v>592</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -7663,16 +7763,16 @@
         <v>117</v>
       </c>
       <c r="B150" t="s">
+        <v>392</v>
+      </c>
+      <c r="D150" t="s">
+        <v>37</v>
+      </c>
+      <c r="E150" t="s">
         <v>393</v>
       </c>
-      <c r="D150" t="s">
-        <v>38</v>
-      </c>
-      <c r="E150" t="s">
-        <v>394</v>
-      </c>
       <c r="G150" s="1" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -7680,30 +7780,30 @@
         <v>96</v>
       </c>
       <c r="B151" t="s">
+        <v>299</v>
+      </c>
+      <c r="D151" t="s">
+        <v>37</v>
+      </c>
+      <c r="E151" t="s">
         <v>300</v>
       </c>
-      <c r="D151" t="s">
-        <v>38</v>
-      </c>
-      <c r="E151" t="s">
-        <v>301</v>
-      </c>
       <c r="G151" s="1" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="B152" t="s">
-        <v>570</v>
+        <v>547</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E152" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -7711,16 +7811,16 @@
         <v>57</v>
       </c>
       <c r="B153" t="s">
+        <v>214</v>
+      </c>
+      <c r="D153" t="s">
+        <v>37</v>
+      </c>
+      <c r="E153" t="s">
         <v>215</v>
       </c>
-      <c r="D153" t="s">
-        <v>38</v>
-      </c>
-      <c r="E153" t="s">
-        <v>216</v>
-      </c>
       <c r="G153" s="1" t="s">
-        <v>603</v>
+        <v>580</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -7728,16 +7828,16 @@
         <v>59</v>
       </c>
       <c r="B154" t="s">
+        <v>219</v>
+      </c>
+      <c r="D154" t="s">
+        <v>37</v>
+      </c>
+      <c r="E154" t="s">
         <v>220</v>
       </c>
-      <c r="D154" t="s">
-        <v>38</v>
-      </c>
-      <c r="E154" t="s">
+      <c r="G154" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -7745,16 +7845,16 @@
         <v>58</v>
       </c>
       <c r="B155" t="s">
+        <v>216</v>
+      </c>
+      <c r="D155" t="s">
+        <v>37</v>
+      </c>
+      <c r="E155" t="s">
         <v>217</v>
       </c>
-      <c r="D155" t="s">
-        <v>38</v>
-      </c>
-      <c r="E155" t="s">
+      <c r="G155" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -7762,16 +7862,16 @@
         <v>136</v>
       </c>
       <c r="B156" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D156" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E156" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/CUQ/_docs/Notes.xlsx
+++ b/CUQ/_docs/Notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gruber04\git_repos\BIPM\Semantic-SI\CUQ\_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fmeynadier\git_projects\SI-Reference-Point-2023\CUQ\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAF9511-BE2B-4822-A852-96CD9A0C43CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DABC3E-DC47-43F4-A646-CA2F228465B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-8310" windowWidth="38640" windowHeight="21390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="2265" windowWidth="23325" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="en" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="673">
   <si>
     <t>id</t>
   </si>
@@ -2692,48 +2692,48 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Akzent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Akzent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Akzent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Akzent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Akzent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Akzent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Ausgabe" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Berechnung" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Eingabe" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Ergebnis" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Erklärender Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Überschrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Überschrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Überschrift 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Überschrift 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Verknüpfte Zelle" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Avertissement" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Calcul" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Cellule liée" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Entrée" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Insatisfaisant" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Neutre" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Satisfaisant" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Sortie" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texte explicatif" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Titre" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Titre 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Titre 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Titre 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Titre 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Vérification" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2754,7 +2754,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4817,7 +4817,12 @@
       <c r="B54" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D54" s="10"/>
+      <c r="C54" s="8">
+        <v>1</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>509</v>
+      </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3">
@@ -4959,6 +4964,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/CUQ/_docs/Notes.xlsx
+++ b/CUQ/_docs/Notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\fmeynadier\git_projects\SI-Reference-Point-2023\CUQ\_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DABC3E-DC47-43F4-A646-CA2F228465B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8373D1A5-9029-470B-AB07-1EE3A80F6201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="2265" windowWidth="23325" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5445" yWindow="1890" windowWidth="23325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="en" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="673">
   <si>
     <t>id</t>
   </si>
@@ -2147,7 +2147,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2301,10 +2301,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="TimesNewRomanPSMT"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2663,7 +2659,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2684,12 +2680,11 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3051,7 +3046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5" style="8" customWidth="1"/>
     <col min="2" max="2" width="16.875" style="8" customWidth="1"/>
@@ -3061,7 +3056,7 @@
     <col min="6" max="16384" width="11" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>342</v>
       </c>
@@ -3078,7 +3073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="3" customFormat="1">
+    <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -3095,7 +3090,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="3" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -3112,7 +3107,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="4" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -3129,7 +3124,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="5" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -3146,7 +3141,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="6" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -3163,7 +3158,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1">
+    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -3180,7 +3175,7 @@
         <v>45104.336331018516</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="3" customFormat="1">
+    <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3197,7 +3192,7 @@
         <v>45104.365567129629</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="9" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -3214,7 +3209,7 @@
         <v>45105.140208333331</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="10" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3231,7 +3226,7 @@
         <v>45105.154224537036</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="11" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3248,7 +3243,7 @@
         <v>45105.16302083333</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="3" customFormat="1">
+    <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3265,7 +3260,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="13" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3282,7 +3277,7 @@
         <v>45105.158726851849</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="14" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3299,7 +3294,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="3" customFormat="1">
+    <row r="15" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3316,7 +3311,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="3" customFormat="1" ht="47.25">
+    <row r="16" spans="1:5" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3333,7 +3328,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="63">
+    <row r="17" spans="1:5" s="3" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3350,7 +3345,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="18" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -3367,7 +3362,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="3" customFormat="1">
+    <row r="19" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -3384,7 +3379,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="3" customFormat="1" ht="47.25">
+    <row r="20" spans="1:5" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3401,7 +3396,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="21" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3418,7 +3413,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="3" customFormat="1" ht="47.25">
+    <row r="22" spans="1:5" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3435,7 +3430,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="23" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3452,7 +3447,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="3" customFormat="1">
+    <row r="24" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3469,7 +3464,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="3" customFormat="1">
+    <row r="25" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3486,7 +3481,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="3" customFormat="1">
+    <row r="26" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3503,7 +3498,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="3" customFormat="1" ht="47.25">
+    <row r="27" spans="1:5" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3520,7 +3515,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="28" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3537,7 +3532,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="29" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3554,7 +3549,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="3" customFormat="1" ht="78.75">
+    <row r="30" spans="1:5" s="3" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3571,7 +3566,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="31" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3588,7 +3583,7 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="32" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3605,7 +3600,7 @@
         <v>44944.721134259256</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="3" customFormat="1">
+    <row r="33" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3622,7 +3617,7 @@
         <v>44944.729699074072</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="3" customFormat="1">
+    <row r="34" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3639,7 +3634,7 @@
         <v>44944.729988425926</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="3" customFormat="1">
+    <row r="35" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3656,7 +3651,7 @@
         <v>44944.728692129633</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="3" customFormat="1">
+    <row r="36" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3673,7 +3668,7 @@
         <v>44944.730671296296</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="3" customFormat="1">
+    <row r="37" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3690,7 +3685,7 @@
         <v>44944.731365740743</v>
       </c>
     </row>
-    <row r="38" spans="1:5" s="3" customFormat="1">
+    <row r="38" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3707,7 +3702,7 @@
         <v>44944.731944444444</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="3" customFormat="1">
+    <row r="39" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -3724,7 +3719,7 @@
         <v>44944.732581018521</v>
       </c>
     </row>
-    <row r="40" spans="1:5" s="3" customFormat="1">
+    <row r="40" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3741,7 +3736,7 @@
         <v>44944.732546296298</v>
       </c>
     </row>
-    <row r="41" spans="1:5" s="3" customFormat="1">
+    <row r="41" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3758,7 +3753,7 @@
         <v>44944.729699074072</v>
       </c>
     </row>
-    <row r="42" spans="1:5" s="3" customFormat="1">
+    <row r="42" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -3775,7 +3770,7 @@
         <v>44944.729699074072</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="3" customFormat="1">
+    <row r="43" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -3792,7 +3787,7 @@
         <v>44944.728715277779</v>
       </c>
     </row>
-    <row r="44" spans="1:5" s="3" customFormat="1">
+    <row r="44" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -3809,7 +3804,7 @@
         <v>44944.72865740741</v>
       </c>
     </row>
-    <row r="45" spans="1:5" s="3" customFormat="1">
+    <row r="45" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3826,7 +3821,7 @@
         <v>44944.728634259256</v>
       </c>
     </row>
-    <row r="46" spans="1:5" s="3" customFormat="1">
+    <row r="46" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -3843,7 +3838,7 @@
         <v>44944.732604166667</v>
       </c>
     </row>
-    <row r="47" spans="1:5" s="3" customFormat="1">
+    <row r="47" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -3860,7 +3855,7 @@
         <v>44944.732523148145</v>
       </c>
     </row>
-    <row r="48" spans="1:5" s="3" customFormat="1">
+    <row r="48" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -3877,7 +3872,7 @@
         <v>44944.731400462966</v>
       </c>
     </row>
-    <row r="49" spans="1:5" s="3" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="49" spans="1:5" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -3894,7 +3889,7 @@
         <v>44944.73133101852</v>
       </c>
     </row>
-    <row r="50" spans="1:5" s="3" customFormat="1">
+    <row r="50" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -3911,10 +3906,10 @@
         <v>44978.666134259256</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B51" s="7"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -3931,16 +3926,21 @@
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D54" s="10"/>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="C54" s="8">
+        <v>1</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="47.25">
+    <row r="56" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -3967,14 +3967,14 @@
       <c r="C56" s="3">
         <v>2</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="10" t="s">
         <v>658</v>
       </c>
       <c r="E56" s="6">
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -4001,14 +4001,14 @@
       <c r="C58" s="3">
         <v>1</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="10" t="s">
         <v>514</v>
       </c>
       <c r="E58" s="6">
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -4018,14 +4018,14 @@
       <c r="C59" s="3">
         <v>1</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="10" t="s">
         <v>514</v>
       </c>
       <c r="E59" s="6">
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -4042,7 +4042,7 @@
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>45126.62222222222</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -4085,7 +4085,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C76578C5-08B3-574F-BA8C-FE251C939966}">
   <dimension ref="A1:E70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5" style="8" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="8" customWidth="1"/>
@@ -4095,7 +4095,7 @@
     <col min="6" max="16384" width="11" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1">
+    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="3" customFormat="1">
+    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" ht="47.25">
+    <row r="6" spans="1:4" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1">
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="3" customFormat="1">
+    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="3" customFormat="1">
+    <row r="12" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" ht="47.25">
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="3" customFormat="1">
+    <row r="14" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="3" customFormat="1">
+    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="3" customFormat="1" ht="47.25">
+    <row r="16" spans="1:4" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="3" customFormat="1" ht="63">
+    <row r="17" spans="1:4" s="3" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="3" customFormat="1">
+    <row r="18" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="3" customFormat="1">
+    <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="3" customFormat="1" ht="47.25">
+    <row r="20" spans="1:4" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="3" customFormat="1" ht="63">
+    <row r="21" spans="1:4" s="3" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="3" customFormat="1" ht="63">
+    <row r="22" spans="1:4" s="3" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="23" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="3" customFormat="1">
+    <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="3" customFormat="1">
+    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="3" customFormat="1">
+    <row r="26" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="3" customFormat="1" ht="47.25">
+    <row r="27" spans="1:4" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="28" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="29" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="29" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="30" spans="1:4" s="3" customFormat="1" ht="78.75">
+    <row r="30" spans="1:4" s="3" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="31" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="31" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="32" spans="1:4" s="3" customFormat="1" ht="31.5">
+    <row r="32" spans="1:4" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="33" spans="1:4" s="3" customFormat="1">
+    <row r="33" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="34" spans="1:4" s="3" customFormat="1">
+    <row r="34" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="35" spans="1:4" s="3" customFormat="1">
+    <row r="35" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="36" spans="1:4" s="3" customFormat="1">
+    <row r="36" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="37" spans="1:4" s="3" customFormat="1">
+    <row r="37" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="38" spans="1:4" s="3" customFormat="1">
+    <row r="38" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="39" spans="1:4" s="3" customFormat="1">
+    <row r="39" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="40" spans="1:4" s="3" customFormat="1">
+    <row r="40" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="41" spans="1:4" s="3" customFormat="1">
+    <row r="41" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>51</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="42" spans="1:4" s="3" customFormat="1">
+    <row r="42" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>52</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="43" spans="1:4" s="3" customFormat="1">
+    <row r="43" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>53</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="44" spans="1:4" s="3" customFormat="1">
+    <row r="44" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>54</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="45" spans="1:4" s="3" customFormat="1">
+    <row r="45" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>55</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="46" spans="1:4" s="3" customFormat="1">
+    <row r="46" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>56</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="47" spans="1:4" s="3" customFormat="1">
+    <row r="47" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>57</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="48" spans="1:4" s="3" customFormat="1">
+    <row r="48" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>58</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="49" spans="1:5" s="3" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="49" spans="1:5" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>59</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="50" spans="1:5" s="3" customFormat="1" ht="31.5">
+    <row r="50" spans="1:5" s="3" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>70</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="E53" s="9"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="E55" s="9"/>
     </row>
-    <row r="56" spans="1:5" ht="47.25">
+    <row r="56" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -4849,12 +4849,12 @@
       <c r="C56" s="3">
         <v>2</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="10" t="s">
         <v>671</v>
       </c>
       <c r="E56" s="6"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="E57" s="6"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -4879,12 +4879,12 @@
       <c r="C58" s="3">
         <v>1</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="10" t="s">
         <v>672</v>
       </c>
       <c r="E58" s="6"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -4894,12 +4894,12 @@
       <c r="C59" s="3">
         <v>1</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="10" t="s">
         <v>672</v>
       </c>
       <c r="E59" s="6"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -4909,12 +4909,12 @@
       <c r="C60" s="3">
         <v>1</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="10" t="s">
         <v>650</v>
       </c>
       <c r="E60" s="6"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="E61" s="6"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -4944,23 +4944,23 @@
       </c>
       <c r="E62" s="6"/>
     </row>
-    <row r="64" spans="1:5">
-      <c r="D64" s="11"/>
-    </row>
-    <row r="65" spans="4:4">
-      <c r="D65" s="12"/>
-    </row>
-    <row r="66" spans="4:4">
-      <c r="D66" s="11"/>
-    </row>
-    <row r="67" spans="4:4">
-      <c r="D67" s="13"/>
-    </row>
-    <row r="68" spans="4:4">
-      <c r="D68" s="12"/>
-    </row>
-    <row r="70" spans="4:4">
-      <c r="D70" s="12"/>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D64" s="10"/>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D65" s="11"/>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D66" s="10"/>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D67" s="12"/>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D68" s="11"/>
+    </row>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D70" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4971,7 +4971,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396D6CEF-66BA-914C-BC20-42B24F721DE4}">
   <dimension ref="A1:I156"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
@@ -4982,7 +4982,7 @@
     <col min="9" max="9" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>67</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>66</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>116</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>35</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>34</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
@@ -5148,7 +5148,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>130</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>139</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>140</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>70</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>76</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>68</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>589</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>52</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>111</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>110</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>51</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>112</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>65</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>86</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>85</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>97</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>134</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>133</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>63</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>91</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>135</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>113</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>62</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>64</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>137</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>455</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>10</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>32</v>
       </c>
@@ -5627,7 +5627,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>122</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>120</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>88</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>129</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>55</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>56</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>90</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>33</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>36</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>7</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>9</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>106</v>
       </c>
@@ -5849,7 +5849,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>593</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>61</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>107</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>98</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>93</v>
       </c>
@@ -5931,7 +5931,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>94</v>
       </c>
@@ -5948,7 +5948,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>596</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>38</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>586</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>4</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>89</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>14</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>31</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>15</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>108</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>21</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>123</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>602</v>
       </c>
@@ -6179,7 +6179,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>60</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>25</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>28</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>16</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>26</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>124</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>104</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>125</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>109</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>29</v>
       </c>
@@ -6397,7 +6397,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>141</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>582</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>119</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>118</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>605</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>74</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>75</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>81</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>71</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>73</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>72</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>80</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>79</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>69</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>103</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>102</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>83</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>82</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>84</v>
       </c>
@@ -6714,7 +6714,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>99</v>
       </c>
@@ -6731,7 +6731,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>87</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>126</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>12</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>5</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>127</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>39</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>138</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>608</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>22</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>30</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>17</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>19</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>18</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>23</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>128</v>
       </c>
@@ -7058,7 +7058,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>95</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>101</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>100</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>105</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>131</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>20</v>
       </c>
@@ -7186,7 +7186,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>13</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>24</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>132</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>611</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>599</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>1</v>
       </c>
@@ -7309,7 +7309,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>8</v>
       </c>
@@ -7335,7 +7335,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>6</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>11</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>27</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>121</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>54</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>53</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>92</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>614</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>77</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>78</v>
       </c>
@@ -7529,7 +7529,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>46</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>43</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>45</v>
       </c>
@@ -7580,7 +7580,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>42</v>
       </c>
@@ -7597,7 +7597,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>50</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>49</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>44</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>41</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>40</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>37</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>48</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>114</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>47</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
         <v>544</v>
       </c>
@@ -7764,7 +7764,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>117</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>96</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
         <v>547</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>57</v>
       </c>
@@ -7829,7 +7829,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>59</v>
       </c>
@@ -7846,7 +7846,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>58</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>136</v>
       </c>
